--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,6 +532,166 @@
       <c r="T1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SPAL.NS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SPAL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>72.38</v>
+      </c>
+      <c r="G2" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1159.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1005.45</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1338.58</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1517.45</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>AUTO_ANCILLARY</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 72.4, need 83), TQ_FAIL(got 54.9, need 73)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>MONITOR</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>48.415</v>
+      </c>
+      <c r="G3" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1012.55</v>
+      </c>
+      <c r="J3" t="n">
+        <v>912.17</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1134.16</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1255.76</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 48.4, need 83), TQ_FAIL(got 59.9, need 73)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -764,7 +924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T121"/>
+  <dimension ref="A1:T119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,41 +1037,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UTLSOLAR.NS</t>
+          <t>IKS.NS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>IKS</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73.7</v>
+        <v>70.5</v>
       </c>
       <c r="E2" t="n">
-        <v>86.06</v>
+        <v>76.61499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>364.5</v>
+        <v>1928.1</v>
       </c>
       <c r="I2" t="n">
-        <v>311.06</v>
+        <v>1715.77</v>
       </c>
       <c r="J2" t="n">
-        <v>402.67</v>
+        <v>2079.76</v>
       </c>
       <c r="K2" t="n">
-        <v>444.66</v>
+        <v>2246.59</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -923,10 +1083,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>58</v>
+        <v>40.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0.41</v>
+        <v>0.27</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -935,7 +1095,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>TQ_FAIL(got 61.0, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=22&gt;top6)</t>
+          <t>CONF_FAIL(got 76.6, need 83), TQ_FAIL(got 69.4, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -957,41 +1117,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JBCHEPHARM.NS</t>
+          <t>CEMPRO.NS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>JBCHEPHARM</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>64.5</v>
       </c>
       <c r="E3" t="n">
-        <v>84.13500000000001</v>
+        <v>74.86</v>
       </c>
       <c r="F3" t="n">
-        <v>66.7</v>
+        <v>48.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H3" t="n">
-        <v>2444.5</v>
+        <v>1566.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2248.94</v>
+        <v>1331.78</v>
       </c>
       <c r="J3" t="n">
-        <v>2561.73</v>
+        <v>1736.57</v>
       </c>
       <c r="K3" t="n">
-        <v>2737.84</v>
+        <v>1919.33</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1003,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>18.9</v>
+        <v>27.8</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1015,12 +1175,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 74.9, need 83), TQ_FAIL(got 48.6, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1037,41 +1197,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ARTEMISMED.NS</t>
+          <t>POLYPLEX.NS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARTEMISMED</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>83.54000000000001</v>
+        <v>72.52</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>70.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.79</v>
+        <v>1.69</v>
       </c>
       <c r="H4" t="n">
-        <v>268</v>
+        <v>1060.55</v>
       </c>
       <c r="I4" t="n">
-        <v>256.71</v>
+        <v>945.45</v>
       </c>
       <c r="J4" t="n">
-        <v>288.3</v>
+        <v>1163.63</v>
       </c>
       <c r="K4" t="n">
-        <v>308.61</v>
+        <v>1266.71</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1083,24 +1243,24 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>1.12</v>
       </c>
       <c r="P4" t="n">
-        <v>0.28</v>
+        <v>0.13</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(1.1%&lt;10%)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1117,41 +1277,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GANESHHOU.NS</t>
+          <t>JINDALSAW.NS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>JINDALSAW</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>83.29000000000001</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>66.2</v>
+        <v>75.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>866.15</v>
+        <v>275.8</v>
       </c>
       <c r="I5" t="n">
-        <v>757.21</v>
+        <v>247.36</v>
       </c>
       <c r="J5" t="n">
-        <v>943.96</v>
+        <v>296.73</v>
       </c>
       <c r="K5" t="n">
-        <v>1029.56</v>
+        <v>318.46</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1163,24 +1323,24 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>15.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1197,41 +1357,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ANANDRATHI.NS</t>
+          <t>PHOENIXLTD.NS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>73.5</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>82.55</v>
+        <v>71.45</v>
       </c>
       <c r="F6" t="n">
-        <v>67.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>1.43</v>
       </c>
       <c r="H6" t="n">
-        <v>2095.6</v>
+        <v>2138.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1886.92</v>
+        <v>1924.22</v>
       </c>
       <c r="J6" t="n">
-        <v>2252.11</v>
+        <v>2292.24</v>
       </c>
       <c r="K6" t="n">
-        <v>2408.62</v>
+        <v>2460.92</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1243,24 +1403,24 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>47.3</v>
+        <v>11.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 71.5, need 83), TQ_FAIL(got 64.1, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1277,41 +1437,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GOODLUCK.NS</t>
+          <t>GODREJPROP.NS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>75.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>81.78</v>
+        <v>70.83</v>
       </c>
       <c r="F7" t="n">
-        <v>73.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>1549.8</v>
+        <v>2133</v>
       </c>
       <c r="I7" t="n">
-        <v>1391.01</v>
+        <v>1925.62</v>
       </c>
       <c r="J7" t="n">
-        <v>1679.8</v>
+        <v>2281.13</v>
       </c>
       <c r="K7" t="n">
-        <v>1809.8</v>
+        <v>2444.07</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1323,10 +1483,10 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>12.9</v>
+        <v>8.82</v>
       </c>
       <c r="P7" t="n">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1335,12 +1495,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 70.8, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1357,41 +1517,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POLYPLEX.NS</t>
+          <t>TSFINV.NS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>76.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>81.23999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="F8" t="n">
-        <v>60.1</v>
+        <v>61.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="n">
-        <v>1029.45</v>
+        <v>475.4</v>
       </c>
       <c r="I8" t="n">
-        <v>945.45</v>
+        <v>414.85</v>
       </c>
       <c r="J8" t="n">
-        <v>1128.32</v>
+        <v>518.65</v>
       </c>
       <c r="K8" t="n">
-        <v>1227.19</v>
+        <v>566.22</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1403,24 +1563,24 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.12</v>
+        <v>8.23</v>
       </c>
       <c r="P8" t="n">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1437,37 +1597,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>QUESS.NS</t>
+          <t>MARKSANS.NS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72.3</v>
+        <v>76.8</v>
       </c>
       <c r="E9" t="n">
-        <v>81.11499999999999</v>
+        <v>70.41500000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65.3</v>
+        <v>70.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.44</v>
+        <v>2.69</v>
       </c>
       <c r="H9" t="n">
-        <v>294.55</v>
+        <v>272.4</v>
       </c>
       <c r="I9" t="n">
-        <v>250.37</v>
+        <v>254.72</v>
       </c>
       <c r="J9" t="n">
-        <v>326.4</v>
+        <v>297.65</v>
       </c>
       <c r="K9" t="n">
-        <v>360.82</v>
+        <v>322.91</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1483,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20.4</v>
+        <v>15.2</v>
       </c>
       <c r="P9" t="n">
         <v>0.11</v>
@@ -1495,12 +1655,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 70.4, need 83), TQ_FAIL(got 70.7, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1517,41 +1677,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL.NS</t>
+          <t>RADICO.NS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74.7</v>
+        <v>67.5</v>
       </c>
       <c r="E10" t="n">
-        <v>80.27</v>
+        <v>70.045</v>
       </c>
       <c r="F10" t="n">
-        <v>73.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="H10" t="n">
-        <v>255.78</v>
+        <v>4073.7</v>
       </c>
       <c r="I10" t="n">
-        <v>225.38</v>
+        <v>3767.07</v>
       </c>
       <c r="J10" t="n">
-        <v>278.5</v>
+        <v>4303.67</v>
       </c>
       <c r="K10" t="n">
-        <v>301.38</v>
+        <v>4533.64</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1563,24 +1723,24 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17.8</v>
+        <v>20.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 70.0, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1597,41 +1757,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JINDALSAW.NS</t>
+          <t>SHREEJISPG.NS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JINDALSAW</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>75.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>80.01000000000001</v>
+        <v>69.88</v>
       </c>
       <c r="F11" t="n">
-        <v>76.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H11" t="n">
-        <v>272.3</v>
+        <v>551.75</v>
       </c>
       <c r="I11" t="n">
-        <v>247.36</v>
+        <v>498.33</v>
       </c>
       <c r="J11" t="n">
-        <v>291</v>
+        <v>589.91</v>
       </c>
       <c r="K11" t="n">
-        <v>309.71</v>
+        <v>631.88</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1643,24 +1803,24 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8.199999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 69.9, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1677,41 +1837,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MARKSANS.NS</t>
+          <t>DIXON.NS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>79.355</v>
+        <v>69.66</v>
       </c>
       <c r="F12" t="n">
-        <v>74.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="H12" t="n">
-        <v>277.3</v>
+        <v>13421</v>
       </c>
       <c r="I12" t="n">
-        <v>254.72</v>
+        <v>11915.75</v>
       </c>
       <c r="J12" t="n">
-        <v>302.22</v>
+        <v>14496.18</v>
       </c>
       <c r="K12" t="n">
-        <v>327.13</v>
+        <v>15678.88</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1723,24 +1883,24 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>15.2</v>
+        <v>37.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 69.7, need 83), TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1757,41 +1917,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TSFINV.NS</t>
+          <t>BHAGCHEM.NS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>BHAGCHEM</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>70.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="E13" t="n">
-        <v>79.2</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>61.7</v>
+        <v>67.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.42</v>
+        <v>2.57</v>
       </c>
       <c r="H13" t="n">
-        <v>473.9</v>
+        <v>295.9</v>
       </c>
       <c r="I13" t="n">
-        <v>415</v>
+        <v>277.8</v>
       </c>
       <c r="J13" t="n">
-        <v>515.97</v>
+        <v>321.23</v>
       </c>
       <c r="K13" t="n">
-        <v>562.25</v>
+        <v>346.55</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1803,24 +1963,24 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>8.23</v>
+        <v>2.63</v>
       </c>
       <c r="P13" t="n">
-        <v>0.04</v>
+        <v>0.34</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(2.6%&lt;10%)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1837,41 +1997,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IOLCP.NS</t>
+          <t>CDSL.NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>68.3</v>
       </c>
       <c r="E14" t="n">
-        <v>78.5</v>
+        <v>69.41</v>
       </c>
       <c r="F14" t="n">
-        <v>54.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>168.15</v>
+        <v>1431.9</v>
       </c>
       <c r="I14" t="n">
-        <v>142.93</v>
+        <v>1314.87</v>
       </c>
       <c r="J14" t="n">
-        <v>189.2</v>
+        <v>1515.49</v>
       </c>
       <c r="K14" t="n">
-        <v>210.24</v>
+        <v>1607.45</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1883,24 +2043,24 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>8.380000000000001</v>
+        <v>24.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 69.4, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1917,41 +2077,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIGNPOST.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SIGNPOST</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E15" t="n">
         <v>69.40000000000001</v>
       </c>
-      <c r="E15" t="n">
-        <v>77.66</v>
-      </c>
       <c r="F15" t="n">
-        <v>53.1</v>
+        <v>70.5</v>
       </c>
       <c r="G15" t="n">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="H15" t="n">
-        <v>320.1</v>
+        <v>330.1</v>
       </c>
       <c r="I15" t="n">
-        <v>272.09</v>
+        <v>303.25</v>
       </c>
       <c r="J15" t="n">
-        <v>363.74</v>
+        <v>349.28</v>
       </c>
       <c r="K15" t="n">
-        <v>407.37</v>
+        <v>370.38</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1963,24 +2123,24 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>27.6</v>
+        <v>15.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 69.4, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=18&gt;top6)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1997,41 +2157,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GODREJPROP.NS</t>
+          <t>AETHER.NS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>70.2</v>
+        <v>66.8</v>
       </c>
       <c r="E16" t="n">
-        <v>77.42</v>
+        <v>69.28</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H16" t="n">
-        <v>2029.9</v>
+        <v>1500.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1845.17</v>
+        <v>1298.47</v>
       </c>
       <c r="J16" t="n">
-        <v>2161.85</v>
+        <v>1652.54</v>
       </c>
       <c r="K16" t="n">
-        <v>2307</v>
+        <v>1804.29</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2043,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>10.2</v>
+        <v>9.66</v>
       </c>
       <c r="P16" t="n">
-        <v>0.82</v>
+        <v>0.19</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -2055,12 +2215,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2077,41 +2237,41 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>WANBURY.NS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>68.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>77.34</v>
+        <v>69.2</v>
       </c>
       <c r="F17" t="n">
-        <v>59.7</v>
+        <v>73.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="H17" t="n">
-        <v>252.64</v>
+        <v>297.85</v>
       </c>
       <c r="I17" t="n">
-        <v>224.91</v>
+        <v>267.65</v>
       </c>
       <c r="J17" t="n">
-        <v>272.45</v>
+        <v>329.74</v>
       </c>
       <c r="K17" t="n">
-        <v>294.23</v>
+        <v>361.62</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2123,24 +2283,24 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>16.5</v>
+        <v>76.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 69.2, need 83), RR_FAIL(got 1.86, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2157,37 +2317,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SUVEN.NS</t>
+          <t>IOLCP.NS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SUVEN</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>68.8</v>
+        <v>63.6</v>
       </c>
       <c r="E18" t="n">
-        <v>77.22</v>
+        <v>68.98</v>
       </c>
       <c r="F18" t="n">
-        <v>58.6</v>
+        <v>52.2</v>
       </c>
       <c r="G18" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H18" t="n">
-        <v>346.75</v>
+        <v>171.06</v>
       </c>
       <c r="I18" t="n">
-        <v>294.74</v>
+        <v>145.4</v>
       </c>
       <c r="J18" t="n">
-        <v>389.92</v>
+        <v>192.73</v>
       </c>
       <c r="K18" t="n">
-        <v>433.1</v>
+        <v>214.4</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2203,24 +2363,24 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-78.8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2237,41 +2397,41 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHOENIXLTD.NS</t>
+          <t>SPARC.NS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70.8</v>
+        <v>65.3</v>
       </c>
       <c r="E19" t="n">
-        <v>77.155</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>62.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="H19" t="n">
-        <v>2088</v>
+        <v>264.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1883.13</v>
+        <v>224.91</v>
       </c>
       <c r="J19" t="n">
-        <v>2234.34</v>
+        <v>295.01</v>
       </c>
       <c r="K19" t="n">
-        <v>2395.3</v>
+        <v>325.42</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2283,24 +2443,24 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>11.6</v>
+        <v>279</v>
       </c>
       <c r="P19" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 68.8, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.48, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2317,41 +2477,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GCSL.NS</t>
+          <t>CGCL.NS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70.2</v>
+        <v>63.9</v>
       </c>
       <c r="E20" t="n">
-        <v>77.12</v>
+        <v>68.58</v>
       </c>
       <c r="F20" t="n">
-        <v>64.59999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="G20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H20" t="n">
-        <v>489.7</v>
+        <v>252.22</v>
       </c>
       <c r="I20" t="n">
-        <v>427</v>
+        <v>223.14</v>
       </c>
       <c r="J20" t="n">
-        <v>534.49</v>
+        <v>272.99</v>
       </c>
       <c r="K20" t="n">
-        <v>583.75</v>
+        <v>295.84</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2363,24 +2523,24 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8.58</v>
+        <v>16.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0.05</v>
+        <v>3.35</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(3.35&gt;1.50)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2397,37 +2557,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TAJGVK.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TAJGVK</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>69</v>
+        <v>62.1</v>
       </c>
       <c r="E21" t="n">
-        <v>76.575</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>64.7</v>
+        <v>43.1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="H21" t="n">
-        <v>361.95</v>
+        <v>290.7</v>
       </c>
       <c r="I21" t="n">
-        <v>322.43</v>
+        <v>247.09</v>
       </c>
       <c r="J21" t="n">
-        <v>390.81</v>
+        <v>332.64</v>
       </c>
       <c r="K21" t="n">
-        <v>421.23</v>
+        <v>374.58</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2443,24 +2603,24 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>18.4</v>
+        <v>10.7</v>
       </c>
       <c r="P21" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 68.5, need 83), TQ_FAIL(got 43.1, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2477,41 +2637,41 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>TAJGVK.NS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>TAJGVK</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>70.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>76.55</v>
+        <v>68.3</v>
       </c>
       <c r="F22" t="n">
-        <v>69.3</v>
+        <v>63.7</v>
       </c>
       <c r="G22" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H22" t="n">
-        <v>324.05</v>
+        <v>371.7</v>
       </c>
       <c r="I22" t="n">
-        <v>298.65</v>
+        <v>330.26</v>
       </c>
       <c r="J22" t="n">
-        <v>343.07</v>
+        <v>401.3</v>
       </c>
       <c r="K22" t="n">
-        <v>362.15</v>
+        <v>433.86</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2523,24 +2683,24 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>15.3</v>
+        <v>18.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 68.3, need 83), TQ_FAIL(got 63.7, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2557,41 +2717,41 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SPAL.NS</t>
+          <t>LLOYDSENT.NS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SPAL</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68.3</v>
+        <v>69.8</v>
       </c>
       <c r="E23" t="n">
-        <v>76.54000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>44.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>2.13</v>
+        <v>1.74</v>
       </c>
       <c r="H23" t="n">
-        <v>1178.6</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1005.45</v>
+        <v>69.75</v>
       </c>
       <c r="J23" t="n">
-        <v>1368.72</v>
+        <v>85.94</v>
       </c>
       <c r="K23" t="n">
-        <v>1558.83</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2603,24 +2763,24 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>11.2</v>
+        <v>0.33</v>
       </c>
       <c r="P23" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(0.3%&lt;10%)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2637,37 +2797,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SPARC.NS</t>
+          <t>EIEL.NS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="E24" t="n">
-        <v>76.405</v>
+        <v>68.05</v>
       </c>
       <c r="F24" t="n">
-        <v>55.4</v>
+        <v>66.8</v>
       </c>
       <c r="G24" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="H24" t="n">
-        <v>277.57</v>
+        <v>244.49</v>
       </c>
       <c r="I24" t="n">
-        <v>235.93</v>
+        <v>211.29</v>
       </c>
       <c r="J24" t="n">
-        <v>308.59</v>
+        <v>270.1</v>
       </c>
       <c r="K24" t="n">
-        <v>340.03</v>
+        <v>295.7</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2683,24 +2843,24 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>17</v>
       </c>
       <c r="P24" t="n">
-        <v>0.42</v>
+        <v>0.34</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 68.0, need 83), TQ_FAIL(got 66.8, need 73), RR_FAIL(got 1.49, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2717,37 +2877,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SENORES.NS</t>
+          <t>MAHLIFE.NS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SENORES</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>70.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>76.125</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>67.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="H25" t="n">
-        <v>1419.7</v>
+        <v>378.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1260.86</v>
+        <v>353.62</v>
       </c>
       <c r="J25" t="n">
-        <v>1542.36</v>
+        <v>401.29</v>
       </c>
       <c r="K25" t="n">
-        <v>1665.01</v>
+        <v>423.68</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2763,24 +2923,24 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>13.4</v>
+        <v>9.91</v>
       </c>
       <c r="P25" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2797,41 +2957,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SHILPAMED.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>69.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>76.11</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>60.1</v>
+        <v>61.8</v>
       </c>
       <c r="G26" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="H26" t="n">
-        <v>622.3</v>
+        <v>229.33</v>
       </c>
       <c r="I26" t="n">
-        <v>554.17</v>
+        <v>201.82</v>
       </c>
       <c r="J26" t="n">
-        <v>679.4400000000001</v>
+        <v>248.98</v>
       </c>
       <c r="K26" t="n">
-        <v>736.58</v>
+        <v>270.6</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2843,24 +3003,24 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>9.4</v>
+        <v>13.2</v>
       </c>
       <c r="P26" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.9, need 83), TQ_FAIL(got 61.8, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2877,41 +3037,41 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>PNBHOUSING.NS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>68.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="E27" t="n">
-        <v>75.94</v>
+        <v>67.89</v>
       </c>
       <c r="F27" t="n">
-        <v>61.6</v>
+        <v>65.8</v>
       </c>
       <c r="G27" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H27" t="n">
-        <v>229.09</v>
+        <v>1110.6</v>
       </c>
       <c r="I27" t="n">
-        <v>201.76</v>
+        <v>1019.18</v>
       </c>
       <c r="J27" t="n">
-        <v>248.61</v>
+        <v>1179.98</v>
       </c>
       <c r="K27" t="n">
-        <v>270.09</v>
+        <v>1249.36</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2923,24 +3083,24 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(2.77&gt;1.50)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -2957,41 +3117,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>68.7</v>
+        <v>63.1</v>
       </c>
       <c r="E28" t="n">
-        <v>75.45</v>
+        <v>67.8</v>
       </c>
       <c r="F28" t="n">
-        <v>64.59999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="G28" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H28" t="n">
-        <v>1262.9</v>
+        <v>541.05</v>
       </c>
       <c r="I28" t="n">
-        <v>1150.13</v>
+        <v>459.89</v>
       </c>
       <c r="J28" t="n">
-        <v>1343.45</v>
+        <v>601.92</v>
       </c>
       <c r="K28" t="n">
-        <v>1432.06</v>
+        <v>662.79</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3003,10 +3163,10 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>4.7</v>
+        <v>9.16</v>
       </c>
       <c r="P28" t="n">
-        <v>0.01</v>
+        <v>0.45</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -3015,12 +3175,12 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3037,37 +3197,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RAYMONDREL.NS</t>
+          <t>SIGNPOST.NS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RAYMONDREL</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>70.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>75.38</v>
+        <v>67.66</v>
       </c>
       <c r="F29" t="n">
-        <v>59.8</v>
+        <v>58.4</v>
       </c>
       <c r="G29" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="H29" t="n">
-        <v>699.75</v>
+        <v>317.6</v>
       </c>
       <c r="I29" t="n">
-        <v>612.0700000000001</v>
+        <v>269.96</v>
       </c>
       <c r="J29" t="n">
-        <v>778.42</v>
+        <v>359.6</v>
       </c>
       <c r="K29" t="n">
-        <v>857.09</v>
+        <v>401.61</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3083,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>36.3</v>
+        <v>27.6</v>
       </c>
       <c r="P29" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -3095,12 +3255,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.69, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3117,41 +3277,41 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RAYMOND.NS</t>
+          <t>RISHABH.NS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>RISHABH</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>76.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="E30" t="n">
-        <v>75.3</v>
+        <v>67.59</v>
       </c>
       <c r="F30" t="n">
-        <v>76.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="H30" t="n">
-        <v>620.55</v>
+        <v>662.1</v>
       </c>
       <c r="I30" t="n">
-        <v>575.36</v>
+        <v>562.78</v>
       </c>
       <c r="J30" t="n">
-        <v>669.2</v>
+        <v>738.5</v>
       </c>
       <c r="K30" t="n">
-        <v>717.86</v>
+        <v>814.89</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3163,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>0.34</v>
+        <v>0.11</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -3175,7 +3335,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3197,41 +3357,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RAMCOSYS.NS</t>
+          <t>KMEW.NS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RAMCOSYS</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>66.5</v>
       </c>
       <c r="E31" t="n">
-        <v>75.29000000000001</v>
+        <v>67.59</v>
       </c>
       <c r="F31" t="n">
-        <v>47.9</v>
+        <v>64.5</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="H31" t="n">
-        <v>837.35</v>
+        <v>2412.7</v>
       </c>
       <c r="I31" t="n">
-        <v>711.75</v>
+        <v>2084.13</v>
       </c>
       <c r="J31" t="n">
-        <v>982.5599999999999</v>
+        <v>2692.65</v>
       </c>
       <c r="K31" t="n">
-        <v>1127.76</v>
+        <v>2972.6</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3243,24 +3403,24 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.6, need 83), TQ_FAIL(got 64.5, need 73), RR_FAIL(got 1.63, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3277,41 +3437,41 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ITCHOTELS.NS</t>
+          <t>SUVEN.NS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ITCHOTELS</t>
+          <t>SUVEN</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>74.3</v>
+        <v>64.3</v>
       </c>
       <c r="E32" t="n">
-        <v>74.78</v>
+        <v>67.55</v>
       </c>
       <c r="F32" t="n">
-        <v>61.1</v>
+        <v>57.5</v>
       </c>
       <c r="G32" t="n">
-        <v>2.33</v>
+        <v>1.66</v>
       </c>
       <c r="H32" t="n">
-        <v>182.31</v>
+        <v>357.85</v>
       </c>
       <c r="I32" t="n">
-        <v>172.04</v>
+        <v>304.17</v>
       </c>
       <c r="J32" t="n">
-        <v>195.15</v>
+        <v>403.83</v>
       </c>
       <c r="K32" t="n">
-        <v>207.99</v>
+        <v>449.81</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3323,24 +3483,24 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>7.83</v>
+        <v>-78.8</v>
       </c>
       <c r="P32" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 57.5, need 73), RR_FAIL(got 1.66, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3357,41 +3517,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INDOBORAX.NS</t>
+          <t>WABAG.NS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INDOBORAX</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>70.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="E33" t="n">
-        <v>74.70999999999999</v>
+        <v>67.545</v>
       </c>
       <c r="F33" t="n">
-        <v>66.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="H33" t="n">
-        <v>433.65</v>
+        <v>2221.2</v>
       </c>
       <c r="I33" t="n">
-        <v>369.64</v>
+        <v>1975.08</v>
       </c>
       <c r="J33" t="n">
-        <v>482.71</v>
+        <v>2466.9</v>
       </c>
       <c r="K33" t="n">
-        <v>531.77</v>
+        <v>2712.6</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3403,24 +3563,24 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>11.9</v>
+        <v>15.9</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.92, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3437,37 +3597,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MMFL.NS</t>
+          <t>JAYBARMARU.NS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MMFL</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>68.59999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="E34" t="n">
-        <v>74.69</v>
+        <v>67.535</v>
       </c>
       <c r="F34" t="n">
-        <v>64.90000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="G34" t="n">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="H34" t="n">
-        <v>510.1</v>
+        <v>187.77</v>
       </c>
       <c r="I34" t="n">
-        <v>445.76</v>
+        <v>162.54</v>
       </c>
       <c r="J34" t="n">
-        <v>558.36</v>
+        <v>208.02</v>
       </c>
       <c r="K34" t="n">
-        <v>606.61</v>
+        <v>228.26</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3483,24 +3643,24 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>10.5</v>
+        <v>22.2</v>
       </c>
       <c r="P34" t="n">
-        <v>1.26</v>
+        <v>0.76</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 47.7, need 73), RR_FAIL(got 1.53, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3517,41 +3677,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SCODATUBES.NS</t>
+          <t>SHILPAMED.NS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SCODATUBES</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>80.09999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="E35" t="n">
-        <v>74.36</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>66.40000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="G35" t="n">
-        <v>3.24</v>
+        <v>1.52</v>
       </c>
       <c r="H35" t="n">
-        <v>147.7</v>
+        <v>627.15</v>
       </c>
       <c r="I35" t="n">
-        <v>141.59</v>
+        <v>554.17</v>
       </c>
       <c r="J35" t="n">
-        <v>159.46</v>
+        <v>684.84</v>
       </c>
       <c r="K35" t="n">
-        <v>171.22</v>
+        <v>742.54</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3563,24 +3723,24 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>14.37</v>
+        <v>9.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3597,37 +3757,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PSPPROJECT.NS</t>
+          <t>STYL.NS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PSPPROJECT</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>70.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>74.31</v>
+        <v>67.3</v>
       </c>
       <c r="F36" t="n">
-        <v>59</v>
+        <v>61.9</v>
       </c>
       <c r="G36" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
-        <v>1069.7</v>
+        <v>359.5</v>
       </c>
       <c r="I36" t="n">
-        <v>962.96</v>
+        <v>305.58</v>
       </c>
       <c r="J36" t="n">
-        <v>1173.14</v>
+        <v>398.68</v>
       </c>
       <c r="K36" t="n">
-        <v>1276.57</v>
+        <v>440.38</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3643,10 +3803,10 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4.55</v>
+        <v>23.3</v>
       </c>
       <c r="P36" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3655,12 +3815,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 61.9, need 73), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3677,37 +3837,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TIPSMUSIC.NS</t>
+          <t>STOVEKRAFT.NS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>72.5</v>
+        <v>72.8</v>
       </c>
       <c r="E37" t="n">
-        <v>74.19</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>76.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>1.41</v>
+        <v>2.27</v>
       </c>
       <c r="H37" t="n">
-        <v>711.15</v>
+        <v>798.95</v>
       </c>
       <c r="I37" t="n">
-        <v>633.17</v>
+        <v>746.35</v>
       </c>
       <c r="J37" t="n">
-        <v>766.85</v>
+        <v>863.7</v>
       </c>
       <c r="K37" t="n">
-        <v>828.12</v>
+        <v>928.4400000000001</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3723,24 +3883,24 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>92.33</v>
+        <v>67.5</v>
       </c>
       <c r="P37" t="n">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 70.1, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
@@ -3757,37 +3917,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>STYL.NS</t>
+          <t>CHOICEIN.NS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>66.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>74.03</v>
+        <v>67.19</v>
       </c>
       <c r="F38" t="n">
-        <v>57.1</v>
+        <v>68.2</v>
       </c>
       <c r="G38" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H38" t="n">
-        <v>360.7</v>
+        <v>835</v>
       </c>
       <c r="I38" t="n">
-        <v>306.91</v>
+        <v>751.4400000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>399.12</v>
+        <v>894.6900000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>441.38</v>
+        <v>960.34</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3803,24 +3963,24 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>23.3</v>
+        <v>16.1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.2, need 83), TQ_FAIL(got 68.2, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3837,41 +3997,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>68.2</v>
+        <v>67</v>
       </c>
       <c r="E39" t="n">
-        <v>73.89</v>
+        <v>67.08</v>
       </c>
       <c r="F39" t="n">
-        <v>63</v>
+        <v>71.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H39" t="n">
-        <v>1770.4</v>
+        <v>1341.8</v>
       </c>
       <c r="I39" t="n">
-        <v>1607.92</v>
+        <v>1209.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1890.7</v>
+        <v>1436.51</v>
       </c>
       <c r="K39" t="n">
-        <v>2014.12</v>
+        <v>1540.7</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3883,24 +4043,24 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="P39" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.1, need 83), TQ_FAIL(got 71.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=17&gt;top6)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3917,41 +4077,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TVSSCS.NS</t>
+          <t>DELHIVERY.NS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>72.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>73.76000000000001</v>
+        <v>67.02</v>
       </c>
       <c r="F40" t="n">
-        <v>73.8</v>
+        <v>74.2</v>
       </c>
       <c r="G40" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="H40" t="n">
-        <v>141.37</v>
+        <v>520.3</v>
       </c>
       <c r="I40" t="n">
-        <v>128.51</v>
+        <v>464.11</v>
       </c>
       <c r="J40" t="n">
-        <v>152.14</v>
+        <v>560.4299999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>162.92</v>
+        <v>604.58</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3963,24 +4123,24 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>9.699999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="P40" t="n">
-        <v>1.34</v>
+        <v>0.15</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(1.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3997,41 +4157,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DIXON.NS</t>
+          <t>PICCADIL.NS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>70.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>73.61</v>
+        <v>67</v>
       </c>
       <c r="F41" t="n">
-        <v>71.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H41" t="n">
-        <v>13477</v>
+        <v>671.8</v>
       </c>
       <c r="I41" t="n">
-        <v>12041.75</v>
+        <v>597.09</v>
       </c>
       <c r="J41" t="n">
-        <v>14502.18</v>
+        <v>725.17</v>
       </c>
       <c r="K41" t="n">
-        <v>15629.88</v>
+        <v>783.86</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4043,24 +4203,24 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>37.4</v>
+        <v>17.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 67.0, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4077,37 +4237,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>THELEELA.NS</t>
+          <t>POONAWALLA.NS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>THELEELA</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>71.5</v>
+        <v>65.2</v>
       </c>
       <c r="E42" t="n">
-        <v>73.42</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>59.4</v>
+        <v>66.7</v>
       </c>
       <c r="G42" t="n">
-        <v>2.09</v>
+        <v>1.43</v>
       </c>
       <c r="H42" t="n">
-        <v>500.6</v>
+        <v>477</v>
       </c>
       <c r="I42" t="n">
-        <v>466.01</v>
+        <v>426.48</v>
       </c>
       <c r="J42" t="n">
-        <v>539.76</v>
+        <v>513.09</v>
       </c>
       <c r="K42" t="n">
-        <v>578.9299999999999</v>
+        <v>552.78</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4123,24 +4283,24 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>8.199999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="P42" t="n">
-        <v>0.28</v>
+        <v>4.68</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(5.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4157,41 +4317,41 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RAMCOIND.NS</t>
+          <t>BORORENEW.NS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAMCOIND</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>68.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>73.23999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="F43" t="n">
-        <v>59.5</v>
+        <v>64</v>
       </c>
       <c r="G43" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="H43" t="n">
-        <v>369</v>
+        <v>640.55</v>
       </c>
       <c r="I43" t="n">
-        <v>324.87</v>
+        <v>584.5599999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>408.24</v>
+        <v>695.65</v>
       </c>
       <c r="K43" t="n">
-        <v>447.49</v>
+        <v>750.75</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4203,24 +4363,24 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>6.87</v>
+        <v>26.1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 66.8, need 83), TQ_FAIL(got 64.0, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4237,37 +4397,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>DATAMATICS.NS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>71.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>73.23</v>
+        <v>66.80500000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H44" t="n">
-        <v>31.68</v>
+        <v>900.45</v>
       </c>
       <c r="I44" t="n">
-        <v>27.61</v>
+        <v>784.85</v>
       </c>
       <c r="J44" t="n">
-        <v>34.59</v>
+        <v>983.02</v>
       </c>
       <c r="K44" t="n">
-        <v>37.78</v>
+        <v>1073.85</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4283,24 +4443,24 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>14.7</v>
+        <v>16.4</v>
       </c>
       <c r="P44" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 66.8, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -4317,41 +4477,41 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL.NS</t>
+          <t>MOSCHIP.NS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>MOSCHIP</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>67.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>73.16</v>
+        <v>66.64</v>
       </c>
       <c r="F45" t="n">
-        <v>61.8</v>
+        <v>64.7</v>
       </c>
       <c r="G45" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="H45" t="n">
-        <v>107.71</v>
+        <v>236.82</v>
       </c>
       <c r="I45" t="n">
-        <v>92.13</v>
+        <v>202.88</v>
       </c>
       <c r="J45" t="n">
-        <v>119.4</v>
+        <v>261.06</v>
       </c>
       <c r="K45" t="n">
-        <v>131.08</v>
+        <v>287.73</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4363,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4.79</v>
+        <v>11</v>
       </c>
       <c r="P45" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -4375,12 +4535,12 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 66.6, need 83), TQ_FAIL(got 64.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4397,41 +4557,41 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DIACABS.NS</t>
+          <t>MBAPL.NS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>68.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E46" t="n">
-        <v>72.47</v>
+        <v>66.63</v>
       </c>
       <c r="F46" t="n">
-        <v>68.8</v>
+        <v>58.1</v>
       </c>
       <c r="G46" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="H46" t="n">
-        <v>239.2</v>
+        <v>131.25</v>
       </c>
       <c r="I46" t="n">
-        <v>203.32</v>
+        <v>111.56</v>
       </c>
       <c r="J46" t="n">
-        <v>266.11</v>
+        <v>146.97</v>
       </c>
       <c r="K46" t="n">
-        <v>293.02</v>
+        <v>162.69</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4443,24 +4603,24 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(1.57&gt;1.50)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -4477,41 +4637,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHOICEIN.NS</t>
+          <t>KABRAEXTRU.NS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>69.3</v>
+        <v>61.9</v>
       </c>
       <c r="E47" t="n">
-        <v>72.33</v>
+        <v>66.31</v>
       </c>
       <c r="F47" t="n">
-        <v>68.7</v>
+        <v>55.3</v>
       </c>
       <c r="G47" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="H47" t="n">
-        <v>830.45</v>
+        <v>294.35</v>
       </c>
       <c r="I47" t="n">
-        <v>750.8200000000001</v>
+        <v>250.2</v>
       </c>
       <c r="J47" t="n">
-        <v>887.3200000000001</v>
+        <v>327.74</v>
       </c>
       <c r="K47" t="n">
-        <v>949.9</v>
+        <v>361.14</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4523,24 +4683,24 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>16.1</v>
+        <v>-1.14</v>
       </c>
       <c r="P47" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 66.3, need 83), TQ_FAIL(got 55.3, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -4557,41 +4717,41 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LENSKART.NS</t>
+          <t>MIRZAINT.NS</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>MIRZAINT</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>71.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>72.29000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="F48" t="n">
-        <v>71.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="H48" t="n">
-        <v>545.95</v>
+        <v>39.86</v>
       </c>
       <c r="I48" t="n">
-        <v>498.69</v>
+        <v>33.88</v>
       </c>
       <c r="J48" t="n">
-        <v>584.84</v>
+        <v>44.79</v>
       </c>
       <c r="K48" t="n">
-        <v>623.72</v>
+        <v>49.72</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4603,24 +4763,24 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>6.86</v>
+        <v>-3.58</v>
       </c>
       <c r="P48" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 66.0, need 83), TQ_FAIL(got 66.9, need 73), RR_FAIL(got 1.50, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4637,41 +4797,41 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>IKIO.NS</t>
+          <t>BALAMINES.NS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IKIO</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>67.8</v>
+        <v>62.8</v>
       </c>
       <c r="E49" t="n">
-        <v>72.23</v>
+        <v>66</v>
       </c>
       <c r="F49" t="n">
-        <v>58.7</v>
+        <v>58.2</v>
       </c>
       <c r="G49" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="H49" t="n">
-        <v>206.88</v>
+        <v>2414.9</v>
       </c>
       <c r="I49" t="n">
-        <v>175.85</v>
+        <v>2052.66</v>
       </c>
       <c r="J49" t="n">
-        <v>234.6</v>
+        <v>2690.47</v>
       </c>
       <c r="K49" t="n">
-        <v>262.32</v>
+        <v>2966.04</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4683,24 +4843,24 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>6.51</v>
+        <v>8.74</v>
       </c>
       <c r="P49" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4717,37 +4877,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UDS.NS</t>
+          <t>INDIQUBE.NS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>72.7</v>
+        <v>66</v>
       </c>
       <c r="E50" t="n">
-        <v>72.17</v>
+        <v>65.86</v>
       </c>
       <c r="F50" t="n">
-        <v>77.59999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="H50" t="n">
-        <v>197.05</v>
+        <v>178.11</v>
       </c>
       <c r="I50" t="n">
-        <v>177.92</v>
+        <v>162.67</v>
       </c>
       <c r="J50" t="n">
-        <v>213.42</v>
+        <v>191.04</v>
       </c>
       <c r="K50" t="n">
-        <v>229.78</v>
+        <v>203.98</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4763,24 +4923,24 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>8.880000000000001</v>
+        <v>-41.57</v>
       </c>
       <c r="P50" t="n">
-        <v>0.04</v>
+        <v>10.12</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(10.12&gt;1.50)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4797,37 +4957,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>THELEELA.NS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>THELEELA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>63.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>72.065</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>48.7</v>
+        <v>59.2</v>
       </c>
       <c r="G51" t="n">
-        <v>1.48</v>
+        <v>2.01</v>
       </c>
       <c r="H51" t="n">
-        <v>151.38</v>
+        <v>501</v>
       </c>
       <c r="I51" t="n">
-        <v>128.67</v>
+        <v>466.01</v>
       </c>
       <c r="J51" t="n">
-        <v>168.78</v>
+        <v>539.08</v>
       </c>
       <c r="K51" t="n">
-        <v>186.19</v>
+        <v>577.15</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4843,24 +5003,24 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="P51" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4886,32 +5046,32 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>68.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>71.87</v>
+        <v>65.74000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>68.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H52" t="n">
-        <v>842.15</v>
+        <v>847.5</v>
       </c>
       <c r="I52" t="n">
-        <v>730.1900000000001</v>
+        <v>721.84</v>
       </c>
       <c r="J52" t="n">
-        <v>922.12</v>
+        <v>937.26</v>
       </c>
       <c r="K52" t="n">
-        <v>1010.09</v>
+        <v>1035.99</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4930,17 +5090,17 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 65.7, need 83), TQ_FAIL(got 67.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -4957,41 +5117,41 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>69.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="E53" t="n">
-        <v>71.8</v>
+        <v>65.61</v>
       </c>
       <c r="F53" t="n">
-        <v>73.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="G53" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="H53" t="n">
-        <v>479.95</v>
+        <v>1225.8</v>
       </c>
       <c r="I53" t="n">
-        <v>438.8</v>
+        <v>1058.53</v>
       </c>
       <c r="J53" t="n">
-        <v>510.81</v>
+        <v>1345.28</v>
       </c>
       <c r="K53" t="n">
-        <v>541.67</v>
+        <v>1476.7</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5003,24 +5163,24 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>25.3</v>
+        <v>-33.74</v>
       </c>
       <c r="P53" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 65.6, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
@@ -5037,41 +5197,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MOREPENLAB.NS</t>
+          <t>BAJAJCON.NS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>BAJAJCON</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>65.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>71.55</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>56.1</v>
+        <v>69.8</v>
       </c>
       <c r="G54" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="H54" t="n">
-        <v>60.96</v>
+        <v>670.25</v>
       </c>
       <c r="I54" t="n">
-        <v>52.19</v>
+        <v>586.62</v>
       </c>
       <c r="J54" t="n">
-        <v>67.72</v>
+        <v>729.98</v>
       </c>
       <c r="K54" t="n">
-        <v>74.47</v>
+        <v>795.7</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5083,24 +5243,24 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>6.2</v>
+        <v>25.3</v>
       </c>
       <c r="P54" t="n">
-        <v>0.17</v>
+        <v>0.02</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 65.4, need 83), TQ_FAIL(got 69.8, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
@@ -5117,41 +5277,41 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AEGISVOPAK.NS</t>
+          <t>IFGLEXPOR.NS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>IFGLEXPOR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>66.8</v>
+        <v>66.2</v>
       </c>
       <c r="E55" t="n">
-        <v>71.42</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>61.5</v>
+        <v>63.2</v>
       </c>
       <c r="G55" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="H55" t="n">
-        <v>275.53</v>
+        <v>231</v>
       </c>
       <c r="I55" t="n">
-        <v>234.2</v>
+        <v>196.35</v>
       </c>
       <c r="J55" t="n">
-        <v>306.52</v>
+        <v>263</v>
       </c>
       <c r="K55" t="n">
-        <v>337.52</v>
+        <v>294.99</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5163,10 +5323,10 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>10</v>
+        <v>3.24</v>
       </c>
       <c r="P55" t="n">
-        <v>0.84</v>
+        <v>0.18</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -5175,12 +5335,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(3.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -5197,41 +5357,41 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CUPID.NS</t>
+          <t>THANGAMAYL.NS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>65.40000000000001</v>
+        <v>65</v>
       </c>
       <c r="E56" t="n">
-        <v>71.35000000000001</v>
+        <v>65.19000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>58</v>
+        <v>57.6</v>
       </c>
       <c r="G56" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="H56" t="n">
-        <v>210.01</v>
+        <v>6540.5</v>
       </c>
       <c r="I56" t="n">
-        <v>178.51</v>
+        <v>5591.9</v>
       </c>
       <c r="J56" t="n">
-        <v>234.14</v>
+        <v>7443.64</v>
       </c>
       <c r="K56" t="n">
-        <v>258.28</v>
+        <v>8346.77</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5243,24 +5403,24 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>27.3</v>
+        <v>27.93</v>
       </c>
       <c r="P56" t="n">
-        <v>0.13</v>
+        <v>0.64</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 65.2, need 83), TQ_FAIL(got 57.6, need 73), RR_FAIL(got 1.85, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
@@ -5277,37 +5437,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SUDARSCHEM.NS</t>
+          <t>EQUITASBNK.NS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>70.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>71.18000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="F57" t="n">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="G57" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H57" t="n">
-        <v>941.95</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>854.71</v>
+        <v>73.48</v>
       </c>
       <c r="J57" t="n">
-        <v>1009.25</v>
+        <v>88.81</v>
       </c>
       <c r="K57" t="n">
-        <v>1076.55</v>
+        <v>95.38</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5323,24 +5483,24 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0.49</v>
+        <v>1.69</v>
       </c>
       <c r="P57" t="n">
-        <v>0.64</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(1.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -5357,41 +5517,41 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PPLPHARMA.NS</t>
+          <t>ASKAUTOLTD.NS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>81.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="E58" t="n">
-        <v>71.13</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>75</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>3.91</v>
+        <v>1.78</v>
       </c>
       <c r="H58" t="n">
-        <v>171.99</v>
+        <v>471.85</v>
       </c>
       <c r="I58" t="n">
-        <v>164.36</v>
+        <v>438.8</v>
       </c>
       <c r="J58" t="n">
-        <v>188.12</v>
+        <v>503.86</v>
       </c>
       <c r="K58" t="n">
-        <v>204.26</v>
+        <v>535.88</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5403,24 +5563,24 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-3.83</v>
+        <v>25.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0.7</v>
+        <v>0.52</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 65.0, need 83), TQ_FAIL(got 65.9, need 73), RR_FAIL(got 1.78, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -5437,41 +5597,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IFGLEXPOR.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IFGLEXPOR</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>66.8</v>
+        <v>70.3</v>
       </c>
       <c r="E59" t="n">
-        <v>70.755</v>
+        <v>64.94</v>
       </c>
       <c r="F59" t="n">
-        <v>57</v>
+        <v>61.6</v>
       </c>
       <c r="G59" t="n">
-        <v>1.63</v>
+        <v>2.26</v>
       </c>
       <c r="H59" t="n">
-        <v>233.88</v>
+        <v>194.11</v>
       </c>
       <c r="I59" t="n">
-        <v>198.8</v>
+        <v>180.09</v>
       </c>
       <c r="J59" t="n">
-        <v>264.27</v>
+        <v>210.91</v>
       </c>
       <c r="K59" t="n">
-        <v>294.67</v>
+        <v>227.71</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5483,10 +5643,10 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>3.24</v>
+        <v>-42.3</v>
       </c>
       <c r="P59" t="n">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5495,12 +5655,12 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 64.9, need 83), TQ_FAIL(got 61.6, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -5517,41 +5677,41 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DATAMATICS.NS</t>
+          <t>FUSION.NS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>FUSION</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>69.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>70.685</v>
+        <v>64.84</v>
       </c>
       <c r="F60" t="n">
-        <v>75.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G60" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="H60" t="n">
-        <v>863.8</v>
+        <v>234.04</v>
       </c>
       <c r="I60" t="n">
-        <v>770.6799999999999</v>
+        <v>198.93</v>
       </c>
       <c r="J60" t="n">
-        <v>933.64</v>
+        <v>261.41</v>
       </c>
       <c r="K60" t="n">
-        <v>1003.48</v>
+        <v>288.78</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5563,24 +5723,24 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>16.4</v>
+        <v>0.68</v>
       </c>
       <c r="P60" t="n">
-        <v>0.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(0.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -5597,37 +5757,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SGMART.NS</t>
+          <t>TVSSCS.NS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SGMART</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>66.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>70.67</v>
+        <v>64.83</v>
       </c>
       <c r="F61" t="n">
-        <v>61.4</v>
+        <v>75.7</v>
       </c>
       <c r="G61" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="H61" t="n">
-        <v>659.8</v>
+        <v>141.66</v>
       </c>
       <c r="I61" t="n">
-        <v>574.73</v>
+        <v>128.51</v>
       </c>
       <c r="J61" t="n">
-        <v>720.5700000000001</v>
+        <v>152.46</v>
       </c>
       <c r="K61" t="n">
-        <v>787.4</v>
+        <v>163.27</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5643,24 +5803,24 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>7.92</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P61" t="n">
-        <v>0.17</v>
+        <v>1.34</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5677,37 +5837,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FEDDERSHOL.NS</t>
+          <t>AEGISVOPAK.NS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>76.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="E62" t="n">
-        <v>70.2</v>
+        <v>64.66</v>
       </c>
       <c r="F62" t="n">
-        <v>60</v>
+        <v>62.3</v>
       </c>
       <c r="G62" t="n">
-        <v>3.72</v>
+        <v>1.45</v>
       </c>
       <c r="H62" t="n">
-        <v>42.18</v>
+        <v>283.18</v>
       </c>
       <c r="I62" t="n">
-        <v>39.11</v>
+        <v>240.7</v>
       </c>
       <c r="J62" t="n">
-        <v>48.48</v>
+        <v>315.04</v>
       </c>
       <c r="K62" t="n">
-        <v>54.77</v>
+        <v>346.9</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5723,24 +5883,24 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="P62" t="n">
-        <v>0.09</v>
+        <v>0.84</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 64.7, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5757,41 +5917,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>APOLLOHOSP.NS</t>
+          <t>EMBDL.NS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>73.2</v>
+        <v>70</v>
       </c>
       <c r="E63" t="n">
-        <v>69.95</v>
+        <v>64.64</v>
       </c>
       <c r="F63" t="n">
-        <v>78.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G63" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H63" t="n">
-        <v>8845.5</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>8549.040000000001</v>
+        <v>60.16</v>
       </c>
       <c r="J63" t="n">
-        <v>9142.26</v>
+        <v>72.05</v>
       </c>
       <c r="K63" t="n">
-        <v>9439.02</v>
+        <v>77.86</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5803,24 +5963,24 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>22.1</v>
+        <v>-9.1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.85</v>
+        <v>0.53</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 64.6, need 83), RR_FAIL(got 1.79, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
@@ -5837,41 +5997,41 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BORORENEW.NS</t>
+          <t>INDOCO.NS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="D64" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>69.91</v>
+        <v>64.52</v>
       </c>
       <c r="F64" t="n">
-        <v>67.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="H64" t="n">
-        <v>651.65</v>
+        <v>260.23</v>
       </c>
       <c r="I64" t="n">
-        <v>584.5599999999999</v>
+        <v>230.94</v>
       </c>
       <c r="J64" t="n">
-        <v>703.62</v>
+        <v>285.74</v>
       </c>
       <c r="K64" t="n">
-        <v>755.6</v>
+        <v>311.25</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5883,24 +6043,24 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>26.1</v>
+        <v>-9.42</v>
       </c>
       <c r="P64" t="n">
-        <v>0.11</v>
+        <v>1.17</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 64.5, need 83), TQ_FAIL(got 72.1, need 73), RR_FAIL(got 1.54, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -5917,41 +6077,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AUROPHARMA.NS</t>
+          <t>UFBL.NS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>75.7</v>
+        <v>62.1</v>
       </c>
       <c r="E65" t="n">
-        <v>69.3</v>
+        <v>63.86</v>
       </c>
       <c r="F65" t="n">
-        <v>66.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="G65" t="n">
-        <v>2.71</v>
+        <v>1.44</v>
       </c>
       <c r="H65" t="n">
-        <v>1587.4</v>
+        <v>755.8</v>
       </c>
       <c r="I65" t="n">
-        <v>1528.32</v>
+        <v>642.4299999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>1676.02</v>
+        <v>840.83</v>
       </c>
       <c r="K65" t="n">
-        <v>1764.64</v>
+        <v>925.86</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5963,24 +6123,24 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>10.1</v>
+        <v>-17.6</v>
       </c>
       <c r="P65" t="n">
-        <v>0.21</v>
+        <v>2.76</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>DE_TOO_HIGH(2.76&gt;1.50)</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -5997,37 +6157,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SHREEJISPG.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>69.59999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="E66" t="n">
-        <v>68.72</v>
+        <v>62.96000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>75.90000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="G66" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="H66" t="n">
-        <v>523.4</v>
+        <v>147.43</v>
       </c>
       <c r="I66" t="n">
-        <v>476.01</v>
+        <v>125.32</v>
       </c>
       <c r="J66" t="n">
-        <v>558.4</v>
+        <v>164.68</v>
       </c>
       <c r="K66" t="n">
-        <v>594.48</v>
+        <v>181.94</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6043,24 +6203,24 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>27.5</v>
+        <v>-0.48</v>
       </c>
       <c r="P66" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 63.0, need 83), TQ_FAIL(got 55.7, need 73), RR_FAIL(got 1.51, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -6077,37 +6237,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>TCIEXP.NS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>65.5</v>
+        <v>68.3</v>
       </c>
       <c r="E67" t="n">
-        <v>68.59999999999999</v>
+        <v>62.91</v>
       </c>
       <c r="F67" t="n">
-        <v>65.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>1.43</v>
+        <v>2.07</v>
       </c>
       <c r="H67" t="n">
-        <v>1934.6</v>
+        <v>559.75</v>
       </c>
       <c r="I67" t="n">
-        <v>1731.95</v>
+        <v>493.02</v>
       </c>
       <c r="J67" t="n">
-        <v>2079.35</v>
+        <v>632.13</v>
       </c>
       <c r="K67" t="n">
-        <v>2238.57</v>
+        <v>704.51</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6123,24 +6283,24 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>27.4</v>
+        <v>10.5</v>
       </c>
       <c r="P67" t="n">
-        <v>2.82</v>
+        <v>0.08</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 62.9, need 83), TQ_FAIL(got 66.9, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -6157,41 +6317,41 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AZAD.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>68.09999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="E68" t="n">
-        <v>67.53</v>
+        <v>62.23999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>70.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H68" t="n">
-        <v>2476.1</v>
+        <v>1977.6</v>
       </c>
       <c r="I68" t="n">
-        <v>2164.43</v>
+        <v>1769.75</v>
       </c>
       <c r="J68" t="n">
-        <v>2698.72</v>
+        <v>2126.06</v>
       </c>
       <c r="K68" t="n">
-        <v>2943.6</v>
+        <v>2289.38</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6203,24 +6363,24 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>9.09</v>
+        <v>27.4</v>
       </c>
       <c r="P68" t="n">
-        <v>0.31</v>
+        <v>2.82</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(2.82&gt;1.50)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -6237,41 +6397,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LTF.NS</t>
+          <t>ITDC.NS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>ITDC</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>69.3</v>
+        <v>62.6</v>
       </c>
       <c r="E69" t="n">
-        <v>67.52500000000001</v>
+        <v>62.08</v>
       </c>
       <c r="F69" t="n">
-        <v>72.2</v>
+        <v>63.4</v>
       </c>
       <c r="G69" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="H69" t="n">
-        <v>321.1</v>
+        <v>716.8</v>
       </c>
       <c r="I69" t="n">
-        <v>296.01</v>
+        <v>609.28</v>
       </c>
       <c r="J69" t="n">
-        <v>343.16</v>
+        <v>797.4400000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>365.22</v>
+        <v>878.08</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6283,10 +6443,10 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>11.2</v>
+        <v>21.1</v>
       </c>
       <c r="P69" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -6295,12 +6455,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 62.1, need 83), TQ_FAIL(got 63.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -6317,41 +6477,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FERMENTA.NS</t>
+          <t>BFINVEST.NS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FERMENTA</t>
+          <t>BFINVEST</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>64.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>67.45999999999999</v>
+        <v>61.55</v>
       </c>
       <c r="F70" t="n">
-        <v>58.5</v>
+        <v>75.7</v>
       </c>
       <c r="G70" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="H70" t="n">
-        <v>401.65</v>
+        <v>487.25</v>
       </c>
       <c r="I70" t="n">
-        <v>341.4</v>
+        <v>433.21</v>
       </c>
       <c r="J70" t="n">
-        <v>455.27</v>
+        <v>525.85</v>
       </c>
       <c r="K70" t="n">
-        <v>508.89</v>
+        <v>568.3099999999999</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6363,24 +6523,24 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>17.4</v>
+        <v>3.65</v>
       </c>
       <c r="P70" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(3.6%&lt;10%)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -6397,41 +6557,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IBULLSLTD.NS</t>
+          <t>MUTHOOTMF.NS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>61.5</v>
+        <v>63.5</v>
       </c>
       <c r="E71" t="n">
-        <v>67.31999999999999</v>
+        <v>61.48999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>47.2</v>
+        <v>67.2</v>
       </c>
       <c r="G71" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="H71" t="n">
-        <v>29.57</v>
+        <v>235.26</v>
       </c>
       <c r="I71" t="n">
-        <v>25.61</v>
+        <v>203.97</v>
       </c>
       <c r="J71" t="n">
-        <v>32.88</v>
+        <v>259.46</v>
       </c>
       <c r="K71" t="n">
-        <v>36.19</v>
+        <v>283.66</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6443,24 +6603,24 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>23.1</v>
+        <v>6.21</v>
       </c>
       <c r="P71" t="n">
-        <v>0.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(6.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
@@ -6477,41 +6637,41 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KAMDHENU.NS</t>
+          <t>GEMAROMA.NS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>61.1</v>
+        <v>62.4</v>
       </c>
       <c r="E72" t="n">
-        <v>65</v>
+        <v>59.76000000000001</v>
       </c>
       <c r="F72" t="n">
-        <v>56.9</v>
+        <v>60.7</v>
       </c>
       <c r="G72" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="H72" t="n">
-        <v>32.56</v>
+        <v>206.54</v>
       </c>
       <c r="I72" t="n">
-        <v>27.72</v>
+        <v>179.09</v>
       </c>
       <c r="J72" t="n">
-        <v>36.12</v>
+        <v>230.93</v>
       </c>
       <c r="K72" t="n">
-        <v>39.82</v>
+        <v>255.32</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6523,10 +6683,10 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>14.7</v>
+        <v>0.39</v>
       </c>
       <c r="P72" t="n">
-        <v>0.02</v>
+        <v>0.34</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6535,12 +6695,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(0.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -6557,41 +6717,41 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SUNPHARMA.NS</t>
+          <t>RAMRAT.NS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>66.2</v>
+        <v>65.8</v>
       </c>
       <c r="E73" t="n">
-        <v>64.94499999999999</v>
+        <v>57.62</v>
       </c>
       <c r="F73" t="n">
-        <v>74.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="H73" t="n">
-        <v>1938.7</v>
+        <v>419.05</v>
       </c>
       <c r="I73" t="n">
-        <v>1841.79</v>
+        <v>388.65</v>
       </c>
       <c r="J73" t="n">
-        <v>2011.38</v>
+        <v>450.39</v>
       </c>
       <c r="K73" t="n">
-        <v>2084.06</v>
+        <v>481.73</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6603,24 +6763,24 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>16</v>
+        <v>20.6</v>
       </c>
       <c r="P73" t="n">
-        <v>0.06</v>
+        <v>1.15</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 57.6, need 83), TQ_FAIL(got 72.6, need 73), RR_FAIL(got 1.83, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -6637,41 +6797,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>64.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="E74" t="n">
-        <v>62.48999999999999</v>
+        <v>57.375</v>
       </c>
       <c r="F74" t="n">
-        <v>67.5</v>
+        <v>58.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>563.55</v>
+        <v>1451.9</v>
       </c>
       <c r="I74" t="n">
-        <v>479.02</v>
+        <v>1325.54</v>
       </c>
       <c r="J74" t="n">
-        <v>626.9400000000001</v>
+        <v>1584.66</v>
       </c>
       <c r="K74" t="n">
-        <v>690.34</v>
+        <v>1717.43</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6683,24 +6843,24 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>9.16</v>
+        <v>13.9</v>
       </c>
       <c r="P74" t="n">
-        <v>0.45</v>
+        <v>0.13</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 57.4, need 83), TQ_FAIL(got 58.5, need 73), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -6717,41 +6877,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BHAGCHEM.NS</t>
+          <t>DLF.NS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BHAGCHEM</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>69.2</v>
+        <v>62.4</v>
       </c>
       <c r="E75" t="n">
-        <v>61.95</v>
+        <v>57.14</v>
       </c>
       <c r="F75" t="n">
-        <v>73</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="H75" t="n">
-        <v>301.25</v>
+        <v>685.75</v>
       </c>
       <c r="I75" t="n">
-        <v>277.8</v>
+        <v>611.9400000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>326.52</v>
+        <v>738.47</v>
       </c>
       <c r="K75" t="n">
-        <v>351.78</v>
+        <v>796.46</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6763,19 +6923,19 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2.63</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P75" t="n">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -6797,41 +6957,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BHARATSE.NS</t>
+          <t>SUPRAJIT.NS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BHARATSE</t>
+          <t>SUPRAJIT</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="E76" t="n">
-        <v>61.65000000000001</v>
+        <v>56.28</v>
       </c>
       <c r="F76" t="n">
-        <v>59.8</v>
+        <v>75.7</v>
       </c>
       <c r="G76" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="H76" t="n">
-        <v>245.09</v>
+        <v>509</v>
       </c>
       <c r="I76" t="n">
-        <v>208.33</v>
+        <v>462.72</v>
       </c>
       <c r="J76" t="n">
-        <v>277.18</v>
+        <v>542.05</v>
       </c>
       <c r="K76" t="n">
-        <v>309.27</v>
+        <v>578.42</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6843,24 +7003,24 @@
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>19.91</v>
+        <v>13.8</v>
       </c>
       <c r="P76" t="n">
-        <v>0.48</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 56.3, need 83), RR_FAIL(got 1.35, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
@@ -6877,37 +7037,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SPANDANA.NS</t>
+          <t>CYIENTDLM.NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SPANDANA</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>62.7</v>
+        <v>59.1</v>
       </c>
       <c r="E77" t="n">
-        <v>61.31</v>
+        <v>55.31</v>
       </c>
       <c r="F77" t="n">
-        <v>66.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="G77" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H77" t="n">
-        <v>303.45</v>
+        <v>545.65</v>
       </c>
       <c r="I77" t="n">
-        <v>259.94</v>
+        <v>463.8</v>
       </c>
       <c r="J77" t="n">
-        <v>336.08</v>
+        <v>607.04</v>
       </c>
       <c r="K77" t="n">
-        <v>368.72</v>
+        <v>668.42</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -6923,24 +7083,24 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>-29.4</v>
+        <v>7.49</v>
       </c>
       <c r="P77" t="n">
-        <v>1.85</v>
+        <v>0.17</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(7.5%&lt;10%)</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -6957,37 +7117,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SUPRAJIT.NS</t>
+          <t>DIACABS.NS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SUPRAJIT</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>64</v>
+        <v>58.3</v>
       </c>
       <c r="E78" t="n">
-        <v>59.95999999999999</v>
+        <v>55.035</v>
       </c>
       <c r="F78" t="n">
-        <v>74</v>
+        <v>59.3</v>
       </c>
       <c r="G78" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="H78" t="n">
-        <v>495.65</v>
+        <v>229.01</v>
       </c>
       <c r="I78" t="n">
-        <v>455.11</v>
+        <v>196.51</v>
       </c>
       <c r="J78" t="n">
-        <v>527.66</v>
+        <v>255.34</v>
       </c>
       <c r="K78" t="n">
-        <v>559.6799999999999</v>
+        <v>281.67</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -7003,10 +7163,10 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
@@ -7015,12 +7175,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 55.0, need 83), TQ_FAIL(got 59.3, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -7037,41 +7197,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ATHERENERG.NS</t>
+          <t>SHAREINDIA.NS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>60.8</v>
+        <v>56.1</v>
       </c>
       <c r="E79" t="n">
-        <v>59.73999999999999</v>
+        <v>54.62</v>
       </c>
       <c r="F79" t="n">
-        <v>61.6</v>
+        <v>53.7</v>
       </c>
       <c r="G79" t="n">
         <v>1.45</v>
       </c>
       <c r="H79" t="n">
-        <v>1218.4</v>
+        <v>179.34</v>
       </c>
       <c r="I79" t="n">
-        <v>1051.69</v>
+        <v>152.44</v>
       </c>
       <c r="J79" t="n">
-        <v>1337.48</v>
+        <v>198.95</v>
       </c>
       <c r="K79" t="n">
-        <v>1468.46</v>
+        <v>219.69</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7083,24 +7243,24 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>-33.74</v>
+        <v>13</v>
       </c>
       <c r="P79" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 54.6, need 83), TQ_FAIL(got 53.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -7117,41 +7277,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EPL.NS</t>
+          <t>SOTL.NS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>63.5</v>
+        <v>61.3</v>
       </c>
       <c r="E80" t="n">
-        <v>59.64</v>
+        <v>54.36</v>
       </c>
       <c r="F80" t="n">
-        <v>66</v>
+        <v>67.2</v>
       </c>
       <c r="G80" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H80" t="n">
-        <v>239.49</v>
+        <v>607.45</v>
       </c>
       <c r="I80" t="n">
-        <v>222.03</v>
+        <v>516.33</v>
       </c>
       <c r="J80" t="n">
-        <v>254.98</v>
+        <v>685.8</v>
       </c>
       <c r="K80" t="n">
-        <v>270.46</v>
+        <v>764.15</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7163,24 +7323,24 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="P80" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 54.4, need 83), TQ_FAIL(got 67.2, need 73), RR_FAIL(got 1.65, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
@@ -7197,41 +7357,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ARKADE.NS</t>
+          <t>OMAXE.NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ARKADE</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>63.3</v>
+        <v>62.6</v>
       </c>
       <c r="E81" t="n">
-        <v>57.23</v>
+        <v>51.49</v>
       </c>
       <c r="F81" t="n">
-        <v>67.2</v>
+        <v>69.5</v>
       </c>
       <c r="G81" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="H81" t="n">
-        <v>131.94</v>
+        <v>90.48</v>
       </c>
       <c r="I81" t="n">
-        <v>121.42</v>
+        <v>76.91</v>
       </c>
       <c r="J81" t="n">
-        <v>142.64</v>
+        <v>103.86</v>
       </c>
       <c r="K81" t="n">
-        <v>153.33</v>
+        <v>117.24</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7243,24 +7403,24 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 51.5, need 83), TQ_FAIL(got 69.5, need 73), RR_FAIL(got 1.90, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
@@ -7286,28 +7446,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>62.3</v>
+        <v>57</v>
       </c>
       <c r="E82" t="n">
-        <v>56.57</v>
+        <v>51.215</v>
       </c>
       <c r="F82" t="n">
-        <v>74.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G82" t="n">
         <v>1.43</v>
       </c>
       <c r="H82" t="n">
-        <v>882.05</v>
+        <v>889.85</v>
       </c>
       <c r="I82" t="n">
-        <v>794.27</v>
+        <v>801.74</v>
       </c>
       <c r="J82" t="n">
-        <v>944.75</v>
+        <v>952.79</v>
       </c>
       <c r="K82" t="n">
-        <v>1013.72</v>
+        <v>1022.02</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -7326,21 +7486,21 @@
         <v>13.7</v>
       </c>
       <c r="P82" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 51.2, need 83), TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
@@ -7357,41 +7517,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BALAMINES.NS</t>
+          <t>KAMDHENU.NS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>62.1</v>
+        <v>57</v>
       </c>
       <c r="E83" t="n">
-        <v>56.155</v>
+        <v>48.82</v>
       </c>
       <c r="F83" t="n">
-        <v>72.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="H83" t="n">
-        <v>2364</v>
+        <v>33.02</v>
       </c>
       <c r="I83" t="n">
-        <v>2009.4</v>
+        <v>28.07</v>
       </c>
       <c r="J83" t="n">
-        <v>2629.95</v>
+        <v>36.74</v>
       </c>
       <c r="K83" t="n">
-        <v>2895.9</v>
+        <v>40.45</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7403,24 +7563,24 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>8.74</v>
+        <v>14.7</v>
       </c>
       <c r="P83" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 48.8, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.36, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -7437,41 +7597,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CAPLIPOINT.NS</t>
+          <t>PRESTIGE.NS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CAPLIPOINT</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>66.7</v>
+        <v>54.6</v>
       </c>
       <c r="E84" t="n">
-        <v>56.05</v>
+        <v>47.99</v>
       </c>
       <c r="F84" t="n">
-        <v>62.3</v>
+        <v>63</v>
       </c>
       <c r="G84" t="n">
-        <v>2.58</v>
+        <v>1.43</v>
       </c>
       <c r="H84" t="n">
-        <v>2621.4</v>
+        <v>1733.2</v>
       </c>
       <c r="I84" t="n">
-        <v>2472.77</v>
+        <v>1547</v>
       </c>
       <c r="J84" t="n">
-        <v>2831.95</v>
+        <v>1866.2</v>
       </c>
       <c r="K84" t="n">
-        <v>3042.5</v>
+        <v>2012.5</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7483,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>20.6</v>
+        <v>7.54</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -7495,12 +7655,12 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 48.0, need 83), TQ_FAIL(got 63.0, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
@@ -7517,41 +7677,41 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>DLF.NS</t>
+          <t>MOREPENLAB.NS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>59</v>
+        <v>53.8</v>
       </c>
       <c r="E85" t="n">
-        <v>55.86</v>
+        <v>47.84</v>
       </c>
       <c r="F85" t="n">
-        <v>63.3</v>
+        <v>57.1</v>
       </c>
       <c r="G85" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H85" t="n">
-        <v>659.6</v>
+        <v>61.22</v>
       </c>
       <c r="I85" t="n">
-        <v>605.61</v>
+        <v>52.19</v>
       </c>
       <c r="J85" t="n">
-        <v>702.2</v>
+        <v>68.06</v>
       </c>
       <c r="K85" t="n">
-        <v>744.8099999999999</v>
+        <v>74.91</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7563,10 +7723,10 @@
         <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>9.619999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="P85" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
@@ -7575,12 +7735,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 47.8, need 83), TQ_FAIL(got 57.1, need 73), RR_FAIL(got 1.47, need 2.0)</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -7597,41 +7757,41 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LUPIN.NS</t>
+          <t>ARTEMISMED.NS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>60.3</v>
+        <v>59.9</v>
       </c>
       <c r="E86" t="n">
-        <v>55.73</v>
+        <v>47.79</v>
       </c>
       <c r="F86" t="n">
-        <v>70</v>
+        <v>72.3</v>
       </c>
       <c r="G86" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="H86" t="n">
-        <v>2503.3</v>
+        <v>277</v>
       </c>
       <c r="I86" t="n">
-        <v>2331.78</v>
+        <v>256.28</v>
       </c>
       <c r="J86" t="n">
-        <v>2627.76</v>
+        <v>298.26</v>
       </c>
       <c r="K86" t="n">
-        <v>2760.58</v>
+        <v>319.51</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7643,24 +7803,24 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>29.1</v>
+        <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 47.8, need 83), TQ_FAIL(got 72.3, need 73), RR_FAIL(got 1.73, need 2.0)</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
@@ -7677,41 +7837,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PPAP.NS</t>
+          <t>STARHEALTH.NS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PPAP</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>59.7</v>
+        <v>56.7</v>
       </c>
       <c r="E87" t="n">
-        <v>55.14</v>
+        <v>47.38</v>
       </c>
       <c r="F87" t="n">
-        <v>66.2</v>
+        <v>59.4</v>
       </c>
       <c r="G87" t="n">
-        <v>1.39</v>
+        <v>1.91</v>
       </c>
       <c r="H87" t="n">
-        <v>276.63</v>
+        <v>603.25</v>
       </c>
       <c r="I87" t="n">
-        <v>235.14</v>
+        <v>569.4400000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>308.4</v>
+        <v>638.0599999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>340.16</v>
+        <v>672.87</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7723,24 +7883,24 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 47.4, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.91, need 2.0)</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -7757,37 +7917,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OMAXE.NS</t>
+          <t>ARKADE.NS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>ARKADE</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>64.5</v>
+        <v>60.4</v>
       </c>
       <c r="E88" t="n">
-        <v>54.35</v>
+        <v>47.37</v>
       </c>
       <c r="F88" t="n">
-        <v>63.1</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>2.31</v>
+        <v>1.67</v>
       </c>
       <c r="H88" t="n">
-        <v>86.90000000000001</v>
+        <v>132.56</v>
       </c>
       <c r="I88" t="n">
-        <v>76.61</v>
+        <v>121.42</v>
       </c>
       <c r="J88" t="n">
-        <v>99.36</v>
+        <v>142.89</v>
       </c>
       <c r="K88" t="n">
-        <v>111.82</v>
+        <v>153.22</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -7803,24 +7963,24 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 47.4, need 83), RR_FAIL(got 1.67, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
@@ -7846,28 +8006,28 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>55.4</v>
+        <v>52.8</v>
       </c>
       <c r="E89" t="n">
-        <v>53.785</v>
+        <v>47.37</v>
       </c>
       <c r="F89" t="n">
-        <v>54.5</v>
+        <v>55.1</v>
       </c>
       <c r="G89" t="n">
         <v>1.44</v>
       </c>
       <c r="H89" t="n">
-        <v>235.58</v>
+        <v>246.44</v>
       </c>
       <c r="I89" t="n">
-        <v>200.24</v>
+        <v>209.47</v>
       </c>
       <c r="J89" t="n">
-        <v>261.8</v>
+        <v>274.13</v>
       </c>
       <c r="K89" t="n">
-        <v>288.59</v>
+        <v>301.9</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -7886,21 +8046,21 @@
         <v>3.87</v>
       </c>
       <c r="P89" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 47.4, need 83), TQ_FAIL(got 55.1, need 73), RR_FAIL(got 1.44, need 2.0)</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -7917,41 +8077,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ORCHPHARMA.NS</t>
+          <t>SOBHA.NS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>SOBHA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>59.4</v>
+        <v>57.4</v>
       </c>
       <c r="E90" t="n">
-        <v>53.095</v>
+        <v>46.58</v>
       </c>
       <c r="F90" t="n">
-        <v>65.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="H90" t="n">
-        <v>1050.95</v>
+        <v>1511.3</v>
       </c>
       <c r="I90" t="n">
-        <v>912.17</v>
+        <v>1360.66</v>
       </c>
       <c r="J90" t="n">
-        <v>1168.38</v>
+        <v>1621.47</v>
       </c>
       <c r="K90" t="n">
-        <v>1285.8</v>
+        <v>1737.26</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -7963,7 +8123,7 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>2.12</v>
+        <v>4.16</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
@@ -7975,12 +8135,12 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 46.6, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -7997,41 +8157,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ANANTRAJ.NS</t>
+          <t>UNICHEMLAB.NS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>61</v>
+        <v>50.8</v>
       </c>
       <c r="E91" t="n">
-        <v>52.06</v>
+        <v>46.19</v>
       </c>
       <c r="F91" t="n">
-        <v>74.8</v>
+        <v>48.3</v>
       </c>
       <c r="G91" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="H91" t="n">
-        <v>569.45</v>
+        <v>638.75</v>
       </c>
       <c r="I91" t="n">
-        <v>508.69</v>
+        <v>542.9400000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>614.71</v>
+        <v>715.24</v>
       </c>
       <c r="K91" t="n">
-        <v>660.59</v>
+        <v>791.72</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8043,24 +8203,24 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>11.2</v>
+        <v>3.17</v>
       </c>
       <c r="P91" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 46.2, need 83), TQ_FAIL(got 48.3, need 73), RR_FAIL(got 1.53, need 2.0), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -8077,37 +8237,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MOSCHIP.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MOSCHIP</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>60.5</v>
+        <v>55.5</v>
       </c>
       <c r="E92" t="n">
-        <v>51.56</v>
+        <v>45.875</v>
       </c>
       <c r="F92" t="n">
-        <v>75.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="G92" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H92" t="n">
-        <v>238.62</v>
+        <v>62.25</v>
       </c>
       <c r="I92" t="n">
-        <v>205.36</v>
+        <v>53.18</v>
       </c>
       <c r="J92" t="n">
-        <v>262.38</v>
+        <v>68.73</v>
       </c>
       <c r="K92" t="n">
-        <v>288.51</v>
+        <v>75.86</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -8123,24 +8283,24 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>11</v>
+        <v>12.9</v>
       </c>
       <c r="P92" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 45.9, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -8157,37 +8317,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STOVEKRAFT.NS</t>
+          <t>JUBLINGREA.NS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>67.59999999999999</v>
+        <v>57.4</v>
       </c>
       <c r="E93" t="n">
-        <v>51.48</v>
+        <v>45.8</v>
       </c>
       <c r="F93" t="n">
-        <v>74.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="G93" t="n">
-        <v>2.48</v>
+        <v>1.42</v>
       </c>
       <c r="H93" t="n">
-        <v>797.4</v>
+        <v>722.3</v>
       </c>
       <c r="I93" t="n">
-        <v>746.35</v>
+        <v>641.65</v>
       </c>
       <c r="J93" t="n">
-        <v>866.1799999999999</v>
+        <v>779.91</v>
       </c>
       <c r="K93" t="n">
-        <v>934.97</v>
+        <v>843.27</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -8203,10 +8363,10 @@
         <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>67.5</v>
+        <v>9.51</v>
       </c>
       <c r="P93" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
@@ -8215,12 +8375,12 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 45.8, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
@@ -8237,41 +8397,41 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>59</v>
+        <v>51.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.465</v>
+        <v>45.29</v>
       </c>
       <c r="F94" t="n">
-        <v>70.59999999999999</v>
+        <v>50.3</v>
       </c>
       <c r="G94" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="H94" t="n">
-        <v>61.06</v>
+        <v>228.34</v>
       </c>
       <c r="I94" t="n">
-        <v>52.37</v>
+        <v>194.09</v>
       </c>
       <c r="J94" t="n">
-        <v>67.27</v>
+        <v>257.01</v>
       </c>
       <c r="K94" t="n">
-        <v>74.09999999999999</v>
+        <v>285.68</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8283,24 +8443,24 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>12.9</v>
+        <v>27.1</v>
       </c>
       <c r="P94" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 45.3, need 83), TQ_FAIL(got 50.3, need 73), RR_FAIL(got 1.61, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -8317,41 +8477,41 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>FUSION.NS</t>
+          <t>IKIO.NS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FUSION</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>57.7</v>
+        <v>53.3</v>
       </c>
       <c r="E95" t="n">
-        <v>51.41</v>
+        <v>45.21</v>
       </c>
       <c r="F95" t="n">
-        <v>66.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="G95" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="H95" t="n">
-        <v>229.32</v>
+        <v>210.75</v>
       </c>
       <c r="I95" t="n">
-        <v>194.92</v>
+        <v>179.14</v>
       </c>
       <c r="J95" t="n">
-        <v>255.66</v>
+        <v>242.42</v>
       </c>
       <c r="K95" t="n">
-        <v>282.01</v>
+        <v>274.08</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8363,24 +8523,24 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>0.68</v>
+        <v>6.51</v>
       </c>
       <c r="P95" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 45.2, need 83), TQ_FAIL(got 50.7, need 73), RR_FAIL(got 1.95, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -8397,41 +8557,41 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>NORTHARC.NS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>62.7</v>
+        <v>57.5</v>
       </c>
       <c r="E96" t="n">
-        <v>51.18</v>
+        <v>45.18</v>
       </c>
       <c r="F96" t="n">
-        <v>69</v>
+        <v>75.5</v>
       </c>
       <c r="G96" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="H96" t="n">
-        <v>1441</v>
+        <v>325.3</v>
       </c>
       <c r="I96" t="n">
-        <v>1325.54</v>
+        <v>288.45</v>
       </c>
       <c r="J96" t="n">
-        <v>1571.29</v>
+        <v>353.88</v>
       </c>
       <c r="K96" t="n">
-        <v>1701.58</v>
+        <v>382.47</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8443,24 +8603,24 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="P96" t="n">
-        <v>0.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>DE_TOO_HIGH(3.14&gt;1.50)</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -8477,41 +8637,41 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>VAIBHAVGBL.NS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>63.4</v>
+        <v>57.7</v>
       </c>
       <c r="E97" t="n">
-        <v>50.7</v>
+        <v>45.1</v>
       </c>
       <c r="F97" t="n">
-        <v>73.7</v>
+        <v>75.3</v>
       </c>
       <c r="G97" t="n">
-        <v>1.94</v>
+        <v>1.43</v>
       </c>
       <c r="H97" t="n">
-        <v>233.59</v>
+        <v>261.36</v>
       </c>
       <c r="I97" t="n">
-        <v>211.55</v>
+        <v>227.8</v>
       </c>
       <c r="J97" t="n">
-        <v>256.36</v>
+        <v>285.33</v>
       </c>
       <c r="K97" t="n">
-        <v>279.14</v>
+        <v>311.7</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8523,24 +8683,24 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>2.95</v>
+        <v>17.8</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 45.1, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -8557,37 +8717,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>ANANDRATHI.NS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>54.8</v>
+        <v>55.9</v>
       </c>
       <c r="E98" t="n">
-        <v>49.2</v>
+        <v>43.775</v>
       </c>
       <c r="F98" t="n">
-        <v>57.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G98" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="H98" t="n">
-        <v>231.55</v>
+        <v>2146.8</v>
       </c>
       <c r="I98" t="n">
-        <v>196.82</v>
+        <v>1906.75</v>
       </c>
       <c r="J98" t="n">
-        <v>258.52</v>
+        <v>2318.26</v>
       </c>
       <c r="K98" t="n">
-        <v>285.5</v>
+        <v>2506.88</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -8603,24 +8763,24 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>27.1</v>
+        <v>47.3</v>
       </c>
       <c r="P98" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 43.8, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -8637,41 +8797,41 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ALKYLAMINE.NS</t>
+          <t>UTLSOLAR.NS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>60.1</v>
+        <v>55.8</v>
       </c>
       <c r="E99" t="n">
-        <v>49.11</v>
+        <v>43.17</v>
       </c>
       <c r="F99" t="n">
-        <v>76.7</v>
+        <v>72.8</v>
       </c>
       <c r="G99" t="n">
         <v>1.43</v>
       </c>
       <c r="H99" t="n">
-        <v>1954.6</v>
+        <v>382.7</v>
       </c>
       <c r="I99" t="n">
-        <v>1700.66</v>
+        <v>329.06</v>
       </c>
       <c r="J99" t="n">
-        <v>2135.99</v>
+        <v>421.01</v>
       </c>
       <c r="K99" t="n">
-        <v>2335.51</v>
+        <v>463.16</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8683,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>41.4</v>
+        <v>58</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -8695,12 +8855,12 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 43.2, need 83), TQ_FAIL(got 72.8, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -8717,41 +8877,41 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JUBLINGREA.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>59.1</v>
+        <v>54.3</v>
       </c>
       <c r="E100" t="n">
-        <v>48.82</v>
+        <v>43.06</v>
       </c>
       <c r="F100" t="n">
-        <v>74.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G100" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H100" t="n">
-        <v>715.5</v>
+        <v>244.75</v>
       </c>
       <c r="I100" t="n">
-        <v>635.71</v>
+        <v>211.55</v>
       </c>
       <c r="J100" t="n">
-        <v>772.49</v>
+        <v>269.44</v>
       </c>
       <c r="K100" t="n">
-        <v>835.1799999999999</v>
+        <v>294.55</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8763,24 +8923,24 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>9.51</v>
+        <v>2.95</v>
       </c>
       <c r="P100" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 43.1, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -8797,37 +8957,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SHAREINDIA.NS</t>
+          <t>STALLION.NS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>51.9</v>
+        <v>54.2</v>
       </c>
       <c r="E101" t="n">
-        <v>44.56</v>
+        <v>41.03</v>
       </c>
       <c r="F101" t="n">
-        <v>56.4</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G101" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="H101" t="n">
-        <v>179.03</v>
+        <v>204.88</v>
       </c>
       <c r="I101" t="n">
-        <v>153.06</v>
+        <v>176.77</v>
       </c>
       <c r="J101" t="n">
-        <v>197.58</v>
+        <v>227.52</v>
       </c>
       <c r="K101" t="n">
-        <v>217.98</v>
+        <v>250.17</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -8843,10 +9003,10 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>13</v>
+        <v>8.93</v>
       </c>
       <c r="P101" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
@@ -8855,12 +9015,12 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(8.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -8877,41 +9037,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OBEROIRLTY.NS</t>
+          <t>MOBIKWIK.NS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MOBIKWIK</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>58.4</v>
+        <v>53.5</v>
       </c>
       <c r="E102" t="n">
-        <v>43.915</v>
+        <v>39.99</v>
       </c>
       <c r="F102" t="n">
-        <v>73.7</v>
+        <v>70.5</v>
       </c>
       <c r="G102" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="H102" t="n">
-        <v>1873.2</v>
+        <v>221.45</v>
       </c>
       <c r="I102" t="n">
-        <v>1730.6</v>
+        <v>196.79</v>
       </c>
       <c r="J102" t="n">
-        <v>1996.64</v>
+        <v>239.06</v>
       </c>
       <c r="K102" t="n">
-        <v>2120.09</v>
+        <v>258.44</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -8923,10 +9083,10 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>14.6</v>
+        <v>-8.26</v>
       </c>
       <c r="P102" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -8935,12 +9095,12 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 40.0, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -8957,41 +9117,41 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LODHA.NS</t>
+          <t>AEQUS.NS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>50.8</v>
+        <v>52.6</v>
       </c>
       <c r="E103" t="n">
-        <v>41.69</v>
+        <v>34.64</v>
       </c>
       <c r="F103" t="n">
-        <v>58.4</v>
+        <v>58.9</v>
       </c>
       <c r="G103" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="H103" t="n">
-        <v>1192.15</v>
+        <v>248.78</v>
       </c>
       <c r="I103" t="n">
-        <v>1048.96</v>
+        <v>221.89</v>
       </c>
       <c r="J103" t="n">
-        <v>1294.43</v>
+        <v>281.26</v>
       </c>
       <c r="K103" t="n">
-        <v>1406.94</v>
+        <v>313.73</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -9003,24 +9163,24 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>15.8</v>
+        <v>-9.99</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 34.6, need 83), TQ_FAIL(got 58.9, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -9037,41 +9197,41 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMANTA.NS</t>
+          <t>AKUMS.NS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>48.2</v>
+        <v>50.2</v>
       </c>
       <c r="E104" t="n">
-        <v>39.84</v>
+        <v>34.35</v>
       </c>
       <c r="F104" t="n">
-        <v>55.6</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="H104" t="n">
-        <v>182.82</v>
+        <v>701.95</v>
       </c>
       <c r="I104" t="n">
-        <v>155.66</v>
+        <v>624.41</v>
       </c>
       <c r="J104" t="n">
-        <v>202.22</v>
+        <v>757.34</v>
       </c>
       <c r="K104" t="n">
-        <v>223.56</v>
+        <v>818.26</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -9083,24 +9243,24 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>9.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P104" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 34.4, need 83), TQ_FAIL(got 70.4, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
@@ -9117,41 +9277,41 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>INDOCO.NS</t>
+          <t>BLUEJET.NS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>BLUEJET</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>55.2</v>
+        <v>50.7</v>
       </c>
       <c r="E105" t="n">
-        <v>39</v>
+        <v>33.965</v>
       </c>
       <c r="F105" t="n">
-        <v>67</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="H105" t="n">
-        <v>255.09</v>
+        <v>624.05</v>
       </c>
       <c r="I105" t="n">
-        <v>230.44</v>
+        <v>534.35</v>
       </c>
       <c r="J105" t="n">
-        <v>279.38</v>
+        <v>688.12</v>
       </c>
       <c r="K105" t="n">
-        <v>303.67</v>
+        <v>758.6</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -9163,24 +9323,24 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>-9.42</v>
+        <v>52.1</v>
       </c>
       <c r="P105" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 34.0, need 83), TQ_FAIL(got 70.9, need 73), RR_FAIL(got 1.45, need 2.0), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T105" t="inlineStr">
@@ -9197,41 +9357,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>AKUMS.NS</t>
+          <t>UJJIVANSFB.NS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>53.6</v>
+        <v>50.7</v>
       </c>
       <c r="E106" t="n">
-        <v>38.805</v>
+        <v>33.15</v>
       </c>
       <c r="F106" t="n">
-        <v>67.8</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G106" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="H106" t="n">
-        <v>658.2</v>
+        <v>65.27</v>
       </c>
       <c r="I106" t="n">
-        <v>603.05</v>
+        <v>57.44</v>
       </c>
       <c r="J106" t="n">
-        <v>703.85</v>
+        <v>70.86</v>
       </c>
       <c r="K106" t="n">
-        <v>749.5</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -9243,24 +9403,24 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 33.1, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
@@ -9277,41 +9437,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>TORNTPHARM.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>53.4</v>
+        <v>48.5</v>
       </c>
       <c r="E107" t="n">
-        <v>38.67</v>
+        <v>33.04</v>
       </c>
       <c r="F107" t="n">
-        <v>73.8</v>
+        <v>66.2</v>
       </c>
       <c r="G107" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H107" t="n">
-        <v>4898.2</v>
+        <v>1854.6</v>
       </c>
       <c r="I107" t="n">
-        <v>4506.34</v>
+        <v>1622.88</v>
       </c>
       <c r="J107" t="n">
-        <v>5136.77</v>
+        <v>2020.12</v>
       </c>
       <c r="K107" t="n">
-        <v>5485.99</v>
+        <v>2202.18</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9323,24 +9483,24 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>27.4</v>
+        <v>16.8</v>
       </c>
       <c r="P107" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 33.0, need 83), TQ_FAIL(got 66.2, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -9357,37 +9517,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SAMBHV.NS</t>
+          <t>SIGMAADV.NS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>53.3</v>
+        <v>49.6</v>
       </c>
       <c r="E108" t="n">
-        <v>38.62</v>
+        <v>32.93</v>
       </c>
       <c r="F108" t="n">
-        <v>69.90000000000001</v>
+        <v>55.7</v>
       </c>
       <c r="G108" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="H108" t="n">
-        <v>119.19</v>
+        <v>582.65</v>
       </c>
       <c r="I108" t="n">
-        <v>107.34</v>
+        <v>513.42</v>
       </c>
       <c r="J108" t="n">
-        <v>129.26</v>
+        <v>655.64</v>
       </c>
       <c r="K108" t="n">
-        <v>139.32</v>
+        <v>728.64</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -9403,10 +9563,10 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>18.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P108" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -9415,12 +9575,12 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 32.9, need 83), TQ_FAIL(got 55.7, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
@@ -9437,37 +9597,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RELIGARE.NS</t>
+          <t>MMFL.NS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>MMFL</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>63.5</v>
+        <v>48.2</v>
       </c>
       <c r="E109" t="n">
-        <v>37.9</v>
+        <v>32.66</v>
       </c>
       <c r="F109" t="n">
-        <v>71.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G109" t="n">
-        <v>3.15</v>
+        <v>1.39</v>
       </c>
       <c r="H109" t="n">
-        <v>271.5</v>
+        <v>523.4</v>
       </c>
       <c r="I109" t="n">
-        <v>258.95</v>
+        <v>454.5</v>
       </c>
       <c r="J109" t="n">
-        <v>293.48</v>
+        <v>572.61</v>
       </c>
       <c r="K109" t="n">
-        <v>315.46</v>
+        <v>626.75</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -9483,24 +9643,24 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>3.17</v>
+        <v>10.5</v>
       </c>
       <c r="P109" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 32.7, need 83), TQ_FAIL(got 65.5, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -9517,41 +9677,41 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NACLIND.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NACLIND</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>57.7</v>
+        <v>46.1</v>
       </c>
       <c r="E110" t="n">
-        <v>37.83</v>
+        <v>32.35</v>
       </c>
       <c r="F110" t="n">
-        <v>67.5</v>
+        <v>58.1</v>
       </c>
       <c r="G110" t="n">
-        <v>2.33</v>
+        <v>1.45</v>
       </c>
       <c r="H110" t="n">
-        <v>225.85</v>
+        <v>1220.75</v>
       </c>
       <c r="I110" t="n">
-        <v>195.07</v>
+        <v>1059.03</v>
       </c>
       <c r="J110" t="n">
-        <v>262.74</v>
+        <v>1336.27</v>
       </c>
       <c r="K110" t="n">
-        <v>299.62</v>
+        <v>1463.33</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -9563,24 +9723,24 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>3.07</v>
+        <v>15.8</v>
       </c>
       <c r="P110" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 32.4, need 83), TQ_FAIL(got 58.1, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
@@ -9597,41 +9757,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>WELCORP.NS</t>
+          <t>ANANTRAJ.NS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="E111" t="n">
-        <v>37.63</v>
+        <v>32.31</v>
       </c>
       <c r="F111" t="n">
-        <v>68.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="G111" t="n">
         <v>1.44</v>
       </c>
       <c r="H111" t="n">
-        <v>1601.9</v>
+        <v>585.85</v>
       </c>
       <c r="I111" t="n">
-        <v>1404.26</v>
+        <v>521.26</v>
       </c>
       <c r="J111" t="n">
-        <v>1743.07</v>
+        <v>631.98</v>
       </c>
       <c r="K111" t="n">
-        <v>1898.36</v>
+        <v>682.74</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -9643,10 +9803,10 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>19.4</v>
+        <v>11.2</v>
       </c>
       <c r="P111" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
@@ -9655,12 +9815,12 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 32.3, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
@@ -9677,41 +9837,41 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UNICHEMLAB.NS</t>
+          <t>SUDARSCHEM.NS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>48.5</v>
+        <v>51.1</v>
       </c>
       <c r="E112" t="n">
-        <v>37.37</v>
+        <v>32.15</v>
       </c>
       <c r="F112" t="n">
-        <v>57.4</v>
+        <v>75.3</v>
       </c>
       <c r="G112" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H112" t="n">
-        <v>650.6</v>
+        <v>999.25</v>
       </c>
       <c r="I112" t="n">
-        <v>553.01</v>
+        <v>885.64</v>
       </c>
       <c r="J112" t="n">
-        <v>723.8</v>
+        <v>1080.4</v>
       </c>
       <c r="K112" t="n">
-        <v>796.99</v>
+        <v>1169.66</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9723,10 +9883,10 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>3.17</v>
+        <v>0.49</v>
       </c>
       <c r="P112" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
@@ -9735,12 +9895,12 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 32.1, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
@@ -9757,41 +9917,41 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ETERNAL.NS</t>
+          <t>GANECOS.NS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>50.3</v>
+        <v>47.2</v>
       </c>
       <c r="E113" t="n">
-        <v>37.04</v>
+        <v>31.9</v>
       </c>
       <c r="F113" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G113" t="n">
         <v>1.43</v>
       </c>
       <c r="H113" t="n">
-        <v>292.45</v>
+        <v>1108.7</v>
       </c>
       <c r="I113" t="n">
-        <v>264.79</v>
+        <v>950.46</v>
       </c>
       <c r="J113" t="n">
-        <v>312.21</v>
+        <v>1221.73</v>
       </c>
       <c r="K113" t="n">
-        <v>333.94</v>
+        <v>1346.06</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9803,24 +9963,24 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1.19</v>
+        <v>3.15</v>
       </c>
       <c r="P113" t="n">
-        <v>0.15</v>
+        <v>0.39</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(3.1%&lt;10%)</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -9837,37 +9997,37 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AEQUS.NS</t>
+          <t>CUPID.NS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>52.5</v>
+        <v>45.8</v>
       </c>
       <c r="E114" t="n">
-        <v>36.89</v>
+        <v>31.42</v>
       </c>
       <c r="F114" t="n">
-        <v>67.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="G114" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="H114" t="n">
-        <v>258.07</v>
+        <v>212.24</v>
       </c>
       <c r="I114" t="n">
-        <v>221.89</v>
+        <v>180.4</v>
       </c>
       <c r="J114" t="n">
-        <v>290.62</v>
+        <v>237.98</v>
       </c>
       <c r="K114" t="n">
-        <v>323.16</v>
+        <v>263.71</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -9883,10 +10043,10 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>-9.99</v>
+        <v>27.3</v>
       </c>
       <c r="P114" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
@@ -9895,12 +10055,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 31.4, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
@@ -9917,41 +10077,41 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AETHER.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="E115" t="n">
-        <v>36.72</v>
+        <v>31.09</v>
       </c>
       <c r="F115" t="n">
-        <v>68.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G115" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="H115" t="n">
-        <v>1485.8</v>
+        <v>31.72</v>
       </c>
       <c r="I115" t="n">
-        <v>1298.47</v>
+        <v>27.8</v>
       </c>
       <c r="J115" t="n">
-        <v>1633.93</v>
+        <v>34.52</v>
       </c>
       <c r="K115" t="n">
-        <v>1782.06</v>
+        <v>37.6</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9963,24 +10123,24 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>9.66</v>
+        <v>14.7</v>
       </c>
       <c r="P115" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 31.1, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -9997,41 +10157,41 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MBAPL.NS</t>
+          <t>BUILDPRO.NS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MBAPL</t>
+          <t>BUILDPRO</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>51.5</v>
+        <v>48.4</v>
       </c>
       <c r="E116" t="n">
-        <v>36.53</v>
+        <v>31.02</v>
       </c>
       <c r="F116" t="n">
-        <v>66.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G116" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="H116" t="n">
-        <v>129.85</v>
+        <v>1250.5</v>
       </c>
       <c r="I116" t="n">
-        <v>110.37</v>
+        <v>1076.47</v>
       </c>
       <c r="J116" t="n">
-        <v>145.6</v>
+        <v>1374.81</v>
       </c>
       <c r="K116" t="n">
-        <v>161.35</v>
+        <v>1511.54</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -10043,10 +10203,10 @@
         <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>31.5</v>
+        <v>25.9</v>
       </c>
       <c r="P116" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
@@ -10055,12 +10215,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 31.0, need 83), TQ_FAIL(got 69.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=15&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -10077,41 +10237,41 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GANECOS.NS</t>
+          <t>GANDHAR.NS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>GANDHAR</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>50.3</v>
+        <v>47.5</v>
       </c>
       <c r="E117" t="n">
-        <v>35.81</v>
+        <v>30.035</v>
       </c>
       <c r="F117" t="n">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="G117" t="n">
         <v>1.43</v>
       </c>
       <c r="H117" t="n">
-        <v>1136.45</v>
+        <v>203.15</v>
       </c>
       <c r="I117" t="n">
-        <v>986.99</v>
+        <v>176.68</v>
       </c>
       <c r="J117" t="n">
-        <v>1243.21</v>
+        <v>222.06</v>
       </c>
       <c r="K117" t="n">
-        <v>1360.64</v>
+        <v>242.86</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -10123,24 +10283,24 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>3.15</v>
+        <v>10.5</v>
       </c>
       <c r="P117" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 30.0, need 83), TQ_FAIL(got 68.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -10157,37 +10317,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>THANGAMAYL.NS</t>
+          <t>AZAD.NS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E118" t="n">
-        <v>35.57</v>
+        <v>29.08</v>
       </c>
       <c r="F118" t="n">
-        <v>51.8</v>
+        <v>68.7</v>
       </c>
       <c r="G118" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="H118" t="n">
-        <v>6598.5</v>
+        <v>2479.5</v>
       </c>
       <c r="I118" t="n">
-        <v>5608.72</v>
+        <v>2153.75</v>
       </c>
       <c r="J118" t="n">
-        <v>7494.88</v>
+        <v>2712.18</v>
       </c>
       <c r="K118" t="n">
-        <v>8391.27</v>
+        <v>2968.12</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -10203,24 +10363,24 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>27.93</v>
+        <v>9.09</v>
       </c>
       <c r="P118" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>ROE_TOO_LOW(9.1%&lt;10%)</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -10237,37 +10397,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RELTD.NS</t>
+          <t>GREAVESCOT.NS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>RELTD</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>51.8</v>
+        <v>44.8</v>
       </c>
       <c r="E119" t="n">
-        <v>33.285</v>
+        <v>28.88</v>
       </c>
       <c r="F119" t="n">
-        <v>62.4</v>
+        <v>58.9</v>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="H119" t="n">
-        <v>179.01</v>
+        <v>263.6</v>
       </c>
       <c r="I119" t="n">
-        <v>156.69</v>
+        <v>224.06</v>
       </c>
       <c r="J119" t="n">
-        <v>202.35</v>
+        <v>292.36</v>
       </c>
       <c r="K119" t="n">
-        <v>225.69</v>
+        <v>322.91</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -10283,187 +10443,27 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>21.2</v>
+        <v>8.1</v>
       </c>
       <c r="P119" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
+          <t>CONF_FAIL(got 28.9, need 83), TQ_FAIL(got 58.9, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T119" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>ITDC.NS</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>ITDC</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>49</v>
-      </c>
-      <c r="E120" t="n">
-        <v>31.31</v>
-      </c>
-      <c r="F120" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H120" t="n">
-        <v>728.1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>619.24</v>
-      </c>
-      <c r="J120" t="n">
-        <v>805.86</v>
-      </c>
-      <c r="K120" t="n">
-        <v>891.39</v>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>CONSUMER</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="N120" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="P120" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
-        </is>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>GEMAROMA.NS</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>GEMAROMA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="E121" t="n">
-        <v>28.66</v>
-      </c>
-      <c r="F121" t="n">
-        <v>67</v>
-      </c>
-      <c r="G121" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H121" t="n">
-        <v>210.66</v>
-      </c>
-      <c r="I121" t="n">
-        <v>179.09</v>
-      </c>
-      <c r="J121" t="n">
-        <v>235.12</v>
-      </c>
-      <c r="K121" t="n">
-        <v>259.59</v>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>METALS</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/MOMENTUM))</t>
-        </is>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -25,6 +25,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fail Reason Analysis" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime x Sector" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Trajectory" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shadow Buckets" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shadow Summary" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +562,7 @@
         <v>70.7</v>
       </c>
       <c r="F2" t="n">
-        <v>72.38</v>
+        <v>71.97999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>54.9</v>
@@ -606,7 +608,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 72.4, need 83), TQ_FAIL(got 54.9, need 73)</t>
+          <t>CONF_FAIL(got 72.0, need 83), TQ_FAIL(got 54.9, need 73)</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -640,7 +642,7 @@
         <v>59.9</v>
       </c>
       <c r="F3" t="n">
-        <v>48.415</v>
+        <v>47.515</v>
       </c>
       <c r="G3" t="n">
         <v>59.9</v>
@@ -686,7 +688,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 48.4, need 83), TQ_FAIL(got 59.9, need 73)</t>
+          <t>CONF_FAIL(got 47.5, need 83), TQ_FAIL(got 59.9, need 73)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -817,6 +819,19 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -914,6 +929,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1046,10 +1074,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>76.61499999999999</v>
+        <v>76.675</v>
       </c>
       <c r="F2" t="n">
         <v>69.40000000000001</v>
@@ -1086,7 +1114,7 @@
         <v>40.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1095,7 +1123,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 76.6, need 83), TQ_FAIL(got 69.4, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 76.7, need 83), TQ_FAIL(got 69.4, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1129,7 +1157,7 @@
         <v>64.5</v>
       </c>
       <c r="E3" t="n">
-        <v>74.86</v>
+        <v>74.81</v>
       </c>
       <c r="F3" t="n">
         <v>48.6</v>
@@ -1175,7 +1203,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 74.9, need 83), TQ_FAIL(got 48.6, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 74.8, need 83), TQ_FAIL(got 48.6, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1357,37 +1385,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHOENIXLTD.NS</t>
+          <t>GODREJPROP.NS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>67</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>71.45</v>
+        <v>70.83</v>
       </c>
       <c r="F6" t="n">
-        <v>64.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>1.43</v>
       </c>
       <c r="H6" t="n">
-        <v>2138.9</v>
+        <v>2133</v>
       </c>
       <c r="I6" t="n">
-        <v>1924.22</v>
+        <v>1925.62</v>
       </c>
       <c r="J6" t="n">
-        <v>2292.24</v>
+        <v>2281.13</v>
       </c>
       <c r="K6" t="n">
-        <v>2460.92</v>
+        <v>2444.07</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1403,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>11.6</v>
+        <v>8.82</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 71.5, need 83), TQ_FAIL(got 64.1, need 73), RR_FAIL(got 1.43, need 2.0)</t>
+          <t>CONF_FAIL(got 70.8, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1437,41 +1465,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GODREJPROP.NS</t>
+          <t>TSFINV.NS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>70.83</v>
+        <v>70.5</v>
       </c>
       <c r="F7" t="n">
-        <v>68.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="G7" t="n">
         <v>1.43</v>
       </c>
       <c r="H7" t="n">
-        <v>2133</v>
+        <v>475.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1925.62</v>
+        <v>414.85</v>
       </c>
       <c r="J7" t="n">
-        <v>2281.13</v>
+        <v>518.65</v>
       </c>
       <c r="K7" t="n">
-        <v>2444.07</v>
+        <v>566.22</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1483,24 +1511,24 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8.82</v>
+        <v>8.23</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 70.8, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0)</t>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>TQ_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1517,41 +1545,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TSFINV.NS</t>
+          <t>MARKSANS.NS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>66.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E8" t="n">
-        <v>70.5</v>
+        <v>70.41500000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>61.1</v>
+        <v>70.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.43</v>
+        <v>2.69</v>
       </c>
       <c r="H8" t="n">
-        <v>475.4</v>
+        <v>272.4</v>
       </c>
       <c r="I8" t="n">
-        <v>414.85</v>
+        <v>254.72</v>
       </c>
       <c r="J8" t="n">
-        <v>518.65</v>
+        <v>297.65</v>
       </c>
       <c r="K8" t="n">
-        <v>566.22</v>
+        <v>322.91</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1563,10 +1591,10 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8.23</v>
+        <v>15.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1575,12 +1603,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
+          <t>CONF_FAIL(got 70.4, need 83), TQ_FAIL(got 70.7, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1597,41 +1625,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MARKSANS.NS</t>
+          <t>RADICO.NS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>76.8</v>
+        <v>67.5</v>
       </c>
       <c r="E9" t="n">
-        <v>70.41500000000001</v>
+        <v>70.105</v>
       </c>
       <c r="F9" t="n">
-        <v>70.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="H9" t="n">
-        <v>272.4</v>
+        <v>4073.7</v>
       </c>
       <c r="I9" t="n">
-        <v>254.72</v>
+        <v>3767.07</v>
       </c>
       <c r="J9" t="n">
-        <v>297.65</v>
+        <v>4303.67</v>
       </c>
       <c r="K9" t="n">
-        <v>322.91</v>
+        <v>4533.64</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1643,19 +1671,19 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>15.2</v>
+        <v>20.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0.11</v>
+        <v>0.21</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 70.4, need 83), TQ_FAIL(got 70.7, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 70.1, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1677,41 +1705,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RADICO.NS</t>
+          <t>SHREEJISPG.NS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>67.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>70.045</v>
+        <v>69.88</v>
       </c>
       <c r="F10" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H10" t="n">
-        <v>4073.7</v>
+        <v>551.75</v>
       </c>
       <c r="I10" t="n">
-        <v>3767.07</v>
+        <v>498.33</v>
       </c>
       <c r="J10" t="n">
-        <v>4303.67</v>
+        <v>589.91</v>
       </c>
       <c r="K10" t="n">
-        <v>4533.64</v>
+        <v>631.88</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1723,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>20.3</v>
+        <v>27.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1735,7 +1763,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 70.0, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+          <t>CONF_FAIL(got 69.9, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1757,37 +1785,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHREEJISPG.NS</t>
+          <t>BHAGCHEM.NS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>BHAGCHEM</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>68.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="E11" t="n">
-        <v>69.88</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>68.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1.43</v>
+        <v>2.57</v>
       </c>
       <c r="H11" t="n">
-        <v>551.75</v>
+        <v>295.9</v>
       </c>
       <c r="I11" t="n">
-        <v>498.33</v>
+        <v>277.8</v>
       </c>
       <c r="J11" t="n">
-        <v>589.91</v>
+        <v>321.23</v>
       </c>
       <c r="K11" t="n">
-        <v>631.88</v>
+        <v>346.55</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1803,19 +1831,19 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>27.5</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 69.9, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 69.7, need 83), TQ_FAIL(got 67.5, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1849,7 +1877,7 @@
         <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>69.66</v>
+        <v>69.69</v>
       </c>
       <c r="F12" t="n">
         <v>64.90000000000001</v>
@@ -1886,7 +1914,7 @@
         <v>37.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1895,7 +1923,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 69.7, need 83), TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 69.7, need 83), TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1917,37 +1945,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BHAGCHEM.NS</t>
+          <t>CDSL.NS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BHAGCHEM</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75.2</v>
+        <v>68.3</v>
       </c>
       <c r="E13" t="n">
-        <v>69.65000000000001</v>
+        <v>69.41</v>
       </c>
       <c r="F13" t="n">
-        <v>67.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2.57</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>295.9</v>
+        <v>1431.9</v>
       </c>
       <c r="I13" t="n">
-        <v>277.8</v>
+        <v>1314.87</v>
       </c>
       <c r="J13" t="n">
-        <v>321.23</v>
+        <v>1515.49</v>
       </c>
       <c r="K13" t="n">
-        <v>346.55</v>
+        <v>1607.45</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1963,24 +1991,24 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.63</v>
+        <v>24.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(2.6%&lt;10%)</t>
+          <t>CONF_FAIL(got 69.4, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1997,41 +2025,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CDSL.NS</t>
+          <t>NYKAA.NS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>68.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>69.41</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>73.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G14" t="n">
         <v>1.41</v>
       </c>
       <c r="H14" t="n">
-        <v>1431.9</v>
+        <v>330.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1314.87</v>
+        <v>303.25</v>
       </c>
       <c r="J14" t="n">
-        <v>1515.49</v>
+        <v>349.28</v>
       </c>
       <c r="K14" t="n">
-        <v>1607.45</v>
+        <v>370.38</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2043,19 +2071,19 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>24.5</v>
+        <v>15.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 69.4, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 69.4, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=19&gt;top6)</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2077,41 +2105,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NYKAA.NS</t>
+          <t>AETHER.NS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>67.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="E15" t="n">
-        <v>69.40000000000001</v>
+        <v>69.31</v>
       </c>
       <c r="F15" t="n">
-        <v>70.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>330.1</v>
+        <v>1500.8</v>
       </c>
       <c r="I15" t="n">
-        <v>303.25</v>
+        <v>1298.47</v>
       </c>
       <c r="J15" t="n">
-        <v>349.28</v>
+        <v>1652.54</v>
       </c>
       <c r="K15" t="n">
-        <v>370.38</v>
+        <v>1804.29</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2123,19 +2151,19 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>15.3</v>
+        <v>9.66</v>
       </c>
       <c r="P15" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 69.4, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=18&gt;top6)</t>
+          <t>CONF_FAIL(got 69.3, need 83), TQ_FAIL(got 66.6, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2157,37 +2185,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AETHER.NS</t>
+          <t>WANBURY.NS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>WANBURY</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>66.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>69.28</v>
+        <v>69.2</v>
       </c>
       <c r="F16" t="n">
-        <v>66.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>1500.8</v>
+        <v>297.85</v>
       </c>
       <c r="I16" t="n">
-        <v>1298.47</v>
+        <v>267.65</v>
       </c>
       <c r="J16" t="n">
-        <v>1652.54</v>
+        <v>329.74</v>
       </c>
       <c r="K16" t="n">
-        <v>1804.29</v>
+        <v>361.62</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2203,24 +2231,24 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>9.66</v>
+        <v>76.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.7%&lt;10%)</t>
+          <t>CONF_FAIL(got 69.2, need 83), RR_FAIL(got 1.86, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2237,37 +2265,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WANBURY.NS</t>
+          <t>IOLCP.NS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WANBURY</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71.59999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="E17" t="n">
-        <v>69.2</v>
+        <v>68.98</v>
       </c>
       <c r="F17" t="n">
-        <v>73.5</v>
+        <v>52.2</v>
       </c>
       <c r="G17" t="n">
-        <v>1.86</v>
+        <v>1.64</v>
       </c>
       <c r="H17" t="n">
-        <v>297.85</v>
+        <v>171.06</v>
       </c>
       <c r="I17" t="n">
-        <v>267.65</v>
+        <v>145.4</v>
       </c>
       <c r="J17" t="n">
-        <v>329.74</v>
+        <v>192.73</v>
       </c>
       <c r="K17" t="n">
-        <v>361.62</v>
+        <v>214.4</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2283,24 +2311,24 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>76.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 69.2, need 83), RR_FAIL(got 1.86, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>ROE_TOO_LOW(8.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2317,37 +2345,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IOLCP.NS</t>
+          <t>CGCL.NS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>63.6</v>
+        <v>63.9</v>
       </c>
       <c r="E18" t="n">
-        <v>68.98</v>
+        <v>68.58</v>
       </c>
       <c r="F18" t="n">
-        <v>52.2</v>
+        <v>58.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="H18" t="n">
-        <v>171.06</v>
+        <v>252.22</v>
       </c>
       <c r="I18" t="n">
-        <v>145.4</v>
+        <v>223.14</v>
       </c>
       <c r="J18" t="n">
-        <v>192.73</v>
+        <v>272.99</v>
       </c>
       <c r="K18" t="n">
-        <v>214.4</v>
+        <v>295.84</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2363,24 +2391,24 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>8.380000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="P18" t="n">
-        <v>0.08</v>
+        <v>3.35</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(8.4%&lt;10%)</t>
+          <t>DE_TOO_HIGH(3.35&gt;1.50)</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2409,7 +2437,7 @@
         <v>65.3</v>
       </c>
       <c r="E19" t="n">
-        <v>68.79000000000001</v>
+        <v>68.54000000000001</v>
       </c>
       <c r="F19" t="n">
         <v>62.3</v>
@@ -2455,7 +2483,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 68.8, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.48, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 68.5, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.48, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2477,37 +2505,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CGCL.NS</t>
+          <t>PNBHOUSING.NS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>PNBHOUSING</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>63.9</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>68.58</v>
+        <v>68.3</v>
       </c>
       <c r="F20" t="n">
-        <v>58.3</v>
+        <v>65.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H20" t="n">
-        <v>252.22</v>
+        <v>1110.6</v>
       </c>
       <c r="I20" t="n">
-        <v>223.14</v>
+        <v>1019.18</v>
       </c>
       <c r="J20" t="n">
-        <v>272.99</v>
+        <v>1179.98</v>
       </c>
       <c r="K20" t="n">
-        <v>295.84</v>
+        <v>1249.36</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2523,24 +2551,24 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>16.5</v>
+        <v>12.7</v>
       </c>
       <c r="P20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(3.35&gt;1.50)</t>
+          <t>CONF_FAIL(got 68.3, need 83), TQ_FAIL(got 65.8, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2557,37 +2585,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>INDIQUBE.NS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SETL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62.1</v>
+        <v>66.7</v>
       </c>
       <c r="E21" t="n">
-        <v>68.45999999999999</v>
+        <v>68.27</v>
       </c>
       <c r="F21" t="n">
-        <v>43.1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.87</v>
+        <v>1.42</v>
       </c>
       <c r="H21" t="n">
-        <v>290.7</v>
+        <v>178.11</v>
       </c>
       <c r="I21" t="n">
-        <v>247.09</v>
+        <v>162.67</v>
       </c>
       <c r="J21" t="n">
-        <v>332.64</v>
+        <v>191.04</v>
       </c>
       <c r="K21" t="n">
-        <v>374.58</v>
+        <v>203.98</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2603,19 +2631,19 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 68.5, need 83), TQ_FAIL(got 43.1, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 68.3, need 83), TQ_FAIL(got 68.6, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2637,37 +2665,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TAJGVK.NS</t>
+          <t>MAHLIFE.NS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TAJGVK</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>68.3</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>63.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="H22" t="n">
-        <v>371.7</v>
+        <v>378.9</v>
       </c>
       <c r="I22" t="n">
-        <v>330.26</v>
+        <v>353.62</v>
       </c>
       <c r="J22" t="n">
-        <v>401.3</v>
+        <v>401.29</v>
       </c>
       <c r="K22" t="n">
-        <v>433.86</v>
+        <v>423.68</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2683,24 +2711,24 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>18.4</v>
+        <v>9.91</v>
       </c>
       <c r="P22" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 68.3, need 83), TQ_FAIL(got 63.7, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>ROE_TOO_LOW(9.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2717,37 +2745,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LLOYDSENT.NS</t>
+          <t>CUB.NS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>68.09999999999999</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>70.40000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="G23" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="H23" t="n">
-        <v>78.18000000000001</v>
+        <v>229.33</v>
       </c>
       <c r="I23" t="n">
-        <v>69.75</v>
+        <v>201.82</v>
       </c>
       <c r="J23" t="n">
-        <v>85.94</v>
+        <v>248.98</v>
       </c>
       <c r="K23" t="n">
-        <v>93.70999999999999</v>
+        <v>270.6</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2763,24 +2791,24 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.33</v>
+        <v>13.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(0.3%&lt;10%)</t>
+          <t>CONF_FAIL(got 67.9, need 83), TQ_FAIL(got 61.8, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2797,37 +2825,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EIEL.NS</t>
+          <t>CHOICEIN.NS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>CHOICEIN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>66.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>68.05</v>
+        <v>67.84</v>
       </c>
       <c r="F24" t="n">
-        <v>66.8</v>
+        <v>68.2</v>
       </c>
       <c r="G24" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="H24" t="n">
-        <v>244.49</v>
+        <v>835</v>
       </c>
       <c r="I24" t="n">
-        <v>211.29</v>
+        <v>751.4400000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>270.1</v>
+        <v>894.6900000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>295.7</v>
+        <v>960.34</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2843,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -2855,7 +2883,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 68.0, need 83), TQ_FAIL(got 66.8, need 73), RR_FAIL(got 1.49, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.8, need 83), TQ_FAIL(got 68.2, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2877,37 +2905,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAHLIFE.NS</t>
+          <t>OPTIEMUS.NS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>69.40000000000001</v>
+        <v>63.1</v>
       </c>
       <c r="E25" t="n">
-        <v>68.01000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="F25" t="n">
-        <v>73.59999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="G25" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="H25" t="n">
-        <v>378.9</v>
+        <v>541.05</v>
       </c>
       <c r="I25" t="n">
-        <v>353.62</v>
+        <v>459.89</v>
       </c>
       <c r="J25" t="n">
-        <v>401.29</v>
+        <v>601.92</v>
       </c>
       <c r="K25" t="n">
-        <v>423.68</v>
+        <v>662.79</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2923,19 +2951,19 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>9.91</v>
+        <v>9.16</v>
       </c>
       <c r="P25" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.9%&lt;10%)</t>
+          <t>ROE_TOO_LOW(9.2%&lt;10%)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2957,37 +2985,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CUB.NS</t>
+          <t>TAJGVK.NS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>TAJGVK</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>67.93000000000001</v>
+        <v>67.755</v>
       </c>
       <c r="F26" t="n">
-        <v>61.8</v>
+        <v>63.7</v>
       </c>
       <c r="G26" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="H26" t="n">
-        <v>229.33</v>
+        <v>371.7</v>
       </c>
       <c r="I26" t="n">
-        <v>201.82</v>
+        <v>330.26</v>
       </c>
       <c r="J26" t="n">
-        <v>248.98</v>
+        <v>401.3</v>
       </c>
       <c r="K26" t="n">
-        <v>270.6</v>
+        <v>433.86</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3003,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>13.2</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -3015,7 +3043,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.9, need 83), TQ_FAIL(got 61.8, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.8, need 83), TQ_FAIL(got 63.7, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3037,37 +3065,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PNBHOUSING.NS</t>
+          <t>JAYBARMARU.NS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PNBHOUSING</t>
+          <t>JAYBARMARU</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>65.7</v>
+        <v>61.2</v>
       </c>
       <c r="E27" t="n">
-        <v>67.89</v>
+        <v>67.71000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>65.8</v>
+        <v>47.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="H27" t="n">
-        <v>1110.6</v>
+        <v>187.77</v>
       </c>
       <c r="I27" t="n">
-        <v>1019.18</v>
+        <v>162.54</v>
       </c>
       <c r="J27" t="n">
-        <v>1179.98</v>
+        <v>208.02</v>
       </c>
       <c r="K27" t="n">
-        <v>1249.36</v>
+        <v>228.26</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3083,24 +3111,24 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>12.7</v>
+        <v>22.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.77</v>
+        <v>0.76</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(2.77&gt;1.50)</t>
+          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 47.7, need 73), RR_FAIL(got 1.53, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3117,37 +3145,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OPTIEMUS.NS</t>
+          <t>EIEL.NS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>63.1</v>
+        <v>66.5</v>
       </c>
       <c r="E28" t="n">
-        <v>67.8</v>
+        <v>67.69499999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>56.5</v>
+        <v>66.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="H28" t="n">
-        <v>541.05</v>
+        <v>244.49</v>
       </c>
       <c r="I28" t="n">
-        <v>459.89</v>
+        <v>211.29</v>
       </c>
       <c r="J28" t="n">
-        <v>601.92</v>
+        <v>270.1</v>
       </c>
       <c r="K28" t="n">
-        <v>662.79</v>
+        <v>295.7</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3163,24 +3191,24 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>9.16</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.2%&lt;10%)</t>
+          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 66.8, need 73), RR_FAIL(got 1.49, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -3197,37 +3225,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SIGNPOST.NS</t>
+          <t>PICCADIL.NS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SIGNPOST</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E29" t="n">
         <v>67.66</v>
       </c>
       <c r="F29" t="n">
-        <v>58.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="H29" t="n">
-        <v>317.6</v>
+        <v>671.8</v>
       </c>
       <c r="I29" t="n">
-        <v>269.96</v>
+        <v>597.09</v>
       </c>
       <c r="J29" t="n">
-        <v>359.6</v>
+        <v>725.17</v>
       </c>
       <c r="K29" t="n">
-        <v>401.61</v>
+        <v>783.86</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3243,19 +3271,19 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>27.6</v>
+        <v>17.4</v>
       </c>
       <c r="P29" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.69, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3277,37 +3305,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RISHABH.NS</t>
+          <t>SIGNPOST.NS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RISHABH</t>
+          <t>SIGNPOST</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>66.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>67.59</v>
+        <v>67.66</v>
       </c>
       <c r="F30" t="n">
-        <v>66.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="G30" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="H30" t="n">
-        <v>662.1</v>
+        <v>317.6</v>
       </c>
       <c r="I30" t="n">
-        <v>562.78</v>
+        <v>269.96</v>
       </c>
       <c r="J30" t="n">
-        <v>738.5</v>
+        <v>359.6</v>
       </c>
       <c r="K30" t="n">
-        <v>814.89</v>
+        <v>401.61</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3323,24 +3351,24 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>27.6</v>
       </c>
       <c r="P30" t="n">
-        <v>0.11</v>
+        <v>0.7</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>CONF_FAIL(got 67.7, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.69, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3357,37 +3385,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KMEW.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KMEW</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>66.5</v>
+        <v>62.1</v>
       </c>
       <c r="E31" t="n">
-        <v>67.59</v>
+        <v>67.63499999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>64.5</v>
+        <v>43.1</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="H31" t="n">
-        <v>2412.7</v>
+        <v>290.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2084.13</v>
+        <v>247.09</v>
       </c>
       <c r="J31" t="n">
-        <v>2692.65</v>
+        <v>332.64</v>
       </c>
       <c r="K31" t="n">
-        <v>2972.6</v>
+        <v>374.58</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3403,19 +3431,19 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>20</v>
+        <v>10.7</v>
       </c>
       <c r="P31" t="n">
-        <v>0.39</v>
+        <v>0.1</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.6, need 83), TQ_FAIL(got 64.5, need 73), RR_FAIL(got 1.63, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.6, need 83), TQ_FAIL(got 43.1, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3437,37 +3465,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SUVEN.NS</t>
+          <t>RISHABH.NS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUVEN</t>
+          <t>RISHABH</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>64.3</v>
+        <v>66.5</v>
       </c>
       <c r="E32" t="n">
-        <v>67.55</v>
+        <v>67.59</v>
       </c>
       <c r="F32" t="n">
-        <v>57.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="H32" t="n">
-        <v>357.85</v>
+        <v>662.1</v>
       </c>
       <c r="I32" t="n">
-        <v>304.17</v>
+        <v>562.78</v>
       </c>
       <c r="J32" t="n">
-        <v>403.83</v>
+        <v>738.5</v>
       </c>
       <c r="K32" t="n">
-        <v>449.81</v>
+        <v>814.89</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3483,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-78.8</v>
+        <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -3495,12 +3523,12 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 57.5, need 73), RR_FAIL(got 1.66, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3575,7 +3603,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.92, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.92, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3597,41 +3625,41 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JAYBARMARU.NS</t>
+          <t>SHILPAMED.NS</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAYBARMARU</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>61.2</v>
+        <v>64.5</v>
       </c>
       <c r="E34" t="n">
-        <v>67.535</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>47.7</v>
+        <v>58.6</v>
       </c>
       <c r="G34" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H34" t="n">
-        <v>187.77</v>
+        <v>627.15</v>
       </c>
       <c r="I34" t="n">
-        <v>162.54</v>
+        <v>554.17</v>
       </c>
       <c r="J34" t="n">
-        <v>208.02</v>
+        <v>684.84</v>
       </c>
       <c r="K34" t="n">
-        <v>228.26</v>
+        <v>742.54</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3643,24 +3671,24 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>22.2</v>
+        <v>9.4</v>
       </c>
       <c r="P34" t="n">
-        <v>0.76</v>
+        <v>0.25</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.5, need 83), TQ_FAIL(got 47.7, need 73), RR_FAIL(got 1.53, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>ROE_TOO_LOW(9.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3677,41 +3705,41 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHILPAMED.NS</t>
+          <t>STYL.NS</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>67.48999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="F35" t="n">
-        <v>58.6</v>
+        <v>61.9</v>
       </c>
       <c r="G35" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="H35" t="n">
-        <v>627.15</v>
+        <v>359.5</v>
       </c>
       <c r="I35" t="n">
-        <v>554.17</v>
+        <v>305.58</v>
       </c>
       <c r="J35" t="n">
-        <v>684.84</v>
+        <v>398.68</v>
       </c>
       <c r="K35" t="n">
-        <v>742.54</v>
+        <v>440.38</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3723,24 +3751,24 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>9.4</v>
+        <v>23.3</v>
       </c>
       <c r="P35" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.4%&lt;10%)</t>
+          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 61.9, need 73), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3757,37 +3785,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>STYL.NS</t>
+          <t>STOVEKRAFT.NS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>STOVEKRAFT</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>64.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E36" t="n">
-        <v>67.3</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>61.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>1.4</v>
+        <v>2.27</v>
       </c>
       <c r="H36" t="n">
-        <v>359.5</v>
+        <v>798.95</v>
       </c>
       <c r="I36" t="n">
-        <v>305.58</v>
+        <v>746.35</v>
       </c>
       <c r="J36" t="n">
-        <v>398.68</v>
+        <v>863.7</v>
       </c>
       <c r="K36" t="n">
-        <v>440.38</v>
+        <v>928.4400000000001</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3803,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>23.3</v>
+        <v>67.5</v>
       </c>
       <c r="P36" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -3815,7 +3843,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 61.9, need 73), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 70.1, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3837,37 +3865,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>STOVEKRAFT.NS</t>
+          <t>SUVEN.NS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>STOVEKRAFT</t>
+          <t>SUVEN</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>72.8</v>
+        <v>64.3</v>
       </c>
       <c r="E37" t="n">
-        <v>67.29000000000001</v>
+        <v>67.175</v>
       </c>
       <c r="F37" t="n">
-        <v>70.09999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="G37" t="n">
-        <v>2.27</v>
+        <v>1.66</v>
       </c>
       <c r="H37" t="n">
-        <v>798.95</v>
+        <v>357.85</v>
       </c>
       <c r="I37" t="n">
-        <v>746.35</v>
+        <v>304.17</v>
       </c>
       <c r="J37" t="n">
-        <v>863.7</v>
+        <v>403.83</v>
       </c>
       <c r="K37" t="n">
-        <v>928.4400000000001</v>
+        <v>449.81</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3883,19 +3911,19 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>67.5</v>
+        <v>-78.8</v>
       </c>
       <c r="P37" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.3, need 83), TQ_FAIL(got 70.1, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.2, need 83), TQ_FAIL(got 57.5, need 73), RR_FAIL(got 1.66, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3917,41 +3945,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHOICEIN.NS</t>
+          <t>PAYTM.NS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHOICEIN</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>66.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E38" t="n">
-        <v>67.19</v>
+        <v>67.08</v>
       </c>
       <c r="F38" t="n">
-        <v>68.2</v>
+        <v>71.5</v>
       </c>
       <c r="G38" t="n">
         <v>1.43</v>
       </c>
       <c r="H38" t="n">
-        <v>835</v>
+        <v>1341.8</v>
       </c>
       <c r="I38" t="n">
-        <v>751.4400000000001</v>
+        <v>1209.2</v>
       </c>
       <c r="J38" t="n">
-        <v>894.6900000000001</v>
+        <v>1436.51</v>
       </c>
       <c r="K38" t="n">
-        <v>960.34</v>
+        <v>1540.7</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3963,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>16.1</v>
+        <v>4.7</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -3975,7 +4003,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.2, need 83), TQ_FAIL(got 68.2, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 67.1, need 83), TQ_FAIL(got 71.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=17&gt;top6)</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -3997,41 +4025,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAYTM.NS</t>
+          <t>DELHIVERY.NS</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>DELHIVERY</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>67</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>67.08</v>
+        <v>67.02</v>
       </c>
       <c r="F39" t="n">
-        <v>71.5</v>
+        <v>74.2</v>
       </c>
       <c r="G39" t="n">
         <v>1.43</v>
       </c>
       <c r="H39" t="n">
-        <v>1341.8</v>
+        <v>520.3</v>
       </c>
       <c r="I39" t="n">
-        <v>1209.2</v>
+        <v>464.11</v>
       </c>
       <c r="J39" t="n">
-        <v>1436.51</v>
+        <v>560.4299999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>1540.7</v>
+        <v>604.58</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4043,10 +4071,10 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4.7</v>
+        <v>1.87</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -4055,12 +4083,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.1, need 83), TQ_FAIL(got 71.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=17&gt;top6)</t>
+          <t>ROE_TOO_LOW(1.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -4077,41 +4105,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DELHIVERY.NS</t>
+          <t>POONAWALLA.NS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>POONAWALLA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>67.40000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="E40" t="n">
-        <v>67.02</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>74.2</v>
+        <v>66.7</v>
       </c>
       <c r="G40" t="n">
         <v>1.43</v>
       </c>
       <c r="H40" t="n">
-        <v>520.3</v>
+        <v>477</v>
       </c>
       <c r="I40" t="n">
-        <v>464.11</v>
+        <v>426.48</v>
       </c>
       <c r="J40" t="n">
-        <v>560.4299999999999</v>
+        <v>513.09</v>
       </c>
       <c r="K40" t="n">
-        <v>604.58</v>
+        <v>552.78</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4123,19 +4151,19 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1.87</v>
+        <v>5.86</v>
       </c>
       <c r="P40" t="n">
-        <v>0.15</v>
+        <v>4.68</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(1.9%&lt;10%)</t>
+          <t>ROE_TOO_LOW(5.9%&lt;10%)</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4157,37 +4185,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PICCADIL.NS</t>
+          <t>CNL.NS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>CNL</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>66.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="E41" t="n">
-        <v>67</v>
+        <v>66.935</v>
       </c>
       <c r="F41" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="H41" t="n">
-        <v>671.8</v>
+        <v>847.5</v>
       </c>
       <c r="I41" t="n">
-        <v>597.09</v>
+        <v>721.84</v>
       </c>
       <c r="J41" t="n">
-        <v>725.17</v>
+        <v>937.26</v>
       </c>
       <c r="K41" t="n">
-        <v>783.86</v>
+        <v>1035.99</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4203,19 +4231,19 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>17.4</v>
+        <v>21.4</v>
       </c>
       <c r="P41" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 67.0, need 83), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 66.9, need 83), TQ_FAIL(got 67.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4237,37 +4265,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>POONAWALLA.NS</t>
+          <t>BORORENEW.NS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>65.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>66.98999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="F42" t="n">
-        <v>66.7</v>
+        <v>64</v>
       </c>
       <c r="G42" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="H42" t="n">
-        <v>477</v>
+        <v>640.55</v>
       </c>
       <c r="I42" t="n">
-        <v>426.48</v>
+        <v>584.5599999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>513.09</v>
+        <v>695.65</v>
       </c>
       <c r="K42" t="n">
-        <v>552.78</v>
+        <v>750.75</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4283,24 +4311,24 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>5.86</v>
+        <v>26.1</v>
       </c>
       <c r="P42" t="n">
-        <v>4.68</v>
+        <v>0.11</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(5.9%&lt;10%)</t>
+          <t>CONF_FAIL(got 66.8, need 83), TQ_FAIL(got 64.0, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4317,37 +4345,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BORORENEW.NS</t>
+          <t>DATAMATICS.NS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>67.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>66.81</v>
+        <v>66.80500000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>64</v>
+        <v>75.8</v>
       </c>
       <c r="G43" t="n">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="H43" t="n">
-        <v>640.55</v>
+        <v>900.45</v>
       </c>
       <c r="I43" t="n">
-        <v>584.5599999999999</v>
+        <v>784.85</v>
       </c>
       <c r="J43" t="n">
-        <v>695.65</v>
+        <v>983.02</v>
       </c>
       <c r="K43" t="n">
-        <v>750.75</v>
+        <v>1073.85</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4363,19 +4391,19 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>26.1</v>
+        <v>16.4</v>
       </c>
       <c r="P43" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 66.8, need 83), TQ_FAIL(got 64.0, need 73), RR_FAIL(got 1.87, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 66.8, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4397,37 +4425,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DATAMATICS.NS</t>
+          <t>MOSCHIP.NS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>MOSCHIP</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>68.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>66.80500000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>75.8</v>
+        <v>64.7</v>
       </c>
       <c r="G44" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H44" t="n">
-        <v>900.45</v>
+        <v>236.82</v>
       </c>
       <c r="I44" t="n">
-        <v>784.85</v>
+        <v>202.88</v>
       </c>
       <c r="J44" t="n">
-        <v>983.02</v>
+        <v>261.06</v>
       </c>
       <c r="K44" t="n">
-        <v>1073.85</v>
+        <v>287.73</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4443,19 +4471,19 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>16.4</v>
+        <v>11</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 66.8, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 66.7, need 83), TQ_FAIL(got 64.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -4477,37 +4505,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MOSCHIP.NS</t>
+          <t>MBAPL.NS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MOSCHIP</t>
+          <t>MBAPL</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>65.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E45" t="n">
-        <v>66.64</v>
+        <v>66.63</v>
       </c>
       <c r="F45" t="n">
-        <v>64.7</v>
+        <v>58.1</v>
       </c>
       <c r="G45" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="H45" t="n">
-        <v>236.82</v>
+        <v>131.25</v>
       </c>
       <c r="I45" t="n">
-        <v>202.88</v>
+        <v>111.56</v>
       </c>
       <c r="J45" t="n">
-        <v>261.06</v>
+        <v>146.97</v>
       </c>
       <c r="K45" t="n">
-        <v>287.73</v>
+        <v>162.69</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4523,24 +4551,24 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>11</v>
+        <v>31.5</v>
       </c>
       <c r="P45" t="n">
-        <v>0.22</v>
+        <v>1.57</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 66.6, need 83), TQ_FAIL(got 64.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>DE_TOO_HIGH(1.57&gt;1.50)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4557,37 +4585,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MBAPL.NS</t>
+          <t>KMEW.NS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MBAPL</t>
+          <t>KMEW</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>63.9</v>
+        <v>66.5</v>
       </c>
       <c r="E46" t="n">
-        <v>66.63</v>
+        <v>66.59</v>
       </c>
       <c r="F46" t="n">
-        <v>58.1</v>
+        <v>64.5</v>
       </c>
       <c r="G46" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="H46" t="n">
-        <v>131.25</v>
+        <v>2412.7</v>
       </c>
       <c r="I46" t="n">
-        <v>111.56</v>
+        <v>2084.13</v>
       </c>
       <c r="J46" t="n">
-        <v>146.97</v>
+        <v>2692.65</v>
       </c>
       <c r="K46" t="n">
-        <v>162.69</v>
+        <v>2972.6</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4603,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>31.5</v>
+        <v>20</v>
       </c>
       <c r="P46" t="n">
-        <v>1.57</v>
+        <v>0.39</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -4615,12 +4643,12 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(1.57&gt;1.50)</t>
+          <t>CONF_FAIL(got 66.6, need 83), TQ_FAIL(got 64.5, need 73), RR_FAIL(got 1.63, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -4695,7 +4723,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 66.3, need 83), TQ_FAIL(got 55.3, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 66.3, need 83), TQ_FAIL(got 55.3, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -4775,7 +4803,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 66.0, need 83), TQ_FAIL(got 66.9, need 73), RR_FAIL(got 1.50, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 66.0, need 83), TQ_FAIL(got 66.9, need 73), RR_FAIL(got 1.50, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -4797,37 +4825,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BALAMINES.NS</t>
+          <t>TVSSCS.NS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>62.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>66</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>58.2</v>
+        <v>75.7</v>
       </c>
       <c r="G49" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="H49" t="n">
-        <v>2414.9</v>
+        <v>141.66</v>
       </c>
       <c r="I49" t="n">
-        <v>2052.66</v>
+        <v>128.51</v>
       </c>
       <c r="J49" t="n">
-        <v>2690.47</v>
+        <v>152.46</v>
       </c>
       <c r="K49" t="n">
-        <v>2966.04</v>
+        <v>163.27</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4843,24 +4871,24 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>8.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(8.7%&lt;10%)</t>
+          <t>CONF_FAIL(got 65.9, need 83), RR_FAIL(got 1.54, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4877,37 +4905,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INDIQUBE.NS</t>
+          <t>BALAMINES.NS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>66</v>
+        <v>62.8</v>
       </c>
       <c r="E50" t="n">
-        <v>65.86</v>
+        <v>65.895</v>
       </c>
       <c r="F50" t="n">
-        <v>68.59999999999999</v>
+        <v>58.2</v>
       </c>
       <c r="G50" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="H50" t="n">
-        <v>178.11</v>
+        <v>2414.9</v>
       </c>
       <c r="I50" t="n">
-        <v>162.67</v>
+        <v>2052.66</v>
       </c>
       <c r="J50" t="n">
-        <v>191.04</v>
+        <v>2690.47</v>
       </c>
       <c r="K50" t="n">
-        <v>203.98</v>
+        <v>2966.04</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4923,24 +4951,24 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-41.57</v>
+        <v>8.74</v>
       </c>
       <c r="P50" t="n">
-        <v>10.12</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(10.12&gt;1.50)</t>
+          <t>CONF_FAIL(got 65.9, need 83), TQ_FAIL(got 58.2, need 73), RR_FAIL(got 1.47, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -5037,37 +5065,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CNL.NS</t>
+          <t>EQUITASBNK.NS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CNL</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>65.59999999999999</v>
+        <v>67.7</v>
       </c>
       <c r="E52" t="n">
-        <v>65.74000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="F52" t="n">
-        <v>67.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="G52" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H52" t="n">
-        <v>847.5</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>721.84</v>
+        <v>73.48</v>
       </c>
       <c r="J52" t="n">
-        <v>937.26</v>
+        <v>88.81</v>
       </c>
       <c r="K52" t="n">
-        <v>1035.99</v>
+        <v>95.38</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -5083,19 +5111,19 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 65.7, need 83), TQ_FAIL(got 67.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 65.8, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5117,57 +5145,57 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ATHERENERG.NS</t>
+          <t>INDOSTAR.NS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>INDOSTAR</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>62.8</v>
+        <v>68.7</v>
       </c>
       <c r="E53" t="n">
-        <v>65.61</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>59.4</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G53" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>269.55</v>
+      </c>
+      <c r="I53" t="n">
+        <v>248.4</v>
+      </c>
+      <c r="J53" t="n">
+        <v>291.91</v>
+      </c>
+      <c r="K53" t="n">
+        <v>314.28</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>TRANSITION</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="P53" t="n">
         <v>1.45</v>
       </c>
-      <c r="H53" t="n">
-        <v>1225.8</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1058.53</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1345.28</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1476.7</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>POWER_EQ</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>TRANSITION</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-33.74</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.26</v>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
@@ -5175,7 +5203,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 65.6, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
+          <t>CONF_FAIL(got 65.7, need 83), TQ_FAIL(got 70.6, need 73), RR_FAIL(got 1.80, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5197,41 +5225,41 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BAJAJCON.NS</t>
+          <t>ATHERENERG.NS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BAJAJCON</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>66.09999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="E54" t="n">
-        <v>65.43000000000001</v>
+        <v>65.67</v>
       </c>
       <c r="F54" t="n">
-        <v>69.8</v>
+        <v>59.4</v>
       </c>
       <c r="G54" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H54" t="n">
-        <v>670.25</v>
+        <v>1225.8</v>
       </c>
       <c r="I54" t="n">
-        <v>586.62</v>
+        <v>1058.53</v>
       </c>
       <c r="J54" t="n">
-        <v>729.98</v>
+        <v>1345.28</v>
       </c>
       <c r="K54" t="n">
-        <v>795.7</v>
+        <v>1476.7</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5243,19 +5271,19 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 65.4, need 83), TQ_FAIL(got 69.8, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 65.7, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -5357,37 +5385,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>THANGAMAYL.NS</t>
+          <t>ASKAUTOLTD.NS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>65</v>
+        <v>67.2</v>
       </c>
       <c r="E56" t="n">
-        <v>65.19000000000001</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>57.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="H56" t="n">
-        <v>6540.5</v>
+        <v>471.85</v>
       </c>
       <c r="I56" t="n">
-        <v>5591.9</v>
+        <v>438.8</v>
       </c>
       <c r="J56" t="n">
-        <v>7443.64</v>
+        <v>503.86</v>
       </c>
       <c r="K56" t="n">
-        <v>8346.77</v>
+        <v>535.88</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -5403,19 +5431,19 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>27.93</v>
+        <v>25.3</v>
       </c>
       <c r="P56" t="n">
-        <v>0.64</v>
+        <v>0.52</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 65.2, need 83), TQ_FAIL(got 57.6, need 73), RR_FAIL(got 1.85, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 65.0, need 83), TQ_FAIL(got 65.9, need 73), RR_FAIL(got 1.78, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -5437,37 +5465,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EQUITASBNK.NS</t>
+          <t>MEESHO.NS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>MEESHO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>67.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="E57" t="n">
-        <v>65.06</v>
+        <v>64.94</v>
       </c>
       <c r="F57" t="n">
-        <v>74.8</v>
+        <v>61.6</v>
       </c>
       <c r="G57" t="n">
-        <v>1.41</v>
+        <v>2.26</v>
       </c>
       <c r="H57" t="n">
-        <v>82.23999999999999</v>
+        <v>194.11</v>
       </c>
       <c r="I57" t="n">
-        <v>73.48</v>
+        <v>180.09</v>
       </c>
       <c r="J57" t="n">
-        <v>88.81</v>
+        <v>210.91</v>
       </c>
       <c r="K57" t="n">
-        <v>95.38</v>
+        <v>227.71</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -5483,24 +5511,24 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1.69</v>
+        <v>-42.3</v>
       </c>
       <c r="P57" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(1.7%&lt;10%)</t>
+          <t>CONF_FAIL(got 64.9, need 83), TQ_FAIL(got 61.6, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
@@ -5517,37 +5545,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD.NS</t>
+          <t>FUSION.NS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>FUSION</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>67.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>65.04000000000001</v>
+        <v>64.84</v>
       </c>
       <c r="F58" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="H58" t="n">
-        <v>471.85</v>
+        <v>234.04</v>
       </c>
       <c r="I58" t="n">
-        <v>438.8</v>
+        <v>198.93</v>
       </c>
       <c r="J58" t="n">
-        <v>503.86</v>
+        <v>261.41</v>
       </c>
       <c r="K58" t="n">
-        <v>535.88</v>
+        <v>288.78</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -5563,24 +5591,24 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>25.3</v>
+        <v>0.68</v>
       </c>
       <c r="P58" t="n">
-        <v>0.52</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 65.0, need 83), TQ_FAIL(got 65.9, need 73), RR_FAIL(got 1.78, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>ROE_TOO_LOW(0.7%&lt;10%)</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -5597,37 +5625,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MEESHO.NS</t>
+          <t>AEGISVOPAK.NS</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MEESHO</t>
+          <t>AEGISVOPAK</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>70.3</v>
+        <v>63.7</v>
       </c>
       <c r="E59" t="n">
-        <v>64.94</v>
+        <v>64.66</v>
       </c>
       <c r="F59" t="n">
-        <v>61.6</v>
+        <v>62.3</v>
       </c>
       <c r="G59" t="n">
-        <v>2.26</v>
+        <v>1.45</v>
       </c>
       <c r="H59" t="n">
-        <v>194.11</v>
+        <v>283.18</v>
       </c>
       <c r="I59" t="n">
-        <v>180.09</v>
+        <v>240.7</v>
       </c>
       <c r="J59" t="n">
-        <v>210.91</v>
+        <v>315.04</v>
       </c>
       <c r="K59" t="n">
-        <v>227.71</v>
+        <v>346.9</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -5643,10 +5671,10 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>-42.3</v>
+        <v>10</v>
       </c>
       <c r="P59" t="n">
-        <v>0.01</v>
+        <v>0.84</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -5655,7 +5683,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 64.9, need 83), TQ_FAIL(got 61.6, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 64.7, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -5677,37 +5705,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FUSION.NS</t>
+          <t>EMBDL.NS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FUSION</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>64.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="E60" t="n">
-        <v>64.84</v>
+        <v>64.64</v>
       </c>
       <c r="F60" t="n">
-        <v>65.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G60" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="H60" t="n">
-        <v>234.04</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>198.93</v>
+        <v>60.16</v>
       </c>
       <c r="J60" t="n">
-        <v>261.41</v>
+        <v>72.05</v>
       </c>
       <c r="K60" t="n">
-        <v>288.78</v>
+        <v>77.86</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -5723,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0.68</v>
+        <v>-9.1</v>
       </c>
       <c r="P60" t="n">
-        <v>2.28</v>
+        <v>0.53</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -5735,12 +5763,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(0.7%&lt;10%)</t>
+          <t>CONF_FAIL(got 64.6, need 83), RR_FAIL(got 1.79, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -5757,37 +5785,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TVSSCS.NS</t>
+          <t>INDOCO.NS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>INDOCO</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>68.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>64.83</v>
+        <v>64.52</v>
       </c>
       <c r="F61" t="n">
-        <v>75.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="G61" t="n">
         <v>1.54</v>
       </c>
       <c r="H61" t="n">
-        <v>141.66</v>
+        <v>260.23</v>
       </c>
       <c r="I61" t="n">
-        <v>128.51</v>
+        <v>230.94</v>
       </c>
       <c r="J61" t="n">
-        <v>152.46</v>
+        <v>285.74</v>
       </c>
       <c r="K61" t="n">
-        <v>163.27</v>
+        <v>311.25</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -5803,24 +5831,24 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>9.699999999999999</v>
+        <v>-9.42</v>
       </c>
       <c r="P61" t="n">
-        <v>1.34</v>
+        <v>1.17</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.7%&lt;10%)</t>
+          <t>CONF_FAIL(got 64.5, need 83), TQ_FAIL(got 72.1, need 73), RR_FAIL(got 1.54, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5837,37 +5865,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AEGISVOPAK.NS</t>
+          <t>UFBL.NS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AEGISVOPAK</t>
+          <t>UFBL</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>63.7</v>
+        <v>62.1</v>
       </c>
       <c r="E62" t="n">
-        <v>64.66</v>
+        <v>63.86</v>
       </c>
       <c r="F62" t="n">
-        <v>62.3</v>
+        <v>58.4</v>
       </c>
       <c r="G62" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H62" t="n">
-        <v>283.18</v>
+        <v>755.8</v>
       </c>
       <c r="I62" t="n">
-        <v>240.7</v>
+        <v>642.4299999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>315.04</v>
+        <v>840.83</v>
       </c>
       <c r="K62" t="n">
-        <v>346.9</v>
+        <v>925.86</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -5883,24 +5911,24 @@
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>10</v>
+        <v>-17.6</v>
       </c>
       <c r="P62" t="n">
-        <v>0.84</v>
+        <v>2.76</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 64.7, need 83), TQ_FAIL(got 62.3, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>DE_TOO_HIGH(2.76&gt;1.50)</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5917,37 +5945,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EMBDL.NS</t>
+          <t>THANGAMAYL.NS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>70</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>64.64</v>
+        <v>63.58</v>
       </c>
       <c r="F63" t="n">
-        <v>74.3</v>
+        <v>57.6</v>
       </c>
       <c r="G63" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H63" t="n">
-        <v>66.23999999999999</v>
+        <v>6540.5</v>
       </c>
       <c r="I63" t="n">
-        <v>60.16</v>
+        <v>5591.9</v>
       </c>
       <c r="J63" t="n">
-        <v>72.05</v>
+        <v>7443.64</v>
       </c>
       <c r="K63" t="n">
-        <v>77.86</v>
+        <v>8346.77</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -5963,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>-9.1</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -5975,7 +6003,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 64.6, need 83), RR_FAIL(got 1.79, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 63.6, need 83), TQ_FAIL(got 57.6, need 73), RR_FAIL(got 1.85, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -5997,37 +6025,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>INDOCO.NS</t>
+          <t>PWL.NS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>INDOCO</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>67.90000000000001</v>
+        <v>61.1</v>
       </c>
       <c r="E64" t="n">
-        <v>64.52</v>
+        <v>62.96000000000001</v>
       </c>
       <c r="F64" t="n">
-        <v>72.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="G64" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="H64" t="n">
-        <v>260.23</v>
+        <v>147.43</v>
       </c>
       <c r="I64" t="n">
-        <v>230.94</v>
+        <v>125.32</v>
       </c>
       <c r="J64" t="n">
-        <v>285.74</v>
+        <v>164.68</v>
       </c>
       <c r="K64" t="n">
-        <v>311.25</v>
+        <v>181.94</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -6043,19 +6071,19 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>-9.42</v>
+        <v>-0.48</v>
       </c>
       <c r="P64" t="n">
-        <v>1.17</v>
+        <v>0.23</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 64.5, need 83), TQ_FAIL(got 72.1, need 73), RR_FAIL(got 1.54, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 63.0, need 83), TQ_FAIL(got 55.7, need 73), RR_FAIL(got 1.51, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -6077,37 +6105,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UFBL.NS</t>
+          <t>TCIEXP.NS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>UFBL</t>
+          <t>TCIEXP</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>62.1</v>
+        <v>68.3</v>
       </c>
       <c r="E65" t="n">
-        <v>63.86</v>
+        <v>62.91</v>
       </c>
       <c r="F65" t="n">
-        <v>58.4</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="H65" t="n">
-        <v>755.8</v>
+        <v>559.75</v>
       </c>
       <c r="I65" t="n">
-        <v>642.4299999999999</v>
+        <v>493.02</v>
       </c>
       <c r="J65" t="n">
-        <v>840.83</v>
+        <v>632.13</v>
       </c>
       <c r="K65" t="n">
-        <v>925.86</v>
+        <v>704.51</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -6123,24 +6151,24 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>-17.6</v>
+        <v>10.5</v>
       </c>
       <c r="P65" t="n">
-        <v>2.76</v>
+        <v>0.08</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(2.76&gt;1.50)</t>
+          <t>CONF_FAIL(got 62.9, need 83), TQ_FAIL(got 66.9, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
@@ -6157,37 +6185,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PWL.NS</t>
+          <t>MUTHOOTMF.NS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PWL</t>
+          <t>MUTHOOTMF</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>61.1</v>
+        <v>63.8</v>
       </c>
       <c r="E66" t="n">
-        <v>62.96000000000001</v>
+        <v>62.73</v>
       </c>
       <c r="F66" t="n">
-        <v>55.7</v>
+        <v>67.2</v>
       </c>
       <c r="G66" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H66" t="n">
-        <v>147.43</v>
+        <v>235.26</v>
       </c>
       <c r="I66" t="n">
-        <v>125.32</v>
+        <v>203.97</v>
       </c>
       <c r="J66" t="n">
-        <v>164.68</v>
+        <v>259.46</v>
       </c>
       <c r="K66" t="n">
-        <v>181.94</v>
+        <v>283.66</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -6203,19 +6231,19 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 63.0, need 83), TQ_FAIL(got 55.7, need 73), RR_FAIL(got 1.51, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 62.7, need 83), TQ_FAIL(got 67.2, need 73), RR_FAIL(got 1.47, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -6237,37 +6265,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TCIEXP.NS</t>
+          <t>NUVAMA.NS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TCIEXP</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>68.3</v>
+        <v>62.3</v>
       </c>
       <c r="E67" t="n">
-        <v>62.91</v>
+        <v>62.23999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>66.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>2.07</v>
+        <v>1.43</v>
       </c>
       <c r="H67" t="n">
-        <v>559.75</v>
+        <v>1977.6</v>
       </c>
       <c r="I67" t="n">
-        <v>493.02</v>
+        <v>1769.75</v>
       </c>
       <c r="J67" t="n">
-        <v>632.13</v>
+        <v>2126.06</v>
       </c>
       <c r="K67" t="n">
-        <v>704.51</v>
+        <v>2289.38</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -6283,24 +6311,24 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>10.5</v>
+        <v>27.4</v>
       </c>
       <c r="P67" t="n">
-        <v>0.08</v>
+        <v>2.82</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>UPTREND</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 62.9, need 83), TQ_FAIL(got 66.9, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>DE_TOO_HIGH(2.82&gt;1.50)</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>DE_TOO_HIGH</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
@@ -6317,37 +6345,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NUVAMA.NS</t>
+          <t>ITDC.NS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>ITDC</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>62.3</v>
+        <v>62.6</v>
       </c>
       <c r="E68" t="n">
-        <v>62.23999999999999</v>
+        <v>62.08</v>
       </c>
       <c r="F68" t="n">
-        <v>65.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="G68" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H68" t="n">
-        <v>1977.6</v>
+        <v>716.8</v>
       </c>
       <c r="I68" t="n">
-        <v>1769.75</v>
+        <v>609.28</v>
       </c>
       <c r="J68" t="n">
-        <v>2126.06</v>
+        <v>797.4400000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>2289.38</v>
+        <v>878.08</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -6363,24 +6391,24 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>27.4</v>
+        <v>21.1</v>
       </c>
       <c r="P68" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(2.82&gt;1.50)</t>
+          <t>CONF_FAIL(got 62.1, need 83), TQ_FAIL(got 63.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
@@ -6397,41 +6425,41 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ITDC.NS</t>
+          <t>BFINVEST.NS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ITDC</t>
+          <t>BFINVEST</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>62.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>62.08</v>
+        <v>61.55</v>
       </c>
       <c r="F69" t="n">
-        <v>63.4</v>
+        <v>75.7</v>
       </c>
       <c r="G69" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="H69" t="n">
-        <v>716.8</v>
+        <v>487.25</v>
       </c>
       <c r="I69" t="n">
-        <v>609.28</v>
+        <v>433.21</v>
       </c>
       <c r="J69" t="n">
-        <v>797.4400000000001</v>
+        <v>525.85</v>
       </c>
       <c r="K69" t="n">
-        <v>878.08</v>
+        <v>568.3099999999999</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6443,24 +6471,24 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>21.1</v>
+        <v>3.65</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 62.1, need 83), TQ_FAIL(got 63.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>ROE_TOO_LOW(3.6%&lt;10%)</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
@@ -6477,41 +6505,41 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BFINVEST.NS</t>
+          <t>DIACABS.NS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BFINVEST</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>65.59999999999999</v>
+        <v>61.3</v>
       </c>
       <c r="E70" t="n">
-        <v>61.55</v>
+        <v>61.22499999999999</v>
       </c>
       <c r="F70" t="n">
-        <v>75.7</v>
+        <v>59.3</v>
       </c>
       <c r="G70" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="H70" t="n">
-        <v>487.25</v>
+        <v>229.01</v>
       </c>
       <c r="I70" t="n">
-        <v>433.21</v>
+        <v>196.51</v>
       </c>
       <c r="J70" t="n">
-        <v>525.85</v>
+        <v>255.34</v>
       </c>
       <c r="K70" t="n">
-        <v>568.3099999999999</v>
+        <v>281.67</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6523,24 +6551,24 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(3.6%&lt;10%)</t>
+          <t>CONF_FAIL(got 61.2, need 83), TQ_FAIL(got 59.3, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
@@ -6557,37 +6585,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MUTHOOTMF.NS</t>
+          <t>GEMAROMA.NS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MUTHOOTMF</t>
+          <t>GEMAROMA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>63.5</v>
+        <v>62.4</v>
       </c>
       <c r="E71" t="n">
-        <v>61.48999999999999</v>
+        <v>59.76000000000001</v>
       </c>
       <c r="F71" t="n">
-        <v>67.2</v>
+        <v>60.7</v>
       </c>
       <c r="G71" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="H71" t="n">
-        <v>235.26</v>
+        <v>206.54</v>
       </c>
       <c r="I71" t="n">
-        <v>203.97</v>
+        <v>179.09</v>
       </c>
       <c r="J71" t="n">
-        <v>259.46</v>
+        <v>230.93</v>
       </c>
       <c r="K71" t="n">
-        <v>283.66</v>
+        <v>255.32</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -6603,19 +6631,19 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>6.21</v>
+        <v>0.39</v>
       </c>
       <c r="P71" t="n">
-        <v>3.4</v>
+        <v>0.34</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(6.2%&lt;10%)</t>
+          <t>ROE_TOO_LOW(0.4%&lt;10%)</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -6637,37 +6665,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEMAROMA.NS</t>
+          <t>RAMRAT.NS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>GEMAROMA</t>
+          <t>RAMRAT</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>62.4</v>
+        <v>65.8</v>
       </c>
       <c r="E72" t="n">
-        <v>59.76000000000001</v>
+        <v>57.62</v>
       </c>
       <c r="F72" t="n">
-        <v>60.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="H72" t="n">
-        <v>206.54</v>
+        <v>419.05</v>
       </c>
       <c r="I72" t="n">
-        <v>179.09</v>
+        <v>388.65</v>
       </c>
       <c r="J72" t="n">
-        <v>230.93</v>
+        <v>450.39</v>
       </c>
       <c r="K72" t="n">
-        <v>255.32</v>
+        <v>481.73</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -6683,10 +6711,10 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>0.39</v>
+        <v>20.6</v>
       </c>
       <c r="P72" t="n">
-        <v>0.34</v>
+        <v>1.15</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -6695,12 +6723,12 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(0.4%&lt;10%)</t>
+          <t>CONF_FAIL(got 57.6, need 83), TQ_FAIL(got 72.6, need 73), RR_FAIL(got 1.83, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -6717,41 +6745,41 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RAMRAT.NS</t>
+          <t>SYRMA.NS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RAMRAT</t>
+          <t>SYRMA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>65.8</v>
+        <v>62</v>
       </c>
       <c r="E73" t="n">
-        <v>57.62</v>
+        <v>57.31</v>
       </c>
       <c r="F73" t="n">
-        <v>72.59999999999999</v>
+        <v>58.5</v>
       </c>
       <c r="G73" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
-        <v>419.05</v>
+        <v>1451.9</v>
       </c>
       <c r="I73" t="n">
-        <v>388.65</v>
+        <v>1325.54</v>
       </c>
       <c r="J73" t="n">
-        <v>450.39</v>
+        <v>1584.66</v>
       </c>
       <c r="K73" t="n">
-        <v>481.73</v>
+        <v>1717.43</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6763,10 +6791,10 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>20.6</v>
+        <v>13.9</v>
       </c>
       <c r="P73" t="n">
-        <v>1.15</v>
+        <v>0.13</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -6775,7 +6803,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 57.6, need 83), TQ_FAIL(got 72.6, need 73), RR_FAIL(got 1.83, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 57.3, need 83), TQ_FAIL(got 58.5, need 73), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -6797,41 +6825,41 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SYRMA.NS</t>
+          <t>DLF.NS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SYRMA</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>62</v>
+        <v>62.4</v>
       </c>
       <c r="E74" t="n">
-        <v>57.375</v>
+        <v>57.14</v>
       </c>
       <c r="F74" t="n">
-        <v>58.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="H74" t="n">
-        <v>1451.9</v>
+        <v>685.75</v>
       </c>
       <c r="I74" t="n">
-        <v>1325.54</v>
+        <v>611.9400000000001</v>
       </c>
       <c r="J74" t="n">
-        <v>1584.66</v>
+        <v>738.47</v>
       </c>
       <c r="K74" t="n">
-        <v>1717.43</v>
+        <v>796.46</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6843,24 +6871,24 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>13.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="P74" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 57.4, need 83), TQ_FAIL(got 58.5, need 73), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>OTHER</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
@@ -6877,41 +6905,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DLF.NS</t>
+          <t>LLOYDSENT.NS</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>62.4</v>
+        <v>63.8</v>
       </c>
       <c r="E75" t="n">
-        <v>57.14</v>
+        <v>56.22</v>
       </c>
       <c r="F75" t="n">
-        <v>73.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="H75" t="n">
-        <v>685.75</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>611.9400000000001</v>
+        <v>69.75</v>
       </c>
       <c r="J75" t="n">
-        <v>738.47</v>
+        <v>85.94</v>
       </c>
       <c r="K75" t="n">
-        <v>796.46</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6923,24 +6951,24 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>9.619999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="P75" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>SETUP_EDGE_SKIP(REGIME_CHOP_NO_BREAKOUT(TRANSITION/OTHER))</t>
+          <t>ROE_TOO_LOW(0.3%&lt;10%)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ROE_TOO_LOW</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -6966,10 +6994,10 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>62.4</v>
+        <v>62.7</v>
       </c>
       <c r="E76" t="n">
-        <v>56.28</v>
+        <v>55.96</v>
       </c>
       <c r="F76" t="n">
         <v>75.7</v>
@@ -7006,7 +7034,7 @@
         <v>13.8</v>
       </c>
       <c r="P76" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -7015,7 +7043,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 56.3, need 83), RR_FAIL(got 1.35, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 56.0, need 83), RR_FAIL(got 1.35, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -7037,37 +7065,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CYIENTDLM.NS</t>
+          <t>SOTL.NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>59.1</v>
+        <v>61.3</v>
       </c>
       <c r="E77" t="n">
-        <v>55.31</v>
+        <v>55.235</v>
       </c>
       <c r="F77" t="n">
-        <v>63.4</v>
+        <v>67.2</v>
       </c>
       <c r="G77" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="H77" t="n">
-        <v>545.65</v>
+        <v>607.45</v>
       </c>
       <c r="I77" t="n">
-        <v>463.8</v>
+        <v>516.33</v>
       </c>
       <c r="J77" t="n">
-        <v>607.04</v>
+        <v>685.8</v>
       </c>
       <c r="K77" t="n">
-        <v>668.42</v>
+        <v>764.15</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -7083,24 +7111,24 @@
         <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>7.49</v>
+        <v>10.5</v>
       </c>
       <c r="P77" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(7.5%&lt;10%)</t>
+          <t>CONF_FAIL(got 55.2, need 83), TQ_FAIL(got 67.2, need 73), RR_FAIL(got 1.65, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -7117,37 +7145,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>DIACABS.NS</t>
+          <t>CYIENTDLM.NS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>58.3</v>
+        <v>59.1</v>
       </c>
       <c r="E78" t="n">
-        <v>55.035</v>
+        <v>54.95</v>
       </c>
       <c r="F78" t="n">
-        <v>59.3</v>
+        <v>63.4</v>
       </c>
       <c r="G78" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="H78" t="n">
-        <v>229.01</v>
+        <v>545.65</v>
       </c>
       <c r="I78" t="n">
-        <v>196.51</v>
+        <v>463.8</v>
       </c>
       <c r="J78" t="n">
-        <v>255.34</v>
+        <v>607.04</v>
       </c>
       <c r="K78" t="n">
-        <v>281.67</v>
+        <v>668.42</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -7163,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>7.49</v>
       </c>
       <c r="P78" t="n">
         <v>0</v>
@@ -7175,7 +7203,7 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 55.0, need 83), TQ_FAIL(got 59.3, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 55.0, need 83), TQ_FAIL(got 63.4, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -7255,7 +7283,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 54.6, need 83), TQ_FAIL(got 53.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 54.6, need 83), TQ_FAIL(got 53.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -7277,37 +7305,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SOTL.NS</t>
+          <t>OMAXE.NS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>OMAXE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>61.3</v>
+        <v>62.6</v>
       </c>
       <c r="E80" t="n">
-        <v>54.36</v>
+        <v>52.24</v>
       </c>
       <c r="F80" t="n">
-        <v>67.2</v>
+        <v>69.5</v>
       </c>
       <c r="G80" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="H80" t="n">
-        <v>607.45</v>
+        <v>90.48</v>
       </c>
       <c r="I80" t="n">
-        <v>516.33</v>
+        <v>76.91</v>
       </c>
       <c r="J80" t="n">
-        <v>685.8</v>
+        <v>103.86</v>
       </c>
       <c r="K80" t="n">
-        <v>764.15</v>
+        <v>117.24</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -7323,19 +7351,19 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 54.4, need 83), TQ_FAIL(got 67.2, need 73), RR_FAIL(got 1.65, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 52.2, need 83), TQ_FAIL(got 69.5, need 73), RR_FAIL(got 1.90, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -7357,37 +7385,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OMAXE.NS</t>
+          <t>KAMDHENU.NS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OMAXE</t>
+          <t>KAMDHENU</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>62.6</v>
+        <v>57</v>
       </c>
       <c r="E81" t="n">
-        <v>51.49</v>
+        <v>49.82</v>
       </c>
       <c r="F81" t="n">
-        <v>69.5</v>
+        <v>68.3</v>
       </c>
       <c r="G81" t="n">
-        <v>1.9</v>
+        <v>1.36</v>
       </c>
       <c r="H81" t="n">
-        <v>90.48</v>
+        <v>33.02</v>
       </c>
       <c r="I81" t="n">
-        <v>76.91</v>
+        <v>28.07</v>
       </c>
       <c r="J81" t="n">
-        <v>103.86</v>
+        <v>36.74</v>
       </c>
       <c r="K81" t="n">
-        <v>117.24</v>
+        <v>40.45</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -7403,19 +7431,19 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 51.5, need 83), TQ_FAIL(got 69.5, need 73), RR_FAIL(got 1.90, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 49.8, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.36, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -7437,41 +7465,41 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GRANULES.NS</t>
+          <t>PHOENIXLTD.NS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>57</v>
+        <v>56.1</v>
       </c>
       <c r="E82" t="n">
-        <v>51.215</v>
+        <v>49.67</v>
       </c>
       <c r="F82" t="n">
-        <v>64.90000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G82" t="n">
         <v>1.43</v>
       </c>
       <c r="H82" t="n">
-        <v>889.85</v>
+        <v>2138.9</v>
       </c>
       <c r="I82" t="n">
-        <v>801.74</v>
+        <v>1924.22</v>
       </c>
       <c r="J82" t="n">
-        <v>952.79</v>
+        <v>2292.24</v>
       </c>
       <c r="K82" t="n">
-        <v>1022.02</v>
+        <v>2460.92</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7483,19 +7511,19 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 51.2, need 83), TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.43, need 2.0)</t>
+          <t>CONF_FAIL(got 49.7, need 83), TQ_FAIL(got 64.1, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -7517,41 +7545,41 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KAMDHENU.NS</t>
+          <t>PRESTIGE.NS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KAMDHENU</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>57</v>
+        <v>54.6</v>
       </c>
       <c r="E83" t="n">
-        <v>48.82</v>
+        <v>48.49</v>
       </c>
       <c r="F83" t="n">
-        <v>68.3</v>
+        <v>63</v>
       </c>
       <c r="G83" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="H83" t="n">
-        <v>33.02</v>
+        <v>1733.2</v>
       </c>
       <c r="I83" t="n">
-        <v>28.07</v>
+        <v>1547</v>
       </c>
       <c r="J83" t="n">
-        <v>36.74</v>
+        <v>1866.2</v>
       </c>
       <c r="K83" t="n">
-        <v>40.45</v>
+        <v>2012.5</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7563,24 +7591,24 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>14.7</v>
+        <v>7.54</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 48.8, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.36, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 48.5, need 83), TQ_FAIL(got 63.0, need 73), RR_FAIL(got 1.43, need 2.0)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -7597,41 +7625,41 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PRESTIGE.NS</t>
+          <t>INDSWFTLAB.NS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>INDSWFTLAB</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>54.6</v>
+        <v>52.8</v>
       </c>
       <c r="E84" t="n">
-        <v>47.99</v>
+        <v>48.245</v>
       </c>
       <c r="F84" t="n">
-        <v>63</v>
+        <v>55.1</v>
       </c>
       <c r="G84" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H84" t="n">
-        <v>1733.2</v>
+        <v>246.44</v>
       </c>
       <c r="I84" t="n">
-        <v>1547</v>
+        <v>209.47</v>
       </c>
       <c r="J84" t="n">
-        <v>1866.2</v>
+        <v>274.13</v>
       </c>
       <c r="K84" t="n">
-        <v>2012.5</v>
+        <v>301.9</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7643,19 +7671,19 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>7.54</v>
+        <v>3.87</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 48.0, need 83), TQ_FAIL(got 63.0, need 73), RR_FAIL(got 1.43, need 2.0)</t>
+          <t>CONF_FAIL(got 48.2, need 83), TQ_FAIL(got 55.1, need 73), RR_FAIL(got 1.44, need 2.0)</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -7837,41 +7865,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STARHEALTH.NS</t>
+          <t>ARKADE.NS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>STARHEALTH</t>
+          <t>ARKADE</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>56.7</v>
+        <v>60.4</v>
       </c>
       <c r="E87" t="n">
-        <v>47.38</v>
+        <v>47.37</v>
       </c>
       <c r="F87" t="n">
-        <v>59.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="H87" t="n">
-        <v>603.25</v>
+        <v>132.56</v>
       </c>
       <c r="I87" t="n">
-        <v>569.4400000000001</v>
+        <v>121.42</v>
       </c>
       <c r="J87" t="n">
-        <v>638.0599999999999</v>
+        <v>142.89</v>
       </c>
       <c r="K87" t="n">
-        <v>672.87</v>
+        <v>153.22</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7883,24 +7911,24 @@
         <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 47.4, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.91, need 2.0)</t>
+          <t>CONF_FAIL(got 47.4, need 83), RR_FAIL(got 1.67, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>TQ_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -7917,37 +7945,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ARKADE.NS</t>
+          <t>FILATEX.NS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ARKADE</t>
+          <t>FILATEX</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>60.4</v>
+        <v>55.5</v>
       </c>
       <c r="E88" t="n">
-        <v>47.37</v>
+        <v>46.75</v>
       </c>
       <c r="F88" t="n">
-        <v>75.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="G88" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="H88" t="n">
-        <v>132.56</v>
+        <v>62.25</v>
       </c>
       <c r="I88" t="n">
-        <v>121.42</v>
+        <v>53.18</v>
       </c>
       <c r="J88" t="n">
-        <v>142.89</v>
+        <v>68.73</v>
       </c>
       <c r="K88" t="n">
-        <v>153.22</v>
+        <v>75.86</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -7963,7 +7991,7 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>20.8</v>
+        <v>12.9</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
@@ -7975,7 +8003,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 47.4, need 83), RR_FAIL(got 1.67, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 46.8, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -7997,41 +8025,41 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>INDSWFTLAB.NS</t>
+          <t>TBZ.NS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>INDSWFTLAB</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>52.8</v>
+        <v>51.5</v>
       </c>
       <c r="E89" t="n">
-        <v>47.37</v>
+        <v>46.665</v>
       </c>
       <c r="F89" t="n">
-        <v>55.1</v>
+        <v>50.3</v>
       </c>
       <c r="G89" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="H89" t="n">
-        <v>246.44</v>
+        <v>228.34</v>
       </c>
       <c r="I89" t="n">
-        <v>209.47</v>
+        <v>194.09</v>
       </c>
       <c r="J89" t="n">
-        <v>274.13</v>
+        <v>257.01</v>
       </c>
       <c r="K89" t="n">
-        <v>301.9</v>
+        <v>285.68</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -8043,24 +8071,24 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>3.87</v>
+        <v>27.1</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH</t>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 47.4, need 83), TQ_FAIL(got 55.1, need 73), RR_FAIL(got 1.44, need 2.0)</t>
+          <t>CONF_FAIL(got 46.7, need 83), TQ_FAIL(got 50.3, need 73), RR_FAIL(got 1.61, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>TQ_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
@@ -8135,7 +8163,7 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 46.6, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 46.6, need 83), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -8157,41 +8185,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UNICHEMLAB.NS</t>
+          <t>MMFL.NS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UNICHEMLAB</t>
+          <t>MMFL</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>50.8</v>
+        <v>54.7</v>
       </c>
       <c r="E91" t="n">
-        <v>46.19</v>
+        <v>46.53</v>
       </c>
       <c r="F91" t="n">
-        <v>48.3</v>
+        <v>65.5</v>
       </c>
       <c r="G91" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="H91" t="n">
-        <v>638.75</v>
+        <v>523.4</v>
       </c>
       <c r="I91" t="n">
-        <v>542.9400000000001</v>
+        <v>454.5</v>
       </c>
       <c r="J91" t="n">
-        <v>715.24</v>
+        <v>572.61</v>
       </c>
       <c r="K91" t="n">
-        <v>791.72</v>
+        <v>626.75</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8203,24 +8231,24 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>3.17</v>
+        <v>10.5</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 46.2, need 83), TQ_FAIL(got 48.3, need 73), RR_FAIL(got 1.53, need 2.0), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 46.5, need 83), TQ_FAIL(got 65.5, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>TQ_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
@@ -8237,41 +8265,41 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FILATEX.NS</t>
+          <t>STARHEALTH.NS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FILATEX</t>
+          <t>STARHEALTH</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>55.5</v>
+        <v>56.7</v>
       </c>
       <c r="E92" t="n">
-        <v>45.875</v>
+        <v>46.38</v>
       </c>
       <c r="F92" t="n">
-        <v>68.3</v>
+        <v>59.4</v>
       </c>
       <c r="G92" t="n">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="H92" t="n">
-        <v>62.25</v>
+        <v>603.25</v>
       </c>
       <c r="I92" t="n">
-        <v>53.18</v>
+        <v>569.4400000000001</v>
       </c>
       <c r="J92" t="n">
-        <v>68.73</v>
+        <v>638.0599999999999</v>
       </c>
       <c r="K92" t="n">
-        <v>75.86</v>
+        <v>672.87</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8283,24 +8311,24 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 45.9, need 83), TQ_FAIL(got 68.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 46.4, need 83), TQ_FAIL(got 59.4, need 73), RR_FAIL(got 1.91, need 2.0)</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -8375,7 +8403,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 45.8, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 45.8, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -8397,37 +8425,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TBZ.NS</t>
+          <t>NORTHARC.NS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>NORTHARC</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>51.5</v>
+        <v>58.2</v>
       </c>
       <c r="E94" t="n">
-        <v>45.29</v>
+        <v>45.59</v>
       </c>
       <c r="F94" t="n">
-        <v>50.3</v>
+        <v>75.5</v>
       </c>
       <c r="G94" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="H94" t="n">
-        <v>228.34</v>
+        <v>325.3</v>
       </c>
       <c r="I94" t="n">
-        <v>194.09</v>
+        <v>288.45</v>
       </c>
       <c r="J94" t="n">
-        <v>257.01</v>
+        <v>353.88</v>
       </c>
       <c r="K94" t="n">
-        <v>285.68</v>
+        <v>382.47</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -8443,19 +8471,19 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>27.1</v>
+        <v>11.1</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 45.3, need 83), TQ_FAIL(got 50.3, need 73), RR_FAIL(got 1.61, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 45.6, need 83), RR_FAIL(got 1.47, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -8477,37 +8505,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IKIO.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IKIO</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
       <c r="E95" t="n">
-        <v>45.21</v>
+        <v>45.22</v>
       </c>
       <c r="F95" t="n">
-        <v>50.7</v>
+        <v>58.1</v>
       </c>
       <c r="G95" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="H95" t="n">
-        <v>210.75</v>
+        <v>1220.75</v>
       </c>
       <c r="I95" t="n">
-        <v>179.14</v>
+        <v>1059.03</v>
       </c>
       <c r="J95" t="n">
-        <v>242.42</v>
+        <v>1336.27</v>
       </c>
       <c r="K95" t="n">
-        <v>274.08</v>
+        <v>1463.33</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -8523,19 +8551,19 @@
         <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>6.51</v>
+        <v>15.8</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 45.2, need 83), TQ_FAIL(got 50.7, need 73), RR_FAIL(got 1.95, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 45.2, need 83), TQ_FAIL(got 58.1, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -8557,37 +8585,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NORTHARC.NS</t>
+          <t>VAIBHAVGBL.NS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>NORTHARC</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="E96" t="n">
-        <v>45.18</v>
+        <v>45.1</v>
       </c>
       <c r="F96" t="n">
-        <v>75.5</v>
+        <v>75.3</v>
       </c>
       <c r="G96" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="H96" t="n">
-        <v>325.3</v>
+        <v>261.36</v>
       </c>
       <c r="I96" t="n">
-        <v>288.45</v>
+        <v>227.8</v>
       </c>
       <c r="J96" t="n">
-        <v>353.88</v>
+        <v>285.33</v>
       </c>
       <c r="K96" t="n">
-        <v>382.47</v>
+        <v>311.7</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -8603,10 +8631,10 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="P96" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
@@ -8615,12 +8643,12 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH(3.14&gt;1.50)</t>
+          <t>CONF_FAIL(got 45.1, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>DE_TOO_HIGH</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -8637,37 +8665,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>57.7</v>
+        <v>54.3</v>
       </c>
       <c r="E97" t="n">
-        <v>45.1</v>
+        <v>43.935</v>
       </c>
       <c r="F97" t="n">
-        <v>75.3</v>
+        <v>67.3</v>
       </c>
       <c r="G97" t="n">
         <v>1.43</v>
       </c>
       <c r="H97" t="n">
-        <v>261.36</v>
+        <v>244.75</v>
       </c>
       <c r="I97" t="n">
-        <v>227.8</v>
+        <v>211.55</v>
       </c>
       <c r="J97" t="n">
-        <v>285.33</v>
+        <v>269.44</v>
       </c>
       <c r="K97" t="n">
-        <v>311.7</v>
+        <v>294.55</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -8683,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>17.8</v>
+        <v>2.95</v>
       </c>
       <c r="P97" t="n">
         <v>0</v>
@@ -8695,7 +8723,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 45.1, need 83), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 43.9, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -8717,37 +8745,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ANANDRATHI.NS</t>
+          <t>BAJAJCON.NS</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>BAJAJCON</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>55.9</v>
+        <v>55.2</v>
       </c>
       <c r="E98" t="n">
-        <v>43.775</v>
+        <v>43.65</v>
       </c>
       <c r="F98" t="n">
-        <v>73.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="G98" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H98" t="n">
-        <v>2146.8</v>
+        <v>670.25</v>
       </c>
       <c r="I98" t="n">
-        <v>1906.75</v>
+        <v>586.62</v>
       </c>
       <c r="J98" t="n">
-        <v>2318.26</v>
+        <v>729.98</v>
       </c>
       <c r="K98" t="n">
-        <v>2506.88</v>
+        <v>795.7</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -8763,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>47.3</v>
+        <v>25.3</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
@@ -8775,7 +8803,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 43.8, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 43.6, need 83), TQ_FAIL(got 69.8, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -8809,7 +8837,7 @@
         <v>55.8</v>
       </c>
       <c r="E99" t="n">
-        <v>43.17</v>
+        <v>43.12</v>
       </c>
       <c r="F99" t="n">
         <v>72.8</v>
@@ -8855,7 +8883,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 43.2, need 83), TQ_FAIL(got 72.8, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
+          <t>CONF_FAIL(got 43.1, need 83), TQ_FAIL(got 72.8, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -8877,37 +8905,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>ANANDRATHI.NS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>54.3</v>
+        <v>55.9</v>
       </c>
       <c r="E100" t="n">
-        <v>43.06</v>
+        <v>42.875</v>
       </c>
       <c r="F100" t="n">
-        <v>67.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G100" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H100" t="n">
-        <v>244.75</v>
+        <v>2146.8</v>
       </c>
       <c r="I100" t="n">
-        <v>211.55</v>
+        <v>1906.75</v>
       </c>
       <c r="J100" t="n">
-        <v>269.44</v>
+        <v>2318.26</v>
       </c>
       <c r="K100" t="n">
-        <v>294.55</v>
+        <v>2506.88</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -8923,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>2.95</v>
+        <v>47.3</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -8935,7 +8963,7 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 43.1, need 83), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 42.9, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -8957,37 +8985,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STALLION.NS</t>
+          <t>IKIO.NS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>STALLION</t>
+          <t>IKIO</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>54.2</v>
+        <v>51.1</v>
       </c>
       <c r="E101" t="n">
-        <v>41.03</v>
+        <v>41.46</v>
       </c>
       <c r="F101" t="n">
-        <v>67.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="G101" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="H101" t="n">
-        <v>204.88</v>
+        <v>210.75</v>
       </c>
       <c r="I101" t="n">
-        <v>176.77</v>
+        <v>179.14</v>
       </c>
       <c r="J101" t="n">
-        <v>227.52</v>
+        <v>242.42</v>
       </c>
       <c r="K101" t="n">
-        <v>250.17</v>
+        <v>274.08</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -9003,24 +9031,24 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>8.93</v>
+        <v>6.51</v>
       </c>
       <c r="P101" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(8.9%&lt;10%)</t>
+          <t>CONF_FAIL(got 41.5, need 83), TQ_FAIL(got 50.7, need 73), RR_FAIL(got 1.95, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
@@ -9046,10 +9074,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>53.5</v>
+        <v>53.9</v>
       </c>
       <c r="E102" t="n">
-        <v>39.99</v>
+        <v>40.64</v>
       </c>
       <c r="F102" t="n">
         <v>70.5</v>
@@ -9086,7 +9114,7 @@
         <v>-8.26</v>
       </c>
       <c r="P102" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -9095,7 +9123,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 40.0, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 40.6, need 83), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -9117,37 +9145,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AEQUS.NS</t>
+          <t>STALLION.NS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>STALLION</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="E103" t="n">
-        <v>34.64</v>
+        <v>38.53</v>
       </c>
       <c r="F103" t="n">
-        <v>58.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G103" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="H103" t="n">
-        <v>248.78</v>
+        <v>204.88</v>
       </c>
       <c r="I103" t="n">
-        <v>221.89</v>
+        <v>176.77</v>
       </c>
       <c r="J103" t="n">
-        <v>281.26</v>
+        <v>227.52</v>
       </c>
       <c r="K103" t="n">
-        <v>313.73</v>
+        <v>250.17</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -9163,19 +9191,19 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>-9.99</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 34.6, need 83), TQ_FAIL(got 58.9, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 38.5, need 83), TQ_FAIL(got 67.9, need 73), RR_FAIL(got 1.54, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -9197,37 +9225,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AKUMS.NS</t>
+          <t>AEQUS.NS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>50.2</v>
+        <v>52.7</v>
       </c>
       <c r="E104" t="n">
-        <v>34.35</v>
+        <v>34.74</v>
       </c>
       <c r="F104" t="n">
-        <v>70.40000000000001</v>
+        <v>58.9</v>
       </c>
       <c r="G104" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="H104" t="n">
-        <v>701.95</v>
+        <v>248.78</v>
       </c>
       <c r="I104" t="n">
-        <v>624.41</v>
+        <v>221.89</v>
       </c>
       <c r="J104" t="n">
-        <v>757.34</v>
+        <v>281.26</v>
       </c>
       <c r="K104" t="n">
-        <v>818.26</v>
+        <v>313.73</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -9243,19 +9271,19 @@
         <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>8.449999999999999</v>
+        <v>-9.99</v>
       </c>
       <c r="P104" t="n">
         <v>0</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 34.4, need 83), TQ_FAIL(got 70.4, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 34.7, need 83), TQ_FAIL(got 58.9, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -9289,7 +9317,7 @@
         <v>50.7</v>
       </c>
       <c r="E105" t="n">
-        <v>33.965</v>
+        <v>34.53</v>
       </c>
       <c r="F105" t="n">
         <v>70.90000000000001</v>
@@ -9335,7 +9363,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 34.0, need 83), TQ_FAIL(got 70.9, need 73), RR_FAIL(got 1.45, need 2.0), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 34.5, need 83), TQ_FAIL(got 70.9, need 73), RR_FAIL(got 1.45, need 2.0), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -9357,37 +9385,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>UJJIVANSFB.NS</t>
+          <t>AKUMS.NS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>50.7</v>
+        <v>50.2</v>
       </c>
       <c r="E106" t="n">
-        <v>33.15</v>
+        <v>34.41</v>
       </c>
       <c r="F106" t="n">
-        <v>73.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G106" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="H106" t="n">
-        <v>65.27</v>
+        <v>701.95</v>
       </c>
       <c r="I106" t="n">
-        <v>57.44</v>
+        <v>624.41</v>
       </c>
       <c r="J106" t="n">
-        <v>70.86</v>
+        <v>757.34</v>
       </c>
       <c r="K106" t="n">
-        <v>77.01000000000001</v>
+        <v>818.26</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -9403,19 +9431,19 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 33.1, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 34.4, need 83), TQ_FAIL(got 70.4, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -9437,41 +9465,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GRAVITA.NS</t>
+          <t>UNICHEMLAB.NS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>GRAVITA</t>
+          <t>UNICHEMLAB</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>48.5</v>
+        <v>44.4</v>
       </c>
       <c r="E107" t="n">
-        <v>33.04</v>
+        <v>33.32</v>
       </c>
       <c r="F107" t="n">
-        <v>66.2</v>
+        <v>48.3</v>
       </c>
       <c r="G107" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="H107" t="n">
-        <v>1854.6</v>
+        <v>638.75</v>
       </c>
       <c r="I107" t="n">
-        <v>1622.88</v>
+        <v>542.9400000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>2020.12</v>
+        <v>715.24</v>
       </c>
       <c r="K107" t="n">
-        <v>2202.18</v>
+        <v>791.72</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -9483,24 +9511,24 @@
         <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>16.8</v>
+        <v>3.17</v>
       </c>
       <c r="P107" t="n">
         <v>0</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 33.0, need 83), TQ_FAIL(got 66.2, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 33.3, need 83), TQ_FAIL(got 48.3, need 73), RR_FAIL(got 1.53, need 2.0), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>SECTOR_RANK_TOO_LOW</t>
+          <t>TQ_TOO_LOW</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -9517,37 +9545,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SIGMAADV.NS</t>
+          <t>UJJIVANSFB.NS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SIGMAADV</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>49.6</v>
+        <v>50.7</v>
       </c>
       <c r="E108" t="n">
-        <v>32.93</v>
+        <v>33.15</v>
       </c>
       <c r="F108" t="n">
-        <v>55.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="G108" t="n">
-        <v>2.01</v>
+        <v>1.44</v>
       </c>
       <c r="H108" t="n">
-        <v>582.65</v>
+        <v>65.27</v>
       </c>
       <c r="I108" t="n">
-        <v>513.42</v>
+        <v>57.44</v>
       </c>
       <c r="J108" t="n">
-        <v>655.64</v>
+        <v>70.86</v>
       </c>
       <c r="K108" t="n">
-        <v>728.64</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -9563,7 +9591,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>90.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -9575,7 +9603,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 32.9, need 83), TQ_FAIL(got 55.7, need 73), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 33.1, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -9597,37 +9625,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>MMFL.NS</t>
+          <t>GRAVITA.NS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MMFL</t>
+          <t>GRAVITA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E109" t="n">
-        <v>32.66</v>
+        <v>33.04</v>
       </c>
       <c r="F109" t="n">
-        <v>65.5</v>
+        <v>66.2</v>
       </c>
       <c r="G109" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="H109" t="n">
-        <v>523.4</v>
+        <v>1854.6</v>
       </c>
       <c r="I109" t="n">
-        <v>454.5</v>
+        <v>1622.88</v>
       </c>
       <c r="J109" t="n">
-        <v>572.61</v>
+        <v>2020.12</v>
       </c>
       <c r="K109" t="n">
-        <v>626.75</v>
+        <v>2202.18</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -9643,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="P109" t="n">
         <v>0</v>
@@ -9655,7 +9683,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 32.7, need 83), TQ_FAIL(got 65.5, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 33.0, need 83), TQ_FAIL(got 66.2, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -9677,37 +9705,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LODHA.NS</t>
+          <t>SIGMAADV.NS</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>SIGMAADV</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>46.1</v>
+        <v>49.6</v>
       </c>
       <c r="E110" t="n">
-        <v>32.35</v>
+        <v>32.93</v>
       </c>
       <c r="F110" t="n">
-        <v>58.1</v>
+        <v>55.7</v>
       </c>
       <c r="G110" t="n">
-        <v>1.45</v>
+        <v>2.01</v>
       </c>
       <c r="H110" t="n">
-        <v>1220.75</v>
+        <v>582.65</v>
       </c>
       <c r="I110" t="n">
-        <v>1059.03</v>
+        <v>513.42</v>
       </c>
       <c r="J110" t="n">
-        <v>1336.27</v>
+        <v>655.64</v>
       </c>
       <c r="K110" t="n">
-        <v>1463.33</v>
+        <v>728.64</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -9723,19 +9751,19 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>15.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P110" t="n">
         <v>0</v>
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 32.4, need 83), TQ_FAIL(got 58.1, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 32.9, need 83), TQ_FAIL(got 55.7, need 73), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -9757,37 +9785,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ANANTRAJ.NS</t>
+          <t>SUMEETINDS.NS</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ANANTRAJ</t>
+          <t>SUMEETINDS</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="E111" t="n">
-        <v>32.31</v>
+        <v>32.39</v>
       </c>
       <c r="F111" t="n">
-        <v>78</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G111" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H111" t="n">
-        <v>585.85</v>
+        <v>31.72</v>
       </c>
       <c r="I111" t="n">
-        <v>521.26</v>
+        <v>27.8</v>
       </c>
       <c r="J111" t="n">
-        <v>631.98</v>
+        <v>34.52</v>
       </c>
       <c r="K111" t="n">
-        <v>682.74</v>
+        <v>37.6</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -9803,19 +9831,19 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>11.2</v>
+        <v>14.7</v>
       </c>
       <c r="P111" t="n">
         <v>0</v>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 32.3, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 32.4, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -9837,37 +9865,37 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SUDARSCHEM.NS</t>
+          <t>ANANTRAJ.NS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>ANANTRAJ</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="E112" t="n">
-        <v>32.15</v>
+        <v>32.31</v>
       </c>
       <c r="F112" t="n">
-        <v>75.3</v>
+        <v>78</v>
       </c>
       <c r="G112" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H112" t="n">
-        <v>999.25</v>
+        <v>585.85</v>
       </c>
       <c r="I112" t="n">
-        <v>885.64</v>
+        <v>521.26</v>
       </c>
       <c r="J112" t="n">
-        <v>1080.4</v>
+        <v>631.98</v>
       </c>
       <c r="K112" t="n">
-        <v>1169.66</v>
+        <v>682.74</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -9883,19 +9911,19 @@
         <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>0.49</v>
+        <v>11.2</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 32.1, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 32.3, need 83), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -9917,37 +9945,37 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GANECOS.NS</t>
+          <t>SUDARSCHEM.NS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>47.2</v>
+        <v>51.1</v>
       </c>
       <c r="E113" t="n">
-        <v>31.9</v>
+        <v>32.15</v>
       </c>
       <c r="F113" t="n">
-        <v>63</v>
+        <v>75.3</v>
       </c>
       <c r="G113" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H113" t="n">
-        <v>1108.7</v>
+        <v>999.25</v>
       </c>
       <c r="I113" t="n">
-        <v>950.46</v>
+        <v>885.64</v>
       </c>
       <c r="J113" t="n">
-        <v>1221.73</v>
+        <v>1080.4</v>
       </c>
       <c r="K113" t="n">
-        <v>1346.06</v>
+        <v>1169.66</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -9963,24 +9991,24 @@
         <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>3.15</v>
+        <v>0.49</v>
       </c>
       <c r="P113" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>UPTREND, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(3.1%&lt;10%)</t>
+          <t>CONF_FAIL(got 32.1, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T113" t="inlineStr">
@@ -9997,37 +10025,37 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>CUPID.NS</t>
+          <t>GANECOS.NS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>45.8</v>
+        <v>47.2</v>
       </c>
       <c r="E114" t="n">
-        <v>31.42</v>
+        <v>31.98</v>
       </c>
       <c r="F114" t="n">
-        <v>58.4</v>
+        <v>63</v>
       </c>
       <c r="G114" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="H114" t="n">
-        <v>212.24</v>
+        <v>1108.7</v>
       </c>
       <c r="I114" t="n">
-        <v>180.4</v>
+        <v>950.46</v>
       </c>
       <c r="J114" t="n">
-        <v>237.98</v>
+        <v>1221.73</v>
       </c>
       <c r="K114" t="n">
-        <v>263.71</v>
+        <v>1346.06</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -10043,19 +10071,19 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>27.3</v>
+        <v>3.15</v>
       </c>
       <c r="P114" t="n">
         <v>0</v>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+          <t>UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 31.4, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), INSTITUTIONAL_EXIT</t>
+          <t>CONF_FAIL(got 32.0, need 83), TQ_FAIL(got 63.0, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6)</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -10077,37 +10105,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SUMEETINDS.NS</t>
+          <t>CUPID.NS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SUMEETINDS</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>50.9</v>
+        <v>45.8</v>
       </c>
       <c r="E115" t="n">
-        <v>31.09</v>
+        <v>31.42</v>
       </c>
       <c r="F115" t="n">
-        <v>76.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="G115" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="H115" t="n">
-        <v>31.72</v>
+        <v>212.24</v>
       </c>
       <c r="I115" t="n">
-        <v>27.8</v>
+        <v>180.4</v>
       </c>
       <c r="J115" t="n">
-        <v>34.52</v>
+        <v>237.98</v>
       </c>
       <c r="K115" t="n">
-        <v>37.6</v>
+        <v>263.71</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -10123,19 +10151,19 @@
         <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>14.7</v>
+        <v>27.3</v>
       </c>
       <c r="P115" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 31.1, need 83), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+          <t>CONF_FAIL(got 31.4, need 83), TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.57, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -10169,7 +10197,7 @@
         <v>48.4</v>
       </c>
       <c r="E116" t="n">
-        <v>31.02</v>
+        <v>30.895</v>
       </c>
       <c r="F116" t="n">
         <v>69.90000000000001</v>
@@ -10215,7 +10243,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 31.0, need 83), TQ_FAIL(got 69.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=15&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 30.9, need 83), TQ_FAIL(got 69.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=15&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -10246,10 +10274,10 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E117" t="n">
-        <v>30.035</v>
+        <v>30.085</v>
       </c>
       <c r="F117" t="n">
         <v>68.5</v>
@@ -10286,7 +10314,7 @@
         <v>10.5</v>
       </c>
       <c r="P117" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
@@ -10295,7 +10323,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 30.0, need 83), TQ_FAIL(got 68.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 30.1, need 83), TQ_FAIL(got 68.5, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -10317,37 +10345,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AZAD.NS</t>
+          <t>GREAVESCOT.NS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>47.8</v>
+        <v>44.8</v>
       </c>
       <c r="E118" t="n">
-        <v>29.08</v>
+        <v>29.755</v>
       </c>
       <c r="F118" t="n">
-        <v>68.7</v>
+        <v>58.9</v>
       </c>
       <c r="G118" t="n">
         <v>1.45</v>
       </c>
       <c r="H118" t="n">
-        <v>2479.5</v>
+        <v>263.6</v>
       </c>
       <c r="I118" t="n">
-        <v>2153.75</v>
+        <v>224.06</v>
       </c>
       <c r="J118" t="n">
-        <v>2712.18</v>
+        <v>292.36</v>
       </c>
       <c r="K118" t="n">
-        <v>2968.12</v>
+        <v>322.91</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -10363,24 +10391,24 @@
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>9.09</v>
+        <v>8.1</v>
       </c>
       <c r="P118" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW(9.1%&lt;10%)</t>
+          <t>CONF_FAIL(got 29.8, need 83), TQ_FAIL(got 58.9, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>ROE_TOO_LOW</t>
+          <t>SECTOR_RANK_TOO_LOW</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
@@ -10397,37 +10425,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GREAVESCOT.NS</t>
+          <t>AZAD.NS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>44.8</v>
+        <v>47.8</v>
       </c>
       <c r="E119" t="n">
-        <v>28.88</v>
+        <v>29.14</v>
       </c>
       <c r="F119" t="n">
-        <v>58.9</v>
+        <v>68.7</v>
       </c>
       <c r="G119" t="n">
         <v>1.45</v>
       </c>
       <c r="H119" t="n">
-        <v>263.6</v>
+        <v>2479.5</v>
       </c>
       <c r="I119" t="n">
-        <v>224.06</v>
+        <v>2153.75</v>
       </c>
       <c r="J119" t="n">
-        <v>292.36</v>
+        <v>2712.18</v>
       </c>
       <c r="K119" t="n">
-        <v>322.91</v>
+        <v>2968.12</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -10443,19 +10471,19 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>8.1</v>
+        <v>9.09</v>
       </c>
       <c r="P119" t="n">
         <v>0</v>
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>CONF_FAIL(got 28.9, need 83), TQ_FAIL(got 58.9, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+          <t>CONF_FAIL(got 29.1, need 83), TQ_FAIL(got 68.7, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=12&gt;top6), INSTITUTIONAL_EXIT</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_TAKEN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B_WATCH_ME" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_NOT_MY_STYLE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_SO_CLOSE" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shadow Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="A_TAKEN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="B_WATCH_ME" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="C_NOT_MY_STYLE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D_SO_CLOSE" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Shadow Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Weekly Factor Summary" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +38,19 @@
       <b val="1"/>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -75,6 +87,12 @@
         <bgColor rgb="00B4C7E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -88,13 +106,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1050,6 +1073,992 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Weekly Factor Summary  (Jul 05 — Jul 11, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Recommendations in window: 6  |  Winners: 0  |  Losers: 0  |  Still Active: 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>All Picks (avg)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Winners (avg)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Losers (avg)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Still Active (avg)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>BUY (avg)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>WATCHLIST (avg)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>N (All)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Outcome factors (from Daily Tracking) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Max Gain%</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Max DD%</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Remaining Upside%</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hit Rate % (settled only)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>── Factor → Return  (what does each factor level actually pay?) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HIGH bucket</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HIGH avg Return%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HIGH Hit Rate%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MID bucket</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MID avg Return%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LOW bucket</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LOW avg Return%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LOW Hit Rate%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Edge (HIGH−LOW Return%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>≥ 62.10  (n=2)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>59.90 – 62.10  (n=1)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>≤ 59.90  (n=3)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>≥ 50.72  (n=2)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>48.41 – 50.72  (n=1)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>≤ 48.41  (n=3)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>≥ 75.80  (n=2)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>74.30 – 75.80  (n=1)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>≤ 74.30  (n=3)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>≥ 2.29  (n=2)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.67 – 2.29  (n=1)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>≤ 1.67  (n=3)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>≥ 0.00  (n=6)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.00 – 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>≥ 16.40  (n=2)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11.20 – 16.40  (n=1)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>≤ 11.20  (n=3)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>≥ 0.49  (n=2)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.12 – 0.49  (n=1)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>≤ 0.12  (n=3)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20664,7 +21673,6 @@
       <c r="G2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20779,10 +21787,6 @@
       <c r="D7" t="n">
         <v>114</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -17,6 +17,18 @@
     <sheet name="D_SO_CLOSE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Shadow Summary" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Weekly Factor Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Weekday Analysis" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Holding Period Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Category Comparison" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Conf x TQ Matrix" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Catalyst Analysis" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Fail Reason Analysis" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regime x Sector" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Confidence Trajectory" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Delivery Flow" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Sector Rotation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Portfolio Metrics" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Backtest vs Live" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -106,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +130,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2059,6 +2072,930 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Weekday Analysis — Does day-of-recommendation matter?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Worst Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INSIGHT: If Friday's Win Rate is &gt;5pts below the average, consider skipping Friday scans (weekend gap risk).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Holding Period Analysis — When do trades close out?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>% of All Closed</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No Daily Tracking data yet (need Holding Days column).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category Comparison — Do BUY, NEAR_MISS, WATCHLIST tiers differ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Avg TQ</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Opp Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEAR_MISS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WATCHLIST</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INSIGHT: BUY win rate should be &gt;= NEAR_MISS &gt;= WATCHLIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>If NEAR_MISS matches BUY, the tier boundary is too strict.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence × TQ Matrix — where do the two factors compound?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each cell shows: Win Rate% (n=count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Return% matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INSIGHT: If High×High dominates, tighten filter to require BOTH factors high.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catalyst Analysis — which catalysts actually pay off?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No parseable catalyst data with outcomes yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fail Reason Analysis — which amber flags actually predict losses?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Fail Reason</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count in Buys+NearMiss</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regime × Sector — which sectors win in each regime?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cell = Avg Return% (n=count). Blank if &lt;2 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No settled trades with Regime + Sector yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence Trajectory — does rising conf beat stable/falling?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Trajectory</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Confidence history too thin (need 2+ days per symbol). Wait ~1 week for meaningful data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rec Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deliv %Today</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Deliv 20d Avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DATAMATICS.NS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARKADE.NS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ANANTRAJ.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RPTECH.NS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EMBDL.NS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2152,6 +3089,945 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rank Today</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rank 5d Ago</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Portfolio Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AGRI_FOOD</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASSET_MGMT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUTO_ANCILLARY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANKING</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BUILDING_MAT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPITAL_GOODS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHEMICALS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEFENCE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>23</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INSURANCE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POWER_EQ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TELECOM</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TEXTILES</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Comparing 2026-07-10 vs n/a (≥5 trading days back)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PORTFOLIO METRICS (from Daily Tracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Daily Tracking sheet is empty</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BACKTEST vs LIVE DIVERGENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Backtest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(no backtest artefact found)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Run backtest_walkforward.py and export results.json</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -16,19 +16,19 @@
     <sheet name="C_NOT_MY_STYLE" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="D_SO_CLOSE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Shadow Summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Weekly Factor Summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Weekday Analysis" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Holding Period Analysis" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Category Comparison" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Conf x TQ Matrix" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Catalyst Analysis" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Fail Reason Analysis" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Regime x Sector" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Confidence Trajectory" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Delivery Flow" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Sector Rotation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Portfolio Metrics" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Backtest vs Live" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Weekday Analysis" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Holding Period Analysis" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Category Comparison" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Conf x TQ Matrix" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Catalyst Analysis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Fail Reason Analysis" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Regime x Sector" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Confidence Trajectory" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Delivery Flow" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Sector Rotation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Portfolio Metrics" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Backtest vs Live" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Weekly Factor Summary" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1092,6 +1092,1962 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Weekday Analysis — Does day-of-recommendation matter?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Worst Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INSIGHT: If Friday's Win Rate is &gt;5pts below the average, consider skipping Friday scans (weekend gap risk).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Holding Period Analysis — When do trades close out?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>% of All Closed</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No Daily Tracking data yet (need Holding Days column).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category Comparison — Do BUY, NEAR_MISS, WATCHLIST tiers differ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Avg TQ</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Opp Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEAR_MISS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WATCHLIST</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INSIGHT: BUY win rate should be &gt;= NEAR_MISS &gt;= WATCHLIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>If NEAR_MISS matches BUY, the tier boundary is too strict.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence × TQ Matrix — where do the two factors compound?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each cell shows: Win Rate% (n=count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Return% matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INSIGHT: If High×High dominates, tighten filter to require BOTH factors high.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catalyst Analysis — which catalysts actually pay off?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No parseable catalyst data with outcomes yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fail Reason Analysis — which amber flags actually predict losses?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Fail Reason</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count in Buys+NearMiss</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regime × Sector — which sectors win in each regime?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cell = Avg Return% (n=count). Blank if &lt;2 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No settled trades with Regime + Sector yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence Trajectory — does rising conf beat stable/falling?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Trajectory</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Confidence history too thin (need 2+ days per symbol). Wait ~1 week for meaningful data.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rec Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deliv %Today</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Deliv 20d Avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DATAMATICS.NS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="F2" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ARKADE.NS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.988</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ANANTRAJ.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38.41</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="F5" t="n">
+        <v>37.54</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RPTECH.NS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.01</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EMBDL.NS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="F7" t="n">
+        <v>46.21</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rank Today</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rank 5d Ago</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Portfolio Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AGRI_FOOD</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASSET_MGMT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUTO_ANCILLARY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANKING</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BUILDING_MAT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPITAL_GOODS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHEMICALS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>16</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEFENCE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>23</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INSURANCE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POWER_EQ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>15</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TELECOM</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TEXTILES</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Comparing 2026-07-10 vs n/a (≥5 trading days back)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tracking Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rec Date</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Day#</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Close</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Max Gain%</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Max DD%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>T1 Hit</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>T2 Hit</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Stop Hit</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Remaining Upside%</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PORTFOLIO METRICS (from Daily Tracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Daily Tracking sheet is empty</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BACKTEST vs LIVE DIVERGENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Backtest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(no backtest artefact found)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Run backtest_walkforward.py and export results.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1110,7 +3066,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Weekly Factor Summary  (Jul 05 — Jul 11, 2026)</t>
+          <t>Weekly Factor Summary  (Jul 06 — Jul 12, 2026)</t>
         </is>
       </c>
     </row>
@@ -2064,1970 +4020,6 @@
       <c r="J31" t="inlineStr">
         <is>
           <t>—</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Weekday Analysis — Does day-of-recommendation matter?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Weekday</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Best Trade%</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Worst Trade%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INSIGHT: If Friday's Win Rate is &gt;5pts below the average, consider skipping Friday scans (weekend gap risk).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Holding Period Analysis — When do trades close out?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Holding Days</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>% of All Closed</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>No Daily Tracking data yet (need Holding Days column).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Category Comparison — Do BUY, NEAR_MISS, WATCHLIST tiers differ?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Confidence</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>Avg TQ</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Opp Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEAR_MISS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G4" t="n">
-        <v>69.8</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>WATCHLIST</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>44</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="G5" t="n">
-        <v>58.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>INSIGHT: BUY win rate should be &gt;= NEAR_MISS &gt;= WATCHLIST.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>If NEAR_MISS matches BUY, the tier boundary is too strict.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Confidence × TQ Matrix — where do the two factors compound?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Each cell shows: Win Rate% (n=count)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Confidence \ TQ</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Low TQ</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Mid TQ</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>High TQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Low Conf</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mid Conf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>High Conf</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Avg Return% matrix</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Confidence \ TQ</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Low TQ</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Mid TQ</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>High TQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Low Conf</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Mid Conf</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>High Conf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>INSIGHT: If High×High dominates, tighten filter to require BOTH factors high.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Catalyst Analysis — which catalysts actually pay off?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Catalyst</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Best Trade%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>No parseable catalyst data with outcomes yet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Fail Reason Analysis — which amber flags actually predict losses?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Fail Reason</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count in Buys+NearMiss</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Regime × Sector — which sectors win in each regime?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cell = Avg Return% (n=count). Blank if &lt;2 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>No settled trades with Regime + Sector yet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Confidence Trajectory — does rising conf beat stable/falling?</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Trajectory</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Win Rate%</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Avg Return%</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Confidence history too thin (need 2+ days per symbol). Wait ~1 week for meaningful data.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Rec Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Return%</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Deliv %Today</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Deliv 20d Avg</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DATAMATICS.NS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44.51</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ARKADE.NS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="F3" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ANANTRAJ.NS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="F4" t="n">
-        <v>38.41</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ORCHPHARMA.NS</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="F5" t="n">
-        <v>37.54</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>WEAK</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RPTECH.NS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.574</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>STRONG_ACCUM</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EMBDL.NS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>46.21</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.086</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Tracking Date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rec Date</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Day#</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Close</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Volume</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Return%</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Max Gain%</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Max DD%</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>T1 Hit</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>T2 Hit</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Stop Hit</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Remaining Upside%</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Holding Days</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Rank Today</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Rank 5d Ago</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Velocity</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Portfolio Exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AGRI_FOOD</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ASSET_MGMT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>27</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>AUTO</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AUTO_ANCILLARY</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>BANKING</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>11</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BUILDING_MAT</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CAPITAL_GOODS</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CHEMICALS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CONSUMER</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>16</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DEFENCE</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>25</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DIVERSIFIED</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ELECTRONICS</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ENERGY</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>FINANCE</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>20</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>HEALTHCARE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>9</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>INFRA</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>23</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>INSURANCE</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>5</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LOGISTICS</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>24</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>METALS</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>19</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PHARMA</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>POWER_EQ</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>17</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REALTY</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RETAIL</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>15</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TELECOM</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>21</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TEXTILES</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Comparing 2026-07-10 vs n/a (≥5 trading days back)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>PORTFOLIO METRICS (from Daily Tracking)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Interpretation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Daily Tracking sheet is empty</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>BACKTEST vs LIVE DIVERGENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Backtest</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Live</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>(no backtest artefact found)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Run backtest_walkforward.py and export results.json</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Recommendations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Daily Tracking" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_TAKEN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B_WATCH_ME" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_NOT_MY_STYLE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_SO_CLOSE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shadow Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="KELLY Recommendations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="KELLY Daily Tracking" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KELLY Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily Tracking" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rejected" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Performance Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="A_TAKEN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="B_WATCH_ME" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="C_NOT_MY_STYLE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="D_SO_CLOSE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Shadow Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Weekly Factor Summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +41,19 @@
       <b val="1"/>
       <color rgb="00000000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -78,6 +90,12 @@
         <bgColor rgb="00B4C7E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,13 +109,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1977,7 +2000,6 @@
       <c r="G2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2092,10 +2114,992 @@
       <c r="D7" t="n">
         <v>116</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Weekly Factor Summary  (Jul 12 — Jul 18, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Recommendations in window: 4  |  Winners: 0  |  Losers: 0  |  Still Active: 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>All Picks (avg)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Winners (avg)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Losers (avg)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Still Active (avg)</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>BUY (avg)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>WATCHLIST (avg)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>N (All)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>62.58</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>70.03</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>70.03</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>70.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Outcome factors (from Daily Tracking) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Max Gain%</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Max DD%</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Remaining Upside%</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hit Rate % (settled only)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>── Factor → Return  (what does each factor level actually pay?) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HIGH bucket</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HIGH avg Return%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HIGH Hit Rate%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MID bucket</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MID avg Return%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LOW bucket</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LOW avg Return%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LOW Hit Rate%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Edge (HIGH−LOW Return%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>≥ 70.60  (n=2)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>67.60 – 70.60  (n=0)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>≤ 67.60  (n=2)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>≥ 70.00  (n=2)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>63.76 – 70.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>≤ 63.76  (n=2)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>≥ 76.50  (n=2)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>63.80 – 76.50  (n=0)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>≤ 63.80  (n=2)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>≥ 2.10  (n=2)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.54 – 2.10  (n=0)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>≤ 1.54  (n=2)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>≥ 0.00  (n=4)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.00 – 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>≥ 10.30  (n=2)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.00 – 10.30  (n=0)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=2)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>≥ 0.12  (n=2)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.02 – 0.12  (n=0)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>≤ 0.02  (n=2)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -20,6 +20,18 @@
     <sheet name="D_SO_CLOSE" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Shadow Summary" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Weekly Factor Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Weekday Analysis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Holding Period Analysis" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Category Comparison" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Conf x TQ Matrix" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Catalyst Analysis" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Fail Reason Analysis" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Regime x Sector" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Confidence Trajectory" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Delivery Flow" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Sector Rotation" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Portfolio Metrics" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Backtest vs Live" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -109,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,6 +133,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3106,6 +3119,566 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Weekday Analysis — Does day-of-recommendation matter?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Worst Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INSIGHT: If Friday's Win Rate is &gt;5pts below the average, consider skipping Friday scans (weekend gap risk).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Holding Period Analysis — When do trades close out?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>% of All Closed</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No Daily Tracking data yet (need Holding Days column).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category Comparison — Do BUY, NEAR_MISS, WATCHLIST tiers differ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>Avg TQ</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Opp Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>WATCHLIST</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>70</v>
+      </c>
+      <c r="G4" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INSIGHT: BUY win rate should be &gt;= NEAR_MISS &gt;= WATCHLIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>If NEAR_MISS matches BUY, the tier boundary is too strict.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence × TQ Matrix — where do the two factors compound?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each cell shows: Win Rate% (n=count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Return% matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INSIGHT: If High×High dominates, tighten filter to require BOTH factors high.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catalyst Analysis — which catalysts actually pay off?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No parseable catalyst data with outcomes yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fail Reason Analysis — which amber flags actually predict losses?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Fail Reason</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count in Buys+NearMiss</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3219,6 +3792,1068 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regime × Sector — which sectors win in each regime?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cell = Avg Return% (n=count). Blank if &lt;2 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No settled trades with Regime + Sector yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence Trajectory — does rising conf beat stable/falling?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Trajectory</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rec Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deliv %Today</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Deliv 20d Avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No nselib delivery data available (cache empty or nselib unavailable)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rank Today</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rank 5d Ago</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Portfolio Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AGRI_FOOD</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ASSET_MGMT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AUTO_ANCILLARY</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BANKING</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BUILDING_MAT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CAPITAL_GOODS</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CHEMICALS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>18</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEFENCE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ELECTRONICS</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INSURANCE</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POWER_EQ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TELECOM</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TEXTILES</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Comparing 2026-07-17 vs n/a (≥5 trading days back)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PORTFOLIO METRICS (from Daily Tracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Daily Tracking sheet is empty</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BACKTEST vs LIVE DIVERGENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Backtest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(no backtest artefact found)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Run backtest_walkforward.py and export results.json</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3889,7 +3889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3942,9 +3942,142 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>No nselib delivery data available (cache empty or nselib unavailable)</t>
-        </is>
-      </c>
+          <t>AMAGI.NS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39.74</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STARHEALTH.NS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ANANTRAJ.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EMBDL.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3995,25 +4128,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4023,25 +4152,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D3" t="n">
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4051,53 +4176,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4107,25 +4224,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4135,25 +4248,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4163,25 +4272,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4191,25 +4296,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4219,53 +4320,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>18</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>13</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4275,25 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4303,25 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4331,25 +4416,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -4359,25 +4440,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4387,25 +4464,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="C16" t="n">
+        <v>21</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4415,25 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4443,25 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>15</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4471,81 +4536,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>19</v>
+      </c>
+      <c r="C19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4555,25 +4608,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="C22" t="n">
+        <v>13</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4583,53 +4632,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="C23" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-13</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>21</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-17</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4639,53 +4680,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-22</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4695,25 +4728,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>17</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4723,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-07-17 vs n/a (≥5 trading days back)</t>
+          <t>Comparing 2026-07-24 vs 2026-07-17 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>50.28</v>
+        <v>42.99</v>
       </c>
       <c r="F2" t="n">
-        <v>39.74</v>
+        <v>41.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1.265</v>
+        <v>1.044</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>46.02</v>
+        <v>54.74</v>
       </c>
       <c r="F3" t="n">
-        <v>50.7</v>
+        <v>53.05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.908</v>
+        <v>1.032</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>46.67</v>
+        <v>55.83</v>
       </c>
       <c r="F4" t="n">
-        <v>37.81</v>
+        <v>39.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1.234</v>
+        <v>1.419</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>STRONG_ACCUM</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,13 +4064,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>41.27</v>
+        <v>49.81</v>
       </c>
       <c r="F5" t="n">
-        <v>45.25</v>
+        <v>45.16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.912</v>
+        <v>1.103</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
         <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4194,23 +4194,23 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4218,20 +4218,20 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4276,13 +4276,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,17 +4320,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4338,23 +4338,23 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4368,17 +4368,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,14 +4416,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4464,17 +4464,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4488,17 +4488,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,14 +4536,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
         <v>-4</v>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
         <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4650,23 +4650,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4704,17 +4704,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D26" t="n">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-07-24 vs 2026-07-17 (≥5 trading days back)</t>
+          <t>Comparing 2026-07-31 vs 2026-07-24 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42.99</v>
+        <v>42.2</v>
       </c>
       <c r="F2" t="n">
-        <v>41.17</v>
+        <v>43.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1.044</v>
+        <v>0.964</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>54.74</v>
+        <v>61.75</v>
       </c>
       <c r="F3" t="n">
-        <v>53.05</v>
+        <v>54.92</v>
       </c>
       <c r="G3" t="n">
-        <v>1.032</v>
+        <v>1.124</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,17 +4029,17 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>55.83</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>39.33</v>
+        <v>40.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.419</v>
+        <v>1.063</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>STRONG_ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>49.81</v>
+        <v>55.81</v>
       </c>
       <c r="F5" t="n">
-        <v>45.16</v>
+        <v>45.65</v>
       </c>
       <c r="G5" t="n">
-        <v>1.103</v>
+        <v>1.223</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D2" t="n">
         <v>24</v>
-      </c>
-      <c r="D2" t="n">
-        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4176,17 +4176,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4218,23 +4218,23 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" t="n">
         <v>23</v>
-      </c>
-      <c r="C9" t="n">
-        <v>26</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,21 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4464,41 +4464,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>STABLE</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>STABLE</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,14 +4536,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>-4</v>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D24" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D25" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4698,23 +4698,23 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Comparing 2026-07-31 vs 2026-07-24 (≥5 trading days back)</t>
+          <t>Comparing 2026-08-07 vs 2026-07-31 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="KELLY Recommendations" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="KELLY Daily Tracking" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="KELLY Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Daily Tracking" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Rejected" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Performance Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="A_TAKEN" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="B_WATCH_ME" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="C_NOT_MY_STYLE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="D_SO_CLOSE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Shadow Summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Weekly Factor Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Weekday Analysis" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Holding Period Analysis" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Category Comparison" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Conf x TQ Matrix" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Catalyst Analysis" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Fail Reason Analysis" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Regime x Sector" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Confidence Trajectory" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Delivery Flow" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Sector Rotation" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Portfolio Metrics" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Backtest vs Live" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Recommendations" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Daily Tracking" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KELLY Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A_TAKEN" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B_WATCH_ME" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C_NOT_MY_STYLE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_SO_CLOSE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shadow Summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Factor Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekday Analysis" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Period Analysis" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Comparison" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conf x TQ Matrix" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalyst Analysis" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fail Reason Analysis" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime x Sector" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Trajectory" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Flow" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Rotation" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Metrics" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest vs Live" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>42.2</v>
+        <v>27.23</v>
       </c>
       <c r="F2" t="n">
-        <v>43.78</v>
+        <v>40.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.964</v>
+        <v>0.676</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>DISTRIBUTION</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>61.75</v>
+        <v>63.54</v>
       </c>
       <c r="F3" t="n">
-        <v>54.92</v>
+        <v>54.95</v>
       </c>
       <c r="G3" t="n">
-        <v>1.124</v>
+        <v>1.156</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>42.34</v>
       </c>
       <c r="F4" t="n">
-        <v>40.45</v>
+        <v>41.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.063</v>
+        <v>1.011</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>55.81</v>
+        <v>53.79</v>
       </c>
       <c r="F5" t="n">
-        <v>45.65</v>
+        <v>46.8</v>
       </c>
       <c r="G5" t="n">
-        <v>1.223</v>
+        <v>1.149</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4090,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4170,23 +4170,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
         <v>23</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,21 +4320,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,17 +4392,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
         <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4464,17 +4464,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4482,23 +4482,23 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,14 +4560,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
         <v>-4</v>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4632,17 +4632,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4650,23 +4650,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4698,23 +4698,23 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12</v>
+        <v>-22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4722,23 +4722,23 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-18</v>
+        <v>-25</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4749,10 +4749,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Comparing 2026-08-07 vs 2026-07-31 (≥5 trading days back)</t>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RETAIL</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Comparing 2026-08-14 vs 2026-08-07 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>27.23</v>
+        <v>28.71</v>
       </c>
       <c r="F2" t="n">
-        <v>40.3</v>
+        <v>39.63</v>
       </c>
       <c r="G2" t="n">
-        <v>0.676</v>
+        <v>0.724</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DISTRIBUTION</t>
+          <t>WEAK</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,17 +3994,17 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>63.54</v>
+        <v>53.29</v>
       </c>
       <c r="F3" t="n">
-        <v>54.95</v>
+        <v>57.82</v>
       </c>
       <c r="G3" t="n">
-        <v>1.156</v>
+        <v>0.922</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>42.34</v>
+        <v>46.49</v>
       </c>
       <c r="F4" t="n">
-        <v>41.88</v>
+        <v>43.42</v>
       </c>
       <c r="G4" t="n">
-        <v>1.011</v>
+        <v>1.071</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>53.79</v>
+        <v>62.59</v>
       </c>
       <c r="F5" t="n">
-        <v>46.8</v>
+        <v>49.82</v>
       </c>
       <c r="G5" t="n">
-        <v>1.149</v>
+        <v>1.256</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>ACCUM</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,14 +4152,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
         <v>19</v>
@@ -4170,23 +4170,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,14 +4200,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
@@ -4224,14 +4224,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -4242,23 +4242,23 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,14 +4272,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4320,14 +4320,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ROTATING_IN</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,17 +4392,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4416,17 +4416,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4488,21 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4512,21 +4512,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D18" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4602,23 +4602,23 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4650,23 +4650,23 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D25" t="n">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4698,23 +4698,23 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>-22</v>
+        <v>-10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>-25</v>
+        <v>-13</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,25 +4752,21 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>26</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-21</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ROTATING_OUT</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4780,7 +4776,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Comparing 2026-08-14 vs 2026-08-07 (≥5 trading days back)</t>
+          <t>Comparing 2026-08-21 vs 2026-08-14 (≥5 trading days back)</t>
         </is>
       </c>
     </row>

--- a/shadow_master.xlsx
+++ b/shadow_master.xlsx
@@ -3959,17 +3959,17 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>28.71</v>
+        <v>42.95</v>
       </c>
       <c r="F2" t="n">
-        <v>39.63</v>
+        <v>40.37</v>
       </c>
       <c r="G2" t="n">
-        <v>0.724</v>
+        <v>1.064</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WEAK</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>53.29</v>
+        <v>56.31</v>
       </c>
       <c r="F3" t="n">
-        <v>57.82</v>
+        <v>57.26</v>
       </c>
       <c r="G3" t="n">
-        <v>0.922</v>
+        <v>0.983</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -4029,13 +4029,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>46.49</v>
+        <v>41.4</v>
       </c>
       <c r="F4" t="n">
-        <v>43.42</v>
+        <v>42.45</v>
       </c>
       <c r="G4" t="n">
-        <v>1.071</v>
+        <v>0.975</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -4064,17 +4064,17 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>62.59</v>
+        <v>45.33</v>
       </c>
       <c r="F5" t="n">
-        <v>49.82</v>
+        <v>50.06</v>
       </c>
       <c r="G5" t="n">
-        <v>1.256</v>
+        <v>0.906</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ACCUM</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -4128,17 +4128,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RETAIL</t>
+          <t>ASSET_MGMT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4152,17 +4152,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>METALS</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4170,23 +4170,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUTO_ANCILLARY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4200,17 +4200,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOGISTICS</t>
+          <t>ELECTRONICS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4224,17 +4224,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4248,17 +4248,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DIVERSIFIED</t>
+          <t>AGRI_FOOD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4272,17 +4272,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHEMICALS</t>
+          <t>AUTO_ANCILLARY</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
         <v>9</v>
-      </c>
-      <c r="D8" t="n">
-        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4314,23 +4314,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FINANCE</t>
+          <t>CONSUMER</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4344,21 +4344,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BUILDING_MAT</t>
+          <t>TELECOM</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4368,21 +4368,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASSET_MGMT</t>
+          <t>TEXTILES</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4392,21 +4392,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAPITAL_GOODS</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>STABLE</t>
+          <t>ROTATING_IN</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -4420,13 +4420,13 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>25</v>
+      </c>
+      <c r="C14" t="n">
         <v>26</v>
       </c>
-      <c r="C14" t="n">
-        <v>25</v>
-      </c>
       <c r="D14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4440,17 +4440,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TEXTILES</t>
+          <t>CAPITAL_GOODS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4464,21 +4464,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AGRI_FOOD</t>
+          <t>BANKING</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D16" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4488,21 +4488,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FINANCE</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ROTATING_OUT</t>
+          <t>STABLE</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4512,17 +4512,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONSUMER</t>
+          <t>BUILDING_MAT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4536,17 +4536,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEFENCE</t>
+          <t>DIVERSIFIED</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4560,17 +4560,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>POWER_EQ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4584,17 +4584,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INSURANCE</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4608,17 +4608,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CHEMICALS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4626,23 +4626,23 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>POWER_EQ</t>
+          <t>DEFENCE</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4656,17 +4656,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BANKING</t>
+          <t>METALS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4680,17 +4680,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INSURANCE</t>
+          <t>LOGISTICS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4698,23 +4698,23 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TELECOM</t>
+          <t>ENERGY</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4728,17 +4728,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>-13</v>
+        <v>-23</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4752,17 +4752,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ELECTRONICS</t>
+          <t>RETAIL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Comparing 2026-08-21 vs 2026-08-14 (≥5 trading days back)</t>
+          <t>Comparing 2026-08-28 vs 2026-08-21 (≥5 trading days back)</t>
         </is>
       </c>
     </row>
